--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,11 @@
           <t>금액(원)</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>편입~편출 누적수익률(%)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -495,6 +500,7 @@
       <c r="G2" t="n">
         <v>249300000</v>
       </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +532,7 @@
       <c r="G3" t="n">
         <v>19979400</v>
       </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -557,6 +564,7 @@
       <c r="G4" t="n">
         <v>20010000</v>
       </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -588,6 +596,7 @@
       <c r="G5" t="n">
         <v>249973500</v>
       </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -619,6 +628,7 @@
       <c r="G6" t="n">
         <v>20002180</v>
       </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -650,6 +660,7 @@
       <c r="G7" t="n">
         <v>29884500</v>
       </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -681,6 +692,7 @@
       <c r="G8" t="n">
         <v>20011900</v>
       </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -712,6 +724,7 @@
       <c r="G9" t="n">
         <v>20008000</v>
       </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,6 +756,7 @@
       <c r="G10" t="n">
         <v>19968000</v>
       </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -774,6 +788,7 @@
       <c r="G11" t="n">
         <v>19960000</v>
       </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -805,6 +820,7 @@
       <c r="G12" t="n">
         <v>19998440</v>
       </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -836,6 +852,7 @@
       <c r="G13" t="n">
         <v>20002500</v>
       </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -867,6 +884,7 @@
       <c r="G14" t="n">
         <v>19993750</v>
       </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -898,6 +916,7 @@
       <c r="G15" t="n">
         <v>20051500</v>
       </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -929,6 +948,7 @@
       <c r="G16" t="n">
         <v>19993750</v>
       </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -960,6 +980,7 @@
       <c r="G17" t="n">
         <v>20011200</v>
       </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -991,6 +1012,7 @@
       <c r="G18" t="n">
         <v>20076000</v>
       </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1022,6 +1044,7 @@
       <c r="G19" t="n">
         <v>34866000</v>
       </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1053,6 +1076,7 @@
       <c r="G20" t="n">
         <v>20043000</v>
       </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1084,6 +1108,7 @@
       <c r="G21" t="n">
         <v>19962000</v>
       </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1115,6 +1140,7 @@
       <c r="G22" t="n">
         <v>19980500</v>
       </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1146,6 +1172,7 @@
       <c r="G23" t="n">
         <v>19980000</v>
       </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1177,6 +1204,7 @@
       <c r="G24" t="n">
         <v>20013750</v>
       </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1208,6 +1236,7 @@
       <c r="G25" t="n">
         <v>20060600</v>
       </c>
+      <c r="H25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,62 +492,64 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1662000</v>
+        <v>10800</v>
       </c>
       <c r="F2" t="n">
-        <v>150</v>
+        <v>1872</v>
       </c>
       <c r="G2" t="n">
-        <v>249300000</v>
+        <v>20217600</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49700</v>
+        <v>11880</v>
       </c>
       <c r="F3" t="n">
-        <v>402</v>
+        <v>1474</v>
       </c>
       <c r="G3" t="n">
-        <v>19979400</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,126 +558,130 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>435000</v>
+        <v>20200</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>1501</v>
       </c>
       <c r="G4" t="n">
-        <v>20010000</v>
+        <v>30320200</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>268500</v>
+        <v>102200</v>
       </c>
       <c r="F5" t="n">
-        <v>931</v>
+        <v>198</v>
       </c>
       <c r="G5" t="n">
-        <v>249973500</v>
+        <v>20235600</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>13570</v>
+        <v>23450</v>
       </c>
       <c r="F6" t="n">
-        <v>1474</v>
+        <v>762</v>
       </c>
       <c r="G6" t="n">
-        <v>20002180</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>17868900</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-10.67</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>343500</v>
+        <v>22050</v>
       </c>
       <c r="F7" t="n">
-        <v>87</v>
+        <v>875</v>
       </c>
       <c r="G7" t="n">
-        <v>29884500</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,47 +690,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>34150</v>
+        <v>32550</v>
       </c>
       <c r="F8" t="n">
-        <v>586</v>
+        <v>621</v>
       </c>
       <c r="G8" t="n">
-        <v>20011900</v>
+        <v>20213550</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>488000</v>
+        <v>99700</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>180</v>
       </c>
       <c r="G9" t="n">
-        <v>20008000</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -734,12 +742,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -748,13 +756,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>153600</v>
+        <v>1662000</v>
       </c>
       <c r="F10" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="G10" t="n">
-        <v>19968000</v>
+        <v>249300000</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -766,12 +774,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -780,13 +788,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>99800</v>
+        <v>49700</v>
       </c>
       <c r="F11" t="n">
-        <v>200</v>
+        <v>402</v>
       </c>
       <c r="G11" t="n">
-        <v>19960000</v>
+        <v>19979400</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -798,12 +806,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -812,13 +820,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040</v>
+        <v>435000</v>
       </c>
       <c r="F12" t="n">
-        <v>3311</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>19998440</v>
+        <v>20010000</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -830,12 +838,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -844,13 +852,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>26250</v>
+        <v>268500</v>
       </c>
       <c r="F13" t="n">
-        <v>762</v>
+        <v>931</v>
       </c>
       <c r="G13" t="n">
-        <v>20002500</v>
+        <v>249973500</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -862,12 +870,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,13 +884,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>22850</v>
+        <v>13570</v>
       </c>
       <c r="F14" t="n">
-        <v>875</v>
+        <v>1474</v>
       </c>
       <c r="G14" t="n">
-        <v>19993750</v>
+        <v>20002180</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -894,12 +902,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -908,13 +916,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>168500</v>
+        <v>343500</v>
       </c>
       <c r="F15" t="n">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>20051500</v>
+        <v>29884500</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -926,12 +934,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -940,13 +948,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>22850</v>
+        <v>34150</v>
       </c>
       <c r="F16" t="n">
-        <v>875</v>
+        <v>586</v>
       </c>
       <c r="G16" t="n">
-        <v>19993750</v>
+        <v>20011900</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -958,12 +966,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -972,13 +980,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>37900</v>
+        <v>488000</v>
       </c>
       <c r="F17" t="n">
-        <v>528</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>20011200</v>
+        <v>20008000</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -990,12 +998,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1004,13 +1012,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>239000</v>
+        <v>153600</v>
       </c>
       <c r="F18" t="n">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="G18" t="n">
-        <v>20076000</v>
+        <v>19968000</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1022,12 +1030,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1036,13 +1044,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>298000</v>
+        <v>99800</v>
       </c>
       <c r="F19" t="n">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>34866000</v>
+        <v>19960000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1054,12 +1062,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1068,13 +1076,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>393000</v>
+        <v>6040</v>
       </c>
       <c r="F20" t="n">
-        <v>51</v>
+        <v>3311</v>
       </c>
       <c r="G20" t="n">
-        <v>20043000</v>
+        <v>19998440</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1086,12 +1094,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1100,13 +1108,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>110900</v>
+        <v>26250</v>
       </c>
       <c r="F21" t="n">
-        <v>180</v>
+        <v>762</v>
       </c>
       <c r="G21" t="n">
-        <v>19962000</v>
+        <v>20002500</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1118,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1132,13 +1140,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>44500</v>
+        <v>22850</v>
       </c>
       <c r="F22" t="n">
-        <v>449</v>
+        <v>875</v>
       </c>
       <c r="G22" t="n">
-        <v>19980500</v>
+        <v>19993750</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1150,12 +1158,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1164,13 +1172,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>135000</v>
+        <v>168500</v>
       </c>
       <c r="F23" t="n">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="G23" t="n">
-        <v>19980000</v>
+        <v>20051500</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1182,12 +1190,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1196,13 +1204,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>33750</v>
+        <v>22850</v>
       </c>
       <c r="F24" t="n">
-        <v>593</v>
+        <v>875</v>
       </c>
       <c r="G24" t="n">
-        <v>20013750</v>
+        <v>19993750</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1214,29 +1222,285 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F25" t="n">
+        <v>528</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20011200</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>코스맥스</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>192820</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>239000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>84</v>
+      </c>
+      <c r="G26" t="n">
+        <v>20076000</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>298000</v>
+      </c>
+      <c r="F27" t="n">
+        <v>117</v>
+      </c>
+      <c r="G27" t="n">
+        <v>34866000</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>393000</v>
+      </c>
+      <c r="F28" t="n">
+        <v>51</v>
+      </c>
+      <c r="G28" t="n">
+        <v>20043000</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F29" t="n">
+        <v>180</v>
+      </c>
+      <c r="G29" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F30" t="n">
+        <v>449</v>
+      </c>
+      <c r="G30" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F31" t="n">
+        <v>148</v>
+      </c>
+      <c r="G31" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F32" t="n">
+        <v>593</v>
+      </c>
+      <c r="G32" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
         <v>124600</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F33" t="n">
         <v>161</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G33" t="n">
         <v>20060600</v>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,115 +473,113 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10800</v>
+        <v>1671000</v>
       </c>
       <c r="F2" t="n">
-        <v>1872</v>
+        <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>20217600</v>
+        <v>73524000</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11880</v>
+        <v>50600</v>
       </c>
       <c r="F3" t="n">
-        <v>1474</v>
+        <v>184</v>
       </c>
       <c r="G3" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>9310400</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20200</v>
+        <v>11720</v>
       </c>
       <c r="F4" t="n">
-        <v>1501</v>
+        <v>658</v>
       </c>
       <c r="G4" t="n">
-        <v>30320200</v>
+        <v>7711760</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -590,196 +588,190 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102200</v>
+        <v>414000</v>
       </c>
       <c r="F5" t="n">
-        <v>198</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>20235600</v>
+        <v>10764000</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23450</v>
+        <v>257000</v>
       </c>
       <c r="F6" t="n">
-        <v>762</v>
+        <v>239</v>
       </c>
       <c r="G6" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>61423000</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>22050</v>
+        <v>33900</v>
       </c>
       <c r="F7" t="n">
-        <v>875</v>
+        <v>289</v>
       </c>
       <c r="G7" t="n">
-        <v>19293750</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-3.5</v>
-      </c>
+        <v>9797100</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>32550</v>
+        <v>515000</v>
       </c>
       <c r="F8" t="n">
-        <v>621</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>20213550</v>
+        <v>8755000</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>99700</v>
+        <v>141200</v>
       </c>
       <c r="F9" t="n">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="G9" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>11296000</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1662000</v>
+        <v>6320</v>
       </c>
       <c r="F10" t="n">
-        <v>150</v>
+        <v>1381</v>
       </c>
       <c r="G10" t="n">
-        <v>249300000</v>
+        <v>8727920</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -788,350 +780,354 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>49700</v>
+        <v>90300</v>
       </c>
       <c r="F11" t="n">
-        <v>402</v>
+        <v>328</v>
       </c>
       <c r="G11" t="n">
-        <v>19979400</v>
+        <v>29618400</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>435000</v>
+        <v>163100</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="G12" t="n">
-        <v>20010000</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>268500</v>
+        <v>37900</v>
       </c>
       <c r="F13" t="n">
-        <v>931</v>
+        <v>161</v>
       </c>
       <c r="G13" t="n">
-        <v>249973500</v>
+        <v>6101900</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13570</v>
+        <v>19990</v>
       </c>
       <c r="F14" t="n">
-        <v>1474</v>
+        <v>608</v>
       </c>
       <c r="G14" t="n">
-        <v>20002180</v>
+        <v>12153920</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>343500</v>
+        <v>35100</v>
       </c>
       <c r="F15" t="n">
-        <v>87</v>
+        <v>317</v>
       </c>
       <c r="G15" t="n">
-        <v>29884500</v>
+        <v>11126700</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>34150</v>
+        <v>286000</v>
       </c>
       <c r="F16" t="n">
-        <v>586</v>
+        <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>20011900</v>
+        <v>5720000</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>488000</v>
+        <v>416000</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G17" t="n">
-        <v>20008000</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>153600</v>
+        <v>49450</v>
       </c>
       <c r="F18" t="n">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G18" t="n">
-        <v>19968000</v>
+        <v>7466950</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>99800</v>
+        <v>138000</v>
       </c>
       <c r="F19" t="n">
-        <v>200</v>
+        <v>67</v>
       </c>
       <c r="G19" t="n">
-        <v>19960000</v>
+        <v>9246000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6040</v>
+        <v>31950</v>
       </c>
       <c r="F20" t="n">
-        <v>3311</v>
+        <v>335</v>
       </c>
       <c r="G20" t="n">
-        <v>19998440</v>
+        <v>10703250</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>26250</v>
+        <v>124800</v>
       </c>
       <c r="F21" t="n">
-        <v>762</v>
+        <v>77</v>
       </c>
       <c r="G21" t="n">
-        <v>20002500</v>
+        <v>9609600</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1140,62 +1136,64 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>22850</v>
+        <v>10800</v>
       </c>
       <c r="F22" t="n">
-        <v>875</v>
+        <v>1872</v>
       </c>
       <c r="G22" t="n">
-        <v>19993750</v>
+        <v>20217600</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>168500</v>
+        <v>11880</v>
       </c>
       <c r="F23" t="n">
-        <v>119</v>
+        <v>1474</v>
       </c>
       <c r="G23" t="n">
-        <v>20051500</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1204,126 +1202,130 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>22850</v>
+        <v>20200</v>
       </c>
       <c r="F24" t="n">
-        <v>875</v>
+        <v>1501</v>
       </c>
       <c r="G24" t="n">
-        <v>19993750</v>
+        <v>30320200</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>37900</v>
+        <v>102200</v>
       </c>
       <c r="F25" t="n">
-        <v>528</v>
+        <v>198</v>
       </c>
       <c r="G25" t="n">
-        <v>20011200</v>
+        <v>20235600</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>239000</v>
+        <v>23450</v>
       </c>
       <c r="F26" t="n">
-        <v>84</v>
+        <v>762</v>
       </c>
       <c r="G26" t="n">
-        <v>20076000</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>17868900</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-10.67</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>298000</v>
+        <v>22050</v>
       </c>
       <c r="F27" t="n">
-        <v>117</v>
+        <v>875</v>
       </c>
       <c r="G27" t="n">
-        <v>34866000</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1332,20 +1334,20 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>393000</v>
+        <v>32550</v>
       </c>
       <c r="F28" t="n">
-        <v>51</v>
+        <v>621</v>
       </c>
       <c r="G28" t="n">
-        <v>20043000</v>
+        <v>20213550</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1360,19 +1362,21 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>110900</v>
+        <v>99700</v>
       </c>
       <c r="F29" t="n">
         <v>180</v>
       </c>
       <c r="G29" t="n">
-        <v>19962000</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1382,12 +1386,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1396,13 +1400,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>44500</v>
+        <v>1662000</v>
       </c>
       <c r="F30" t="n">
-        <v>449</v>
+        <v>150</v>
       </c>
       <c r="G30" t="n">
-        <v>19980500</v>
+        <v>249300000</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1414,12 +1418,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1428,13 +1432,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>135000</v>
+        <v>49700</v>
       </c>
       <c r="F31" t="n">
-        <v>148</v>
+        <v>402</v>
       </c>
       <c r="G31" t="n">
-        <v>19980000</v>
+        <v>19979400</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1446,12 +1450,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1460,13 +1464,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>33750</v>
+        <v>435000</v>
       </c>
       <c r="F32" t="n">
-        <v>593</v>
+        <v>46</v>
       </c>
       <c r="G32" t="n">
-        <v>20013750</v>
+        <v>20010000</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1478,29 +1482,669 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>268500</v>
+      </c>
+      <c r="F33" t="n">
+        <v>931</v>
+      </c>
+      <c r="G33" t="n">
+        <v>249973500</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>이수화학</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>005950</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>13570</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1474</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20002180</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>006260</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>343500</v>
+      </c>
+      <c r="F35" t="n">
+        <v>87</v>
+      </c>
+      <c r="G35" t="n">
+        <v>29884500</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>006360</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>34150</v>
+      </c>
+      <c r="F36" t="n">
+        <v>586</v>
+      </c>
+      <c r="G36" t="n">
+        <v>20011900</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>006400</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>488000</v>
+      </c>
+      <c r="F37" t="n">
+        <v>41</v>
+      </c>
+      <c r="G37" t="n">
+        <v>20008000</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>S-OIL</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>010950</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>153600</v>
+      </c>
+      <c r="F38" t="n">
+        <v>130</v>
+      </c>
+      <c r="G38" t="n">
+        <v>19968000</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SK텔레콤</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>017670</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>99800</v>
+      </c>
+      <c r="F39" t="n">
+        <v>200</v>
+      </c>
+      <c r="G39" t="n">
+        <v>19960000</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>팬오션</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>028670</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6040</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3311</v>
+      </c>
+      <c r="G40" t="n">
+        <v>19998440</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>STX엔진</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>077970</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>26250</v>
+      </c>
+      <c r="F41" t="n">
+        <v>762</v>
+      </c>
+      <c r="G41" t="n">
+        <v>20002500</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>089890</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>22850</v>
+      </c>
+      <c r="F42" t="n">
+        <v>875</v>
+      </c>
+      <c r="G42" t="n">
+        <v>19993750</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>KB금융</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>105560</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>168500</v>
+      </c>
+      <c r="F43" t="n">
+        <v>119</v>
+      </c>
+      <c r="G43" t="n">
+        <v>20051500</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>22850</v>
+      </c>
+      <c r="F44" t="n">
+        <v>875</v>
+      </c>
+      <c r="G44" t="n">
+        <v>19993750</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F45" t="n">
+        <v>528</v>
+      </c>
+      <c r="G45" t="n">
+        <v>20011200</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>코스맥스</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>192820</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>239000</v>
+      </c>
+      <c r="F46" t="n">
+        <v>84</v>
+      </c>
+      <c r="G46" t="n">
+        <v>20076000</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>298000</v>
+      </c>
+      <c r="F47" t="n">
+        <v>117</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34866000</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>393000</v>
+      </c>
+      <c r="F48" t="n">
+        <v>51</v>
+      </c>
+      <c r="G48" t="n">
+        <v>20043000</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F49" t="n">
+        <v>180</v>
+      </c>
+      <c r="G49" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F50" t="n">
+        <v>449</v>
+      </c>
+      <c r="G50" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F51" t="n">
+        <v>148</v>
+      </c>
+      <c r="G51" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F52" t="n">
+        <v>593</v>
+      </c>
+      <c r="G52" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
         <v>124600</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F53" t="n">
         <v>161</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G53" t="n">
         <v>20060600</v>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,128 +473,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1671000</v>
+        <v>28200</v>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>1084</v>
       </c>
       <c r="G2" t="n">
-        <v>73524000</v>
+        <v>30568800</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50600</v>
+        <v>398000</v>
       </c>
       <c r="F3" t="n">
-        <v>184</v>
+        <v>72</v>
       </c>
       <c r="G3" t="n">
-        <v>9310400</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11720</v>
+        <v>5620</v>
       </c>
       <c r="F4" t="n">
-        <v>658</v>
+        <v>4692</v>
       </c>
       <c r="G4" t="n">
-        <v>7711760</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>26369040</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-8.210000000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>414000</v>
+        <v>126900</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>241</v>
       </c>
       <c r="G5" t="n">
-        <v>10764000</v>
+        <v>30582900</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -606,12 +610,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -620,13 +624,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>257000</v>
+        <v>1671000</v>
       </c>
       <c r="F6" t="n">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>61423000</v>
+        <v>73524000</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -638,12 +642,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,13 +656,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>33900</v>
+        <v>50600</v>
       </c>
       <c r="F7" t="n">
-        <v>289</v>
+        <v>184</v>
       </c>
       <c r="G7" t="n">
-        <v>9797100</v>
+        <v>9310400</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -670,12 +674,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,13 +688,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>515000</v>
+        <v>11720</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>658</v>
       </c>
       <c r="G8" t="n">
-        <v>8755000</v>
+        <v>7711760</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -702,12 +706,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -716,13 +720,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>141200</v>
+        <v>414000</v>
       </c>
       <c r="F9" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="G9" t="n">
-        <v>11296000</v>
+        <v>10764000</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -734,27 +738,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6320</v>
+        <v>257000</v>
       </c>
       <c r="F10" t="n">
-        <v>1381</v>
+        <v>239</v>
       </c>
       <c r="G10" t="n">
-        <v>8727920</v>
+        <v>61423000</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -766,27 +770,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>90300</v>
+        <v>33900</v>
       </c>
       <c r="F11" t="n">
-        <v>328</v>
+        <v>289</v>
       </c>
       <c r="G11" t="n">
-        <v>29618400</v>
+        <v>9797100</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -798,31 +802,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>163100</v>
+        <v>515000</v>
       </c>
       <c r="F12" t="n">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>8755000</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -832,12 +834,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -846,13 +848,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>37900</v>
+        <v>141200</v>
       </c>
       <c r="F13" t="n">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="G13" t="n">
-        <v>6101900</v>
+        <v>11296000</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -864,12 +866,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -878,13 +880,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>19990</v>
+        <v>6320</v>
       </c>
       <c r="F14" t="n">
-        <v>608</v>
+        <v>1381</v>
       </c>
       <c r="G14" t="n">
-        <v>12153920</v>
+        <v>8727920</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -896,27 +898,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>35100</v>
+        <v>90300</v>
       </c>
       <c r="F15" t="n">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="G15" t="n">
-        <v>11126700</v>
+        <v>29618400</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -928,29 +930,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>286000</v>
+        <v>163100</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G16" t="n">
-        <v>5720000</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -960,31 +964,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>416000</v>
+        <v>37900</v>
       </c>
       <c r="F17" t="n">
-        <v>51</v>
+        <v>161</v>
       </c>
       <c r="G17" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H17" t="n">
-        <v>5.85</v>
-      </c>
+        <v>6101900</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -994,12 +996,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1008,13 +1010,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>49450</v>
+        <v>19990</v>
       </c>
       <c r="F18" t="n">
-        <v>151</v>
+        <v>608</v>
       </c>
       <c r="G18" t="n">
-        <v>7466950</v>
+        <v>12153920</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1026,12 +1028,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1040,13 +1042,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>138000</v>
+        <v>35100</v>
       </c>
       <c r="F19" t="n">
-        <v>67</v>
+        <v>317</v>
       </c>
       <c r="G19" t="n">
-        <v>9246000</v>
+        <v>11126700</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1058,12 +1060,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1072,13 +1074,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>31950</v>
+        <v>286000</v>
       </c>
       <c r="F20" t="n">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>10703250</v>
+        <v>5720000</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1090,142 +1092,142 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>124800</v>
+        <v>416000</v>
       </c>
       <c r="F21" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>9609600</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>10800</v>
+        <v>49450</v>
       </c>
       <c r="F22" t="n">
-        <v>1872</v>
+        <v>151</v>
       </c>
       <c r="G22" t="n">
-        <v>20217600</v>
+        <v>7466950</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>11880</v>
+        <v>138000</v>
       </c>
       <c r="F23" t="n">
-        <v>1474</v>
+        <v>67</v>
       </c>
       <c r="G23" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>9246000</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>20200</v>
+        <v>31950</v>
       </c>
       <c r="F24" t="n">
-        <v>1501</v>
+        <v>335</v>
       </c>
       <c r="G24" t="n">
-        <v>30320200</v>
+        <v>10703250</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1234,13 +1236,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102200</v>
+        <v>124800</v>
       </c>
       <c r="F25" t="n">
-        <v>198</v>
+        <v>77</v>
       </c>
       <c r="G25" t="n">
-        <v>20235600</v>
+        <v>9609600</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1252,31 +1254,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>23450</v>
+        <v>10800</v>
       </c>
       <c r="F26" t="n">
-        <v>762</v>
+        <v>1872</v>
       </c>
       <c r="G26" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20217600</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1300,16 +1300,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>22050</v>
+        <v>11880</v>
       </c>
       <c r="F27" t="n">
-        <v>875</v>
+        <v>1474</v>
       </c>
       <c r="G27" t="n">
-        <v>19293750</v>
+        <v>17511120</v>
       </c>
       <c r="H27" t="n">
-        <v>-3.5</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="28">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>32550</v>
+        <v>20200</v>
       </c>
       <c r="F28" t="n">
-        <v>621</v>
+        <v>1501</v>
       </c>
       <c r="G28" t="n">
-        <v>20213550</v>
+        <v>30320200</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1352,110 +1352,112 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>99700</v>
+        <v>102200</v>
       </c>
       <c r="F29" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="G29" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20235600</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1662000</v>
+        <v>23450</v>
       </c>
       <c r="F30" t="n">
-        <v>150</v>
+        <v>762</v>
       </c>
       <c r="G30" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>17868900</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-10.67</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>49700</v>
+        <v>22050</v>
       </c>
       <c r="F31" t="n">
-        <v>402</v>
+        <v>875</v>
       </c>
       <c r="G31" t="n">
-        <v>19979400</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1464,47 +1466,49 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>435000</v>
+        <v>32550</v>
       </c>
       <c r="F32" t="n">
-        <v>46</v>
+        <v>621</v>
       </c>
       <c r="G32" t="n">
-        <v>20010000</v>
+        <v>20213550</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>268500</v>
+        <v>99700</v>
       </c>
       <c r="F33" t="n">
-        <v>931</v>
+        <v>180</v>
       </c>
       <c r="G33" t="n">
-        <v>249973500</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1514,12 +1518,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1528,13 +1532,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>13570</v>
+        <v>1662000</v>
       </c>
       <c r="F34" t="n">
-        <v>1474</v>
+        <v>150</v>
       </c>
       <c r="G34" t="n">
-        <v>20002180</v>
+        <v>249300000</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1546,12 +1550,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1560,13 +1564,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>343500</v>
+        <v>49700</v>
       </c>
       <c r="F35" t="n">
-        <v>87</v>
+        <v>402</v>
       </c>
       <c r="G35" t="n">
-        <v>29884500</v>
+        <v>19979400</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1578,12 +1582,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1592,13 +1596,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>34150</v>
+        <v>435000</v>
       </c>
       <c r="F36" t="n">
-        <v>586</v>
+        <v>46</v>
       </c>
       <c r="G36" t="n">
-        <v>20011900</v>
+        <v>20010000</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1610,12 +1614,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1624,13 +1628,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>488000</v>
+        <v>268500</v>
       </c>
       <c r="F37" t="n">
-        <v>41</v>
+        <v>931</v>
       </c>
       <c r="G37" t="n">
-        <v>20008000</v>
+        <v>249973500</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1642,12 +1646,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1656,13 +1660,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>153600</v>
+        <v>13570</v>
       </c>
       <c r="F38" t="n">
-        <v>130</v>
+        <v>1474</v>
       </c>
       <c r="G38" t="n">
-        <v>19968000</v>
+        <v>20002180</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1674,12 +1678,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1688,13 +1692,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>99800</v>
+        <v>343500</v>
       </c>
       <c r="F39" t="n">
-        <v>200</v>
+        <v>87</v>
       </c>
       <c r="G39" t="n">
-        <v>19960000</v>
+        <v>29884500</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1706,12 +1710,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1720,13 +1724,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6040</v>
+        <v>34150</v>
       </c>
       <c r="F40" t="n">
-        <v>3311</v>
+        <v>586</v>
       </c>
       <c r="G40" t="n">
-        <v>19998440</v>
+        <v>20011900</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1738,12 +1742,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1752,13 +1756,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>26250</v>
+        <v>488000</v>
       </c>
       <c r="F41" t="n">
-        <v>762</v>
+        <v>41</v>
       </c>
       <c r="G41" t="n">
-        <v>20002500</v>
+        <v>20008000</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1770,12 +1774,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1784,13 +1788,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>22850</v>
+        <v>153600</v>
       </c>
       <c r="F42" t="n">
-        <v>875</v>
+        <v>130</v>
       </c>
       <c r="G42" t="n">
-        <v>19993750</v>
+        <v>19968000</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1802,12 +1806,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1816,13 +1820,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>168500</v>
+        <v>99800</v>
       </c>
       <c r="F43" t="n">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="G43" t="n">
-        <v>20051500</v>
+        <v>19960000</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1834,12 +1838,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1848,13 +1852,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>22850</v>
+        <v>6040</v>
       </c>
       <c r="F44" t="n">
-        <v>875</v>
+        <v>3311</v>
       </c>
       <c r="G44" t="n">
-        <v>19993750</v>
+        <v>19998440</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1866,12 +1870,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1880,13 +1884,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>37900</v>
+        <v>26250</v>
       </c>
       <c r="F45" t="n">
-        <v>528</v>
+        <v>762</v>
       </c>
       <c r="G45" t="n">
-        <v>20011200</v>
+        <v>20002500</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1898,12 +1902,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1912,13 +1916,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>239000</v>
+        <v>22850</v>
       </c>
       <c r="F46" t="n">
-        <v>84</v>
+        <v>875</v>
       </c>
       <c r="G46" t="n">
-        <v>20076000</v>
+        <v>19993750</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1930,12 +1934,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1944,13 +1948,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>298000</v>
+        <v>168500</v>
       </c>
       <c r="F47" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G47" t="n">
-        <v>34866000</v>
+        <v>20051500</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1962,12 +1966,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1976,13 +1980,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>393000</v>
+        <v>22850</v>
       </c>
       <c r="F48" t="n">
-        <v>51</v>
+        <v>875</v>
       </c>
       <c r="G48" t="n">
-        <v>20043000</v>
+        <v>19993750</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1994,12 +1998,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2008,13 +2012,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>110900</v>
+        <v>37900</v>
       </c>
       <c r="F49" t="n">
-        <v>180</v>
+        <v>528</v>
       </c>
       <c r="G49" t="n">
-        <v>19962000</v>
+        <v>20011200</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2026,12 +2030,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2040,13 +2044,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>44500</v>
+        <v>239000</v>
       </c>
       <c r="F50" t="n">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="G50" t="n">
-        <v>19980500</v>
+        <v>20076000</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2058,12 +2062,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2072,13 +2076,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>135000</v>
+        <v>298000</v>
       </c>
       <c r="F51" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="G51" t="n">
-        <v>19980000</v>
+        <v>34866000</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2090,12 +2094,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2104,13 +2108,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>33750</v>
+        <v>393000</v>
       </c>
       <c r="F52" t="n">
-        <v>593</v>
+        <v>51</v>
       </c>
       <c r="G52" t="n">
-        <v>20013750</v>
+        <v>20043000</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2122,29 +2126,157 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F53" t="n">
+        <v>180</v>
+      </c>
+      <c r="G53" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F54" t="n">
+        <v>449</v>
+      </c>
+      <c r="G54" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F55" t="n">
+        <v>148</v>
+      </c>
+      <c r="G55" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F56" t="n">
+        <v>593</v>
+      </c>
+      <c r="G56" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
         <v>124600</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F57" t="n">
         <v>161</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G57" t="n">
         <v>20060600</v>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,30 +492,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>28200</v>
+        <v>22250</v>
       </c>
       <c r="F2" t="n">
-        <v>1084</v>
+        <v>1373</v>
       </c>
       <c r="G2" t="n">
-        <v>30568800</v>
+        <v>30549250</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,32 +524,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>398000</v>
+        <v>33500</v>
       </c>
       <c r="F3" t="n">
-        <v>72</v>
+        <v>845</v>
       </c>
       <c r="G3" t="n">
-        <v>28656000</v>
+        <v>28307500</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.88</v>
+        <v>-9.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5620</v>
+        <v>300000</v>
       </c>
       <c r="F4" t="n">
-        <v>4692</v>
+        <v>104</v>
       </c>
       <c r="G4" t="n">
-        <v>26369040</v>
+        <v>31200000</v>
       </c>
       <c r="H4" t="n">
-        <v>-8.210000000000001</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="5">
@@ -578,12 +578,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -592,109 +592,113 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>126900</v>
+        <v>28200</v>
       </c>
       <c r="F5" t="n">
-        <v>241</v>
+        <v>1084</v>
       </c>
       <c r="G5" t="n">
-        <v>30582900</v>
+        <v>30568800</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1671000</v>
+        <v>398000</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="G6" t="n">
-        <v>73524000</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>50600</v>
+        <v>5620</v>
       </c>
       <c r="F7" t="n">
-        <v>184</v>
+        <v>4692</v>
       </c>
       <c r="G7" t="n">
-        <v>9310400</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>26369040</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-8.210000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>11720</v>
+        <v>126900</v>
       </c>
       <c r="F8" t="n">
-        <v>658</v>
+        <v>241</v>
       </c>
       <c r="G8" t="n">
-        <v>7711760</v>
+        <v>30582900</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -706,27 +710,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>414000</v>
+        <v>1671000</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>10764000</v>
+        <v>73524000</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -738,27 +742,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>257000</v>
+        <v>50600</v>
       </c>
       <c r="F10" t="n">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="G10" t="n">
-        <v>61423000</v>
+        <v>9310400</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -770,12 +774,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -784,13 +788,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>33900</v>
+        <v>11720</v>
       </c>
       <c r="F11" t="n">
-        <v>289</v>
+        <v>658</v>
       </c>
       <c r="G11" t="n">
-        <v>9797100</v>
+        <v>7711760</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -802,12 +806,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -816,13 +820,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>515000</v>
+        <v>414000</v>
       </c>
       <c r="F12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>8755000</v>
+        <v>10764000</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -834,27 +838,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>141200</v>
+        <v>257000</v>
       </c>
       <c r="F13" t="n">
-        <v>80</v>
+        <v>239</v>
       </c>
       <c r="G13" t="n">
-        <v>11296000</v>
+        <v>61423000</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -866,12 +870,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,13 +884,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6320</v>
+        <v>33900</v>
       </c>
       <c r="F14" t="n">
-        <v>1381</v>
+        <v>289</v>
       </c>
       <c r="G14" t="n">
-        <v>8727920</v>
+        <v>9797100</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -898,27 +902,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>90300</v>
+        <v>515000</v>
       </c>
       <c r="F15" t="n">
-        <v>328</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>29618400</v>
+        <v>8755000</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -930,31 +934,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>163100</v>
+        <v>141200</v>
       </c>
       <c r="F16" t="n">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="G16" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>11296000</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -964,12 +966,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -978,13 +980,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>37900</v>
+        <v>6320</v>
       </c>
       <c r="F17" t="n">
-        <v>161</v>
+        <v>1381</v>
       </c>
       <c r="G17" t="n">
-        <v>6101900</v>
+        <v>8727920</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -996,27 +998,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>19990</v>
+        <v>90300</v>
       </c>
       <c r="F18" t="n">
-        <v>608</v>
+        <v>328</v>
       </c>
       <c r="G18" t="n">
-        <v>12153920</v>
+        <v>29618400</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1028,29 +1030,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>35100</v>
+        <v>163100</v>
       </c>
       <c r="F19" t="n">
-        <v>317</v>
+        <v>119</v>
       </c>
       <c r="G19" t="n">
-        <v>11126700</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1060,12 +1064,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1074,13 +1078,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>286000</v>
+        <v>37900</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="G20" t="n">
-        <v>5720000</v>
+        <v>6101900</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1092,31 +1096,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>416000</v>
+        <v>19990</v>
       </c>
       <c r="F21" t="n">
-        <v>51</v>
+        <v>608</v>
       </c>
       <c r="G21" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H21" t="n">
-        <v>5.85</v>
-      </c>
+        <v>12153920</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1126,12 +1128,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1140,13 +1142,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>49450</v>
+        <v>35100</v>
       </c>
       <c r="F22" t="n">
-        <v>151</v>
+        <v>317</v>
       </c>
       <c r="G22" t="n">
-        <v>7466950</v>
+        <v>11126700</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1158,12 +1160,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1172,13 +1174,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>138000</v>
+        <v>286000</v>
       </c>
       <c r="F23" t="n">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="G23" t="n">
-        <v>9246000</v>
+        <v>5720000</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1190,29 +1192,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>31950</v>
+        <v>416000</v>
       </c>
       <c r="F24" t="n">
-        <v>335</v>
+        <v>51</v>
       </c>
       <c r="G24" t="n">
-        <v>10703250</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1222,12 +1226,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1236,111 +1240,109 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>124800</v>
+        <v>49450</v>
       </c>
       <c r="F25" t="n">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="G25" t="n">
-        <v>9609600</v>
+        <v>7466950</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10800</v>
+        <v>138000</v>
       </c>
       <c r="F26" t="n">
-        <v>1872</v>
+        <v>67</v>
       </c>
       <c r="G26" t="n">
-        <v>20217600</v>
+        <v>9246000</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>11880</v>
+        <v>31950</v>
       </c>
       <c r="F27" t="n">
-        <v>1474</v>
+        <v>335</v>
       </c>
       <c r="G27" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>10703250</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>20200</v>
+        <v>124800</v>
       </c>
       <c r="F28" t="n">
-        <v>1501</v>
+        <v>77</v>
       </c>
       <c r="G28" t="n">
-        <v>30320200</v>
+        <v>9609600</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1352,27 +1354,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102200</v>
+        <v>10800</v>
       </c>
       <c r="F29" t="n">
-        <v>198</v>
+        <v>1872</v>
       </c>
       <c r="G29" t="n">
-        <v>20235600</v>
+        <v>20217600</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1384,12 +1386,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1398,16 +1400,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>23450</v>
+        <v>11880</v>
       </c>
       <c r="F30" t="n">
-        <v>762</v>
+        <v>1474</v>
       </c>
       <c r="G30" t="n">
-        <v>17868900</v>
+        <v>17511120</v>
       </c>
       <c r="H30" t="n">
-        <v>-10.67</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="31">
@@ -1418,31 +1420,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>22050</v>
+        <v>20200</v>
       </c>
       <c r="F31" t="n">
-        <v>875</v>
+        <v>1501</v>
       </c>
       <c r="G31" t="n">
-        <v>19293750</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-3.5</v>
-      </c>
+        <v>30320200</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>32550</v>
+        <v>102200</v>
       </c>
       <c r="F32" t="n">
-        <v>621</v>
+        <v>198</v>
       </c>
       <c r="G32" t="n">
-        <v>20213550</v>
+        <v>20235600</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1498,64 +1498,66 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>99700</v>
+        <v>23450</v>
       </c>
       <c r="F33" t="n">
-        <v>180</v>
+        <v>762</v>
       </c>
       <c r="G33" t="n">
-        <v>17946000</v>
+        <v>17868900</v>
       </c>
       <c r="H33" t="n">
-        <v>-10.1</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1662000</v>
+        <v>22050</v>
       </c>
       <c r="F34" t="n">
-        <v>150</v>
+        <v>875</v>
       </c>
       <c r="G34" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1564,47 +1566,49 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>49700</v>
+        <v>32550</v>
       </c>
       <c r="F35" t="n">
-        <v>402</v>
+        <v>621</v>
       </c>
       <c r="G35" t="n">
-        <v>19979400</v>
+        <v>20213550</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>435000</v>
+        <v>99700</v>
       </c>
       <c r="F36" t="n">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="G36" t="n">
-        <v>20010000</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1614,12 +1618,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1628,13 +1632,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>268500</v>
+        <v>1662000</v>
       </c>
       <c r="F37" t="n">
-        <v>931</v>
+        <v>150</v>
       </c>
       <c r="G37" t="n">
-        <v>249973500</v>
+        <v>249300000</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1646,12 +1650,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1660,13 +1664,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>13570</v>
+        <v>49700</v>
       </c>
       <c r="F38" t="n">
-        <v>1474</v>
+        <v>402</v>
       </c>
       <c r="G38" t="n">
-        <v>20002180</v>
+        <v>19979400</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1678,12 +1682,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1692,13 +1696,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>343500</v>
+        <v>435000</v>
       </c>
       <c r="F39" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="G39" t="n">
-        <v>29884500</v>
+        <v>20010000</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1710,12 +1714,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1724,13 +1728,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>34150</v>
+        <v>268500</v>
       </c>
       <c r="F40" t="n">
-        <v>586</v>
+        <v>931</v>
       </c>
       <c r="G40" t="n">
-        <v>20011900</v>
+        <v>249973500</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1742,12 +1746,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1756,13 +1760,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>488000</v>
+        <v>13570</v>
       </c>
       <c r="F41" t="n">
-        <v>41</v>
+        <v>1474</v>
       </c>
       <c r="G41" t="n">
-        <v>20008000</v>
+        <v>20002180</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1774,12 +1778,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1788,13 +1792,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>153600</v>
+        <v>343500</v>
       </c>
       <c r="F42" t="n">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="G42" t="n">
-        <v>19968000</v>
+        <v>29884500</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1806,12 +1810,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1820,13 +1824,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>99800</v>
+        <v>34150</v>
       </c>
       <c r="F43" t="n">
-        <v>200</v>
+        <v>586</v>
       </c>
       <c r="G43" t="n">
-        <v>19960000</v>
+        <v>20011900</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1838,12 +1842,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1852,13 +1856,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6040</v>
+        <v>488000</v>
       </c>
       <c r="F44" t="n">
-        <v>3311</v>
+        <v>41</v>
       </c>
       <c r="G44" t="n">
-        <v>19998440</v>
+        <v>20008000</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1870,12 +1874,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1884,13 +1888,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>26250</v>
+        <v>153600</v>
       </c>
       <c r="F45" t="n">
-        <v>762</v>
+        <v>130</v>
       </c>
       <c r="G45" t="n">
-        <v>20002500</v>
+        <v>19968000</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1902,12 +1906,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1916,13 +1920,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>22850</v>
+        <v>99800</v>
       </c>
       <c r="F46" t="n">
-        <v>875</v>
+        <v>200</v>
       </c>
       <c r="G46" t="n">
-        <v>19993750</v>
+        <v>19960000</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1934,12 +1938,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1948,13 +1952,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>168500</v>
+        <v>6040</v>
       </c>
       <c r="F47" t="n">
-        <v>119</v>
+        <v>3311</v>
       </c>
       <c r="G47" t="n">
-        <v>20051500</v>
+        <v>19998440</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1966,12 +1970,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1980,13 +1984,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>22850</v>
+        <v>26250</v>
       </c>
       <c r="F48" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G48" t="n">
-        <v>19993750</v>
+        <v>20002500</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1998,12 +2002,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2012,13 +2016,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>37900</v>
+        <v>22850</v>
       </c>
       <c r="F49" t="n">
-        <v>528</v>
+        <v>875</v>
       </c>
       <c r="G49" t="n">
-        <v>20011200</v>
+        <v>19993750</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2030,12 +2034,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2044,13 +2048,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>239000</v>
+        <v>168500</v>
       </c>
       <c r="F50" t="n">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="G50" t="n">
-        <v>20076000</v>
+        <v>20051500</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2062,12 +2066,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2076,13 +2080,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>298000</v>
+        <v>22850</v>
       </c>
       <c r="F51" t="n">
-        <v>117</v>
+        <v>875</v>
       </c>
       <c r="G51" t="n">
-        <v>34866000</v>
+        <v>19993750</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2094,12 +2098,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2108,13 +2112,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>393000</v>
+        <v>37900</v>
       </c>
       <c r="F52" t="n">
-        <v>51</v>
+        <v>528</v>
       </c>
       <c r="G52" t="n">
-        <v>20043000</v>
+        <v>20011200</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2126,12 +2130,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2140,13 +2144,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>110900</v>
+        <v>239000</v>
       </c>
       <c r="F53" t="n">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="G53" t="n">
-        <v>19962000</v>
+        <v>20076000</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2158,12 +2162,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2172,13 +2176,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>44500</v>
+        <v>298000</v>
       </c>
       <c r="F54" t="n">
-        <v>449</v>
+        <v>117</v>
       </c>
       <c r="G54" t="n">
-        <v>19980500</v>
+        <v>34866000</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2190,12 +2194,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2204,13 +2208,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>135000</v>
+        <v>393000</v>
       </c>
       <c r="F55" t="n">
-        <v>148</v>
+        <v>51</v>
       </c>
       <c r="G55" t="n">
-        <v>19980000</v>
+        <v>20043000</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2222,12 +2226,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2236,13 +2240,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>33750</v>
+        <v>110900</v>
       </c>
       <c r="F56" t="n">
-        <v>593</v>
+        <v>180</v>
       </c>
       <c r="G56" t="n">
-        <v>20013750</v>
+        <v>19962000</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2254,29 +2258,125 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F57" t="n">
+        <v>449</v>
+      </c>
+      <c r="G57" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F58" t="n">
+        <v>148</v>
+      </c>
+      <c r="G58" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F59" t="n">
+        <v>593</v>
+      </c>
+      <c r="G59" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
         <v>124600</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F60" t="n">
         <v>161</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G60" t="n">
         <v>20060600</v>
       </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,117 +473,115 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22250</v>
+        <v>21000</v>
       </c>
       <c r="F2" t="n">
-        <v>1373</v>
+        <v>1501</v>
       </c>
       <c r="G2" t="n">
-        <v>30549250</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>31521000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>33500</v>
+        <v>21900</v>
       </c>
       <c r="F3" t="n">
-        <v>845</v>
+        <v>888</v>
       </c>
       <c r="G3" t="n">
-        <v>28307500</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-9.09</v>
-      </c>
+        <v>19447200</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>300000</v>
+        <v>135300</v>
       </c>
       <c r="F4" t="n">
-        <v>104</v>
+        <v>222</v>
       </c>
       <c r="G4" t="n">
-        <v>31200000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>20.95</v>
-      </c>
+        <v>30036600</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -592,30 +590,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>28200</v>
+        <v>22250</v>
       </c>
       <c r="F5" t="n">
-        <v>1084</v>
+        <v>1373</v>
       </c>
       <c r="G5" t="n">
-        <v>30568800</v>
+        <v>30549250</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -624,32 +622,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>398000</v>
+        <v>33500</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>845</v>
       </c>
       <c r="G6" t="n">
-        <v>28656000</v>
+        <v>28307500</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.88</v>
+        <v>-9.09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -658,16 +656,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5620</v>
+        <v>300000</v>
       </c>
       <c r="F7" t="n">
-        <v>4692</v>
+        <v>104</v>
       </c>
       <c r="G7" t="n">
-        <v>26369040</v>
+        <v>31200000</v>
       </c>
       <c r="H7" t="n">
-        <v>-8.210000000000001</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="8">
@@ -678,12 +676,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -692,109 +690,113 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>126900</v>
+        <v>28200</v>
       </c>
       <c r="F8" t="n">
-        <v>241</v>
+        <v>1084</v>
       </c>
       <c r="G8" t="n">
-        <v>30582900</v>
+        <v>30568800</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1671000</v>
+        <v>398000</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="G9" t="n">
-        <v>73524000</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>50600</v>
+        <v>5620</v>
       </c>
       <c r="F10" t="n">
-        <v>184</v>
+        <v>4692</v>
       </c>
       <c r="G10" t="n">
-        <v>9310400</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>26369040</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-8.210000000000001</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>11720</v>
+        <v>126900</v>
       </c>
       <c r="F11" t="n">
-        <v>658</v>
+        <v>241</v>
       </c>
       <c r="G11" t="n">
-        <v>7711760</v>
+        <v>30582900</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -806,27 +808,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>414000</v>
+        <v>1671000</v>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>10764000</v>
+        <v>73524000</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -838,27 +840,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>257000</v>
+        <v>50600</v>
       </c>
       <c r="F13" t="n">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="G13" t="n">
-        <v>61423000</v>
+        <v>9310400</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -870,12 +872,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -884,13 +886,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>33900</v>
+        <v>11720</v>
       </c>
       <c r="F14" t="n">
-        <v>289</v>
+        <v>658</v>
       </c>
       <c r="G14" t="n">
-        <v>9797100</v>
+        <v>7711760</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -902,12 +904,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -916,13 +918,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>515000</v>
+        <v>414000</v>
       </c>
       <c r="F15" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>8755000</v>
+        <v>10764000</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -934,27 +936,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>141200</v>
+        <v>257000</v>
       </c>
       <c r="F16" t="n">
-        <v>80</v>
+        <v>239</v>
       </c>
       <c r="G16" t="n">
-        <v>11296000</v>
+        <v>61423000</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -966,12 +968,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -980,13 +982,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6320</v>
+        <v>33900</v>
       </c>
       <c r="F17" t="n">
-        <v>1381</v>
+        <v>289</v>
       </c>
       <c r="G17" t="n">
-        <v>8727920</v>
+        <v>9797100</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -998,27 +1000,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>90300</v>
+        <v>515000</v>
       </c>
       <c r="F18" t="n">
-        <v>328</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
-        <v>29618400</v>
+        <v>8755000</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1030,31 +1032,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>163100</v>
+        <v>141200</v>
       </c>
       <c r="F19" t="n">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="G19" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>11296000</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1078,13 +1078,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>37900</v>
+        <v>6320</v>
       </c>
       <c r="F20" t="n">
-        <v>161</v>
+        <v>1381</v>
       </c>
       <c r="G20" t="n">
-        <v>6101900</v>
+        <v>8727920</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1096,27 +1096,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>19990</v>
+        <v>90300</v>
       </c>
       <c r="F21" t="n">
-        <v>608</v>
+        <v>328</v>
       </c>
       <c r="G21" t="n">
-        <v>12153920</v>
+        <v>29618400</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1128,29 +1128,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>35100</v>
+        <v>163100</v>
       </c>
       <c r="F22" t="n">
-        <v>317</v>
+        <v>119</v>
       </c>
       <c r="G22" t="n">
-        <v>11126700</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1160,12 +1162,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1174,13 +1176,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>286000</v>
+        <v>37900</v>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="G23" t="n">
-        <v>5720000</v>
+        <v>6101900</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1192,31 +1194,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>416000</v>
+        <v>19990</v>
       </c>
       <c r="F24" t="n">
-        <v>51</v>
+        <v>608</v>
       </c>
       <c r="G24" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H24" t="n">
-        <v>5.85</v>
-      </c>
+        <v>12153920</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>49450</v>
+        <v>35100</v>
       </c>
       <c r="F25" t="n">
-        <v>151</v>
+        <v>317</v>
       </c>
       <c r="G25" t="n">
-        <v>7466950</v>
+        <v>11126700</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>138000</v>
+        <v>286000</v>
       </c>
       <c r="F26" t="n">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>9246000</v>
+        <v>5720000</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1290,29 +1290,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>31950</v>
+        <v>416000</v>
       </c>
       <c r="F27" t="n">
-        <v>335</v>
+        <v>51</v>
       </c>
       <c r="G27" t="n">
-        <v>10703250</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1322,12 +1324,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1336,111 +1338,109 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>124800</v>
+        <v>49450</v>
       </c>
       <c r="F28" t="n">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="G28" t="n">
-        <v>9609600</v>
+        <v>7466950</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>10800</v>
+        <v>138000</v>
       </c>
       <c r="F29" t="n">
-        <v>1872</v>
+        <v>67</v>
       </c>
       <c r="G29" t="n">
-        <v>20217600</v>
+        <v>9246000</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>11880</v>
+        <v>31950</v>
       </c>
       <c r="F30" t="n">
-        <v>1474</v>
+        <v>335</v>
       </c>
       <c r="G30" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>10703250</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>20200</v>
+        <v>124800</v>
       </c>
       <c r="F31" t="n">
-        <v>1501</v>
+        <v>77</v>
       </c>
       <c r="G31" t="n">
-        <v>30320200</v>
+        <v>9609600</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1452,27 +1452,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102200</v>
+        <v>10800</v>
       </c>
       <c r="F32" t="n">
-        <v>198</v>
+        <v>1872</v>
       </c>
       <c r="G32" t="n">
-        <v>20235600</v>
+        <v>20217600</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1498,16 +1498,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>23450</v>
+        <v>11880</v>
       </c>
       <c r="F33" t="n">
-        <v>762</v>
+        <v>1474</v>
       </c>
       <c r="G33" t="n">
-        <v>17868900</v>
+        <v>17511120</v>
       </c>
       <c r="H33" t="n">
-        <v>-10.67</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="34">
@@ -1518,31 +1518,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>22050</v>
+        <v>20200</v>
       </c>
       <c r="F34" t="n">
-        <v>875</v>
+        <v>1501</v>
       </c>
       <c r="G34" t="n">
-        <v>19293750</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-3.5</v>
-      </c>
+        <v>30320200</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1552,27 +1550,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>32550</v>
+        <v>102200</v>
       </c>
       <c r="F35" t="n">
-        <v>621</v>
+        <v>198</v>
       </c>
       <c r="G35" t="n">
-        <v>20213550</v>
+        <v>20235600</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1584,12 +1582,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1598,64 +1596,66 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>99700</v>
+        <v>23450</v>
       </c>
       <c r="F36" t="n">
-        <v>180</v>
+        <v>762</v>
       </c>
       <c r="G36" t="n">
-        <v>17946000</v>
+        <v>17868900</v>
       </c>
       <c r="H36" t="n">
-        <v>-10.1</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1662000</v>
+        <v>22050</v>
       </c>
       <c r="F37" t="n">
-        <v>150</v>
+        <v>875</v>
       </c>
       <c r="G37" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1664,47 +1664,49 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>49700</v>
+        <v>32550</v>
       </c>
       <c r="F38" t="n">
-        <v>402</v>
+        <v>621</v>
       </c>
       <c r="G38" t="n">
-        <v>19979400</v>
+        <v>20213550</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>435000</v>
+        <v>99700</v>
       </c>
       <c r="F39" t="n">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="G39" t="n">
-        <v>20010000</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1714,12 +1716,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1728,13 +1730,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>268500</v>
+        <v>1662000</v>
       </c>
       <c r="F40" t="n">
-        <v>931</v>
+        <v>150</v>
       </c>
       <c r="G40" t="n">
-        <v>249973500</v>
+        <v>249300000</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1746,12 +1748,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1760,13 +1762,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>13570</v>
+        <v>49700</v>
       </c>
       <c r="F41" t="n">
-        <v>1474</v>
+        <v>402</v>
       </c>
       <c r="G41" t="n">
-        <v>20002180</v>
+        <v>19979400</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1778,12 +1780,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1792,13 +1794,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>343500</v>
+        <v>435000</v>
       </c>
       <c r="F42" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="G42" t="n">
-        <v>29884500</v>
+        <v>20010000</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1810,12 +1812,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1824,13 +1826,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>34150</v>
+        <v>268500</v>
       </c>
       <c r="F43" t="n">
-        <v>586</v>
+        <v>931</v>
       </c>
       <c r="G43" t="n">
-        <v>20011900</v>
+        <v>249973500</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1842,12 +1844,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1856,13 +1858,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>488000</v>
+        <v>13570</v>
       </c>
       <c r="F44" t="n">
-        <v>41</v>
+        <v>1474</v>
       </c>
       <c r="G44" t="n">
-        <v>20008000</v>
+        <v>20002180</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1874,12 +1876,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1888,13 +1890,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>153600</v>
+        <v>343500</v>
       </c>
       <c r="F45" t="n">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="G45" t="n">
-        <v>19968000</v>
+        <v>29884500</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1906,12 +1908,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1920,13 +1922,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>99800</v>
+        <v>34150</v>
       </c>
       <c r="F46" t="n">
-        <v>200</v>
+        <v>586</v>
       </c>
       <c r="G46" t="n">
-        <v>19960000</v>
+        <v>20011900</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1938,12 +1940,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1952,13 +1954,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6040</v>
+        <v>488000</v>
       </c>
       <c r="F47" t="n">
-        <v>3311</v>
+        <v>41</v>
       </c>
       <c r="G47" t="n">
-        <v>19998440</v>
+        <v>20008000</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1970,12 +1972,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1984,13 +1986,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>26250</v>
+        <v>153600</v>
       </c>
       <c r="F48" t="n">
-        <v>762</v>
+        <v>130</v>
       </c>
       <c r="G48" t="n">
-        <v>20002500</v>
+        <v>19968000</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -2002,12 +2004,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2016,13 +2018,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>22850</v>
+        <v>99800</v>
       </c>
       <c r="F49" t="n">
-        <v>875</v>
+        <v>200</v>
       </c>
       <c r="G49" t="n">
-        <v>19993750</v>
+        <v>19960000</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2034,12 +2036,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2048,13 +2050,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>168500</v>
+        <v>6040</v>
       </c>
       <c r="F50" t="n">
-        <v>119</v>
+        <v>3311</v>
       </c>
       <c r="G50" t="n">
-        <v>20051500</v>
+        <v>19998440</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2066,12 +2068,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2080,13 +2082,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>22850</v>
+        <v>26250</v>
       </c>
       <c r="F51" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G51" t="n">
-        <v>19993750</v>
+        <v>20002500</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2098,12 +2100,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2112,13 +2114,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>37900</v>
+        <v>22850</v>
       </c>
       <c r="F52" t="n">
-        <v>528</v>
+        <v>875</v>
       </c>
       <c r="G52" t="n">
-        <v>20011200</v>
+        <v>19993750</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2130,12 +2132,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2144,13 +2146,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>239000</v>
+        <v>168500</v>
       </c>
       <c r="F53" t="n">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="G53" t="n">
-        <v>20076000</v>
+        <v>20051500</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2162,12 +2164,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2176,13 +2178,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>298000</v>
+        <v>22850</v>
       </c>
       <c r="F54" t="n">
-        <v>117</v>
+        <v>875</v>
       </c>
       <c r="G54" t="n">
-        <v>34866000</v>
+        <v>19993750</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2194,12 +2196,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2208,13 +2210,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>393000</v>
+        <v>37900</v>
       </c>
       <c r="F55" t="n">
-        <v>51</v>
+        <v>528</v>
       </c>
       <c r="G55" t="n">
-        <v>20043000</v>
+        <v>20011200</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2226,12 +2228,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2240,13 +2242,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>110900</v>
+        <v>239000</v>
       </c>
       <c r="F56" t="n">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="G56" t="n">
-        <v>19962000</v>
+        <v>20076000</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2258,12 +2260,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2272,13 +2274,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>44500</v>
+        <v>298000</v>
       </c>
       <c r="F57" t="n">
-        <v>449</v>
+        <v>117</v>
       </c>
       <c r="G57" t="n">
-        <v>19980500</v>
+        <v>34866000</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2290,12 +2292,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2304,13 +2306,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>135000</v>
+        <v>393000</v>
       </c>
       <c r="F58" t="n">
-        <v>148</v>
+        <v>51</v>
       </c>
       <c r="G58" t="n">
-        <v>19980000</v>
+        <v>20043000</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2322,12 +2324,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2336,13 +2338,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>33750</v>
+        <v>110900</v>
       </c>
       <c r="F59" t="n">
-        <v>593</v>
+        <v>180</v>
       </c>
       <c r="G59" t="n">
-        <v>20013750</v>
+        <v>19962000</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2354,29 +2356,125 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F60" t="n">
+        <v>449</v>
+      </c>
+      <c r="G60" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F61" t="n">
+        <v>148</v>
+      </c>
+      <c r="G61" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F62" t="n">
+        <v>593</v>
+      </c>
+      <c r="G62" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
         <v>124600</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F63" t="n">
         <v>161</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G63" t="n">
         <v>20060600</v>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,96 +492,100 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>21000</v>
+        <v>32250</v>
       </c>
       <c r="F2" t="n">
-        <v>1501</v>
+        <v>875</v>
       </c>
       <c r="G2" t="n">
-        <v>31521000</v>
+        <v>28218750</v>
       </c>
       <c r="H2" t="n">
-        <v>3.96</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>21900</v>
+        <v>105800</v>
       </c>
       <c r="F3" t="n">
-        <v>888</v>
+        <v>328</v>
       </c>
       <c r="G3" t="n">
-        <v>19447200</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>34702400</v>
+      </c>
+      <c r="H3" t="n">
+        <v>17.17</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>135300</v>
+        <v>33750</v>
       </c>
       <c r="F4" t="n">
-        <v>222</v>
+        <v>782</v>
       </c>
       <c r="G4" t="n">
-        <v>30036600</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>26392500</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -590,30 +594,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22250</v>
+        <v>86300</v>
       </c>
       <c r="F5" t="n">
-        <v>1373</v>
+        <v>348</v>
       </c>
       <c r="G5" t="n">
-        <v>30549250</v>
+        <v>30032400</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -622,66 +626,64 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>33500</v>
+        <v>21000</v>
       </c>
       <c r="F6" t="n">
-        <v>845</v>
+        <v>1501</v>
       </c>
       <c r="G6" t="n">
-        <v>28307500</v>
+        <v>31521000</v>
       </c>
       <c r="H6" t="n">
-        <v>-9.09</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>300000</v>
+        <v>21900</v>
       </c>
       <c r="F7" t="n">
-        <v>104</v>
+        <v>888</v>
       </c>
       <c r="G7" t="n">
-        <v>31200000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>20.95</v>
-      </c>
+        <v>19447200</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -690,64 +692,62 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>28200</v>
+        <v>135300</v>
       </c>
       <c r="F8" t="n">
-        <v>1084</v>
+        <v>222</v>
       </c>
       <c r="G8" t="n">
-        <v>30568800</v>
+        <v>30036600</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>398000</v>
+        <v>22250</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>1373</v>
       </c>
       <c r="G9" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>30549250</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -756,175 +756,181 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5620</v>
+        <v>33500</v>
       </c>
       <c r="F10" t="n">
-        <v>4692</v>
+        <v>845</v>
       </c>
       <c r="G10" t="n">
-        <v>26369040</v>
+        <v>28307500</v>
       </c>
       <c r="H10" t="n">
-        <v>-8.210000000000001</v>
+        <v>-9.09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>126900</v>
+        <v>300000</v>
       </c>
       <c r="F11" t="n">
-        <v>241</v>
+        <v>104</v>
       </c>
       <c r="G11" t="n">
-        <v>30582900</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1671000</v>
+        <v>28200</v>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>1084</v>
       </c>
       <c r="G12" t="n">
-        <v>73524000</v>
+        <v>30568800</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>50600</v>
+        <v>398000</v>
       </c>
       <c r="F13" t="n">
-        <v>184</v>
+        <v>72</v>
       </c>
       <c r="G13" t="n">
-        <v>9310400</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>11720</v>
+        <v>5620</v>
       </c>
       <c r="F14" t="n">
-        <v>658</v>
+        <v>4692</v>
       </c>
       <c r="G14" t="n">
-        <v>7711760</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>26369040</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-8.210000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>414000</v>
+        <v>126900</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>241</v>
       </c>
       <c r="G15" t="n">
-        <v>10764000</v>
+        <v>30582900</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -936,12 +942,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -950,13 +956,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>257000</v>
+        <v>1671000</v>
       </c>
       <c r="F16" t="n">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="G16" t="n">
-        <v>61423000</v>
+        <v>73524000</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -968,12 +974,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -982,13 +988,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>33900</v>
+        <v>50600</v>
       </c>
       <c r="F17" t="n">
-        <v>289</v>
+        <v>184</v>
       </c>
       <c r="G17" t="n">
-        <v>9797100</v>
+        <v>9310400</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -1000,12 +1006,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1014,13 +1020,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>515000</v>
+        <v>11720</v>
       </c>
       <c r="F18" t="n">
-        <v>17</v>
+        <v>658</v>
       </c>
       <c r="G18" t="n">
-        <v>8755000</v>
+        <v>7711760</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1032,12 +1038,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1046,13 +1052,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>141200</v>
+        <v>414000</v>
       </c>
       <c r="F19" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>11296000</v>
+        <v>10764000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1064,27 +1070,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6320</v>
+        <v>257000</v>
       </c>
       <c r="F20" t="n">
-        <v>1381</v>
+        <v>239</v>
       </c>
       <c r="G20" t="n">
-        <v>8727920</v>
+        <v>61423000</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1096,27 +1102,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>90300</v>
+        <v>33900</v>
       </c>
       <c r="F21" t="n">
-        <v>328</v>
+        <v>289</v>
       </c>
       <c r="G21" t="n">
-        <v>29618400</v>
+        <v>9797100</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1128,31 +1134,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>163100</v>
+        <v>515000</v>
       </c>
       <c r="F22" t="n">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="G22" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>8755000</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1162,12 +1166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1176,13 +1180,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>37900</v>
+        <v>141200</v>
       </c>
       <c r="F23" t="n">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="G23" t="n">
-        <v>6101900</v>
+        <v>11296000</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1194,12 +1198,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1208,13 +1212,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>19990</v>
+        <v>6320</v>
       </c>
       <c r="F24" t="n">
-        <v>608</v>
+        <v>1381</v>
       </c>
       <c r="G24" t="n">
-        <v>12153920</v>
+        <v>8727920</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1226,27 +1230,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>35100</v>
+        <v>90300</v>
       </c>
       <c r="F25" t="n">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="G25" t="n">
-        <v>11126700</v>
+        <v>29618400</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1258,29 +1262,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>286000</v>
+        <v>163100</v>
       </c>
       <c r="F26" t="n">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G26" t="n">
-        <v>5720000</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1290,31 +1296,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>416000</v>
+        <v>37900</v>
       </c>
       <c r="F27" t="n">
-        <v>51</v>
+        <v>161</v>
       </c>
       <c r="G27" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H27" t="n">
-        <v>5.85</v>
-      </c>
+        <v>6101900</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1324,12 +1328,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1338,13 +1342,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>49450</v>
+        <v>19990</v>
       </c>
       <c r="F28" t="n">
-        <v>151</v>
+        <v>608</v>
       </c>
       <c r="G28" t="n">
-        <v>7466950</v>
+        <v>12153920</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1356,12 +1360,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1370,13 +1374,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>138000</v>
+        <v>35100</v>
       </c>
       <c r="F29" t="n">
-        <v>67</v>
+        <v>317</v>
       </c>
       <c r="G29" t="n">
-        <v>9246000</v>
+        <v>11126700</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1388,12 +1392,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1402,13 +1406,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>31950</v>
+        <v>286000</v>
       </c>
       <c r="F30" t="n">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="G30" t="n">
-        <v>10703250</v>
+        <v>5720000</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1420,142 +1424,142 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>124800</v>
+        <v>416000</v>
       </c>
       <c r="F31" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="G31" t="n">
-        <v>9609600</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10800</v>
+        <v>49450</v>
       </c>
       <c r="F32" t="n">
-        <v>1872</v>
+        <v>151</v>
       </c>
       <c r="G32" t="n">
-        <v>20217600</v>
+        <v>7466950</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>11880</v>
+        <v>138000</v>
       </c>
       <c r="F33" t="n">
-        <v>1474</v>
+        <v>67</v>
       </c>
       <c r="G33" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>9246000</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>20200</v>
+        <v>31950</v>
       </c>
       <c r="F34" t="n">
-        <v>1501</v>
+        <v>335</v>
       </c>
       <c r="G34" t="n">
-        <v>30320200</v>
+        <v>10703250</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1564,13 +1568,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102200</v>
+        <v>124800</v>
       </c>
       <c r="F35" t="n">
-        <v>198</v>
+        <v>77</v>
       </c>
       <c r="G35" t="n">
-        <v>20235600</v>
+        <v>9609600</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1582,31 +1586,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>23450</v>
+        <v>10800</v>
       </c>
       <c r="F36" t="n">
-        <v>762</v>
+        <v>1872</v>
       </c>
       <c r="G36" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20217600</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1616,12 +1618,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1630,16 +1632,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>22050</v>
+        <v>11880</v>
       </c>
       <c r="F37" t="n">
-        <v>875</v>
+        <v>1474</v>
       </c>
       <c r="G37" t="n">
-        <v>19293750</v>
+        <v>17511120</v>
       </c>
       <c r="H37" t="n">
-        <v>-3.5</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="38">
@@ -1650,12 +1652,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1664,13 +1666,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>32550</v>
+        <v>20200</v>
       </c>
       <c r="F38" t="n">
-        <v>621</v>
+        <v>1501</v>
       </c>
       <c r="G38" t="n">
-        <v>20213550</v>
+        <v>30320200</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1682,110 +1684,112 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>99700</v>
+        <v>102200</v>
       </c>
       <c r="F39" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="G39" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20235600</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1662000</v>
+        <v>23450</v>
       </c>
       <c r="F40" t="n">
-        <v>150</v>
+        <v>762</v>
       </c>
       <c r="G40" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>17868900</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-10.67</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>49700</v>
+        <v>22050</v>
       </c>
       <c r="F41" t="n">
-        <v>402</v>
+        <v>875</v>
       </c>
       <c r="G41" t="n">
-        <v>19979400</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1794,47 +1798,49 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>435000</v>
+        <v>32550</v>
       </c>
       <c r="F42" t="n">
-        <v>46</v>
+        <v>621</v>
       </c>
       <c r="G42" t="n">
-        <v>20010000</v>
+        <v>20213550</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>268500</v>
+        <v>99700</v>
       </c>
       <c r="F43" t="n">
-        <v>931</v>
+        <v>180</v>
       </c>
       <c r="G43" t="n">
-        <v>249973500</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1844,12 +1850,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1858,13 +1864,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>13570</v>
+        <v>1662000</v>
       </c>
       <c r="F44" t="n">
-        <v>1474</v>
+        <v>150</v>
       </c>
       <c r="G44" t="n">
-        <v>20002180</v>
+        <v>249300000</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1876,12 +1882,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1890,13 +1896,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>343500</v>
+        <v>49700</v>
       </c>
       <c r="F45" t="n">
-        <v>87</v>
+        <v>402</v>
       </c>
       <c r="G45" t="n">
-        <v>29884500</v>
+        <v>19979400</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1908,12 +1914,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1922,13 +1928,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>34150</v>
+        <v>435000</v>
       </c>
       <c r="F46" t="n">
-        <v>586</v>
+        <v>46</v>
       </c>
       <c r="G46" t="n">
-        <v>20011900</v>
+        <v>20010000</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1940,12 +1946,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1954,13 +1960,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>488000</v>
+        <v>268500</v>
       </c>
       <c r="F47" t="n">
-        <v>41</v>
+        <v>931</v>
       </c>
       <c r="G47" t="n">
-        <v>20008000</v>
+        <v>249973500</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1972,12 +1978,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1986,13 +1992,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>153600</v>
+        <v>13570</v>
       </c>
       <c r="F48" t="n">
-        <v>130</v>
+        <v>1474</v>
       </c>
       <c r="G48" t="n">
-        <v>19968000</v>
+        <v>20002180</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -2004,12 +2010,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2018,13 +2024,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>99800</v>
+        <v>343500</v>
       </c>
       <c r="F49" t="n">
-        <v>200</v>
+        <v>87</v>
       </c>
       <c r="G49" t="n">
-        <v>19960000</v>
+        <v>29884500</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2036,12 +2042,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2050,13 +2056,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6040</v>
+        <v>34150</v>
       </c>
       <c r="F50" t="n">
-        <v>3311</v>
+        <v>586</v>
       </c>
       <c r="G50" t="n">
-        <v>19998440</v>
+        <v>20011900</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2068,12 +2074,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2082,13 +2088,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>26250</v>
+        <v>488000</v>
       </c>
       <c r="F51" t="n">
-        <v>762</v>
+        <v>41</v>
       </c>
       <c r="G51" t="n">
-        <v>20002500</v>
+        <v>20008000</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2100,12 +2106,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2114,13 +2120,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>22850</v>
+        <v>153600</v>
       </c>
       <c r="F52" t="n">
-        <v>875</v>
+        <v>130</v>
       </c>
       <c r="G52" t="n">
-        <v>19993750</v>
+        <v>19968000</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2132,12 +2138,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2146,13 +2152,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>168500</v>
+        <v>99800</v>
       </c>
       <c r="F53" t="n">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="G53" t="n">
-        <v>20051500</v>
+        <v>19960000</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2164,12 +2170,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2178,13 +2184,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>22850</v>
+        <v>6040</v>
       </c>
       <c r="F54" t="n">
-        <v>875</v>
+        <v>3311</v>
       </c>
       <c r="G54" t="n">
-        <v>19993750</v>
+        <v>19998440</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2196,12 +2202,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2210,13 +2216,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>37900</v>
+        <v>26250</v>
       </c>
       <c r="F55" t="n">
-        <v>528</v>
+        <v>762</v>
       </c>
       <c r="G55" t="n">
-        <v>20011200</v>
+        <v>20002500</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2228,12 +2234,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2242,13 +2248,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>239000</v>
+        <v>22850</v>
       </c>
       <c r="F56" t="n">
-        <v>84</v>
+        <v>875</v>
       </c>
       <c r="G56" t="n">
-        <v>20076000</v>
+        <v>19993750</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2260,12 +2266,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2274,13 +2280,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>298000</v>
+        <v>168500</v>
       </c>
       <c r="F57" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G57" t="n">
-        <v>34866000</v>
+        <v>20051500</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2292,12 +2298,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2306,13 +2312,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>393000</v>
+        <v>22850</v>
       </c>
       <c r="F58" t="n">
-        <v>51</v>
+        <v>875</v>
       </c>
       <c r="G58" t="n">
-        <v>20043000</v>
+        <v>19993750</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2324,12 +2330,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2338,13 +2344,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>110900</v>
+        <v>37900</v>
       </c>
       <c r="F59" t="n">
-        <v>180</v>
+        <v>528</v>
       </c>
       <c r="G59" t="n">
-        <v>19962000</v>
+        <v>20011200</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2356,12 +2362,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2370,13 +2376,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>44500</v>
+        <v>239000</v>
       </c>
       <c r="F60" t="n">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="G60" t="n">
-        <v>19980500</v>
+        <v>20076000</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2388,12 +2394,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2402,13 +2408,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>135000</v>
+        <v>298000</v>
       </c>
       <c r="F61" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="G61" t="n">
-        <v>19980000</v>
+        <v>34866000</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2420,12 +2426,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2434,13 +2440,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>33750</v>
+        <v>393000</v>
       </c>
       <c r="F62" t="n">
-        <v>593</v>
+        <v>51</v>
       </c>
       <c r="G62" t="n">
-        <v>20013750</v>
+        <v>20043000</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2452,29 +2458,157 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F63" t="n">
+        <v>180</v>
+      </c>
+      <c r="G63" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F64" t="n">
+        <v>449</v>
+      </c>
+      <c r="G64" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F65" t="n">
+        <v>148</v>
+      </c>
+      <c r="G65" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F66" t="n">
+        <v>593</v>
+      </c>
+      <c r="G66" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
         <v>124600</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F67" t="n">
         <v>161</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G67" t="n">
         <v>20060600</v>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -495,10 +495,10 @@
         <v>32250</v>
       </c>
       <c r="F2" t="n">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="G2" t="n">
-        <v>28218750</v>
+        <v>28315500</v>
       </c>
       <c r="H2" t="n">
         <v>-5.33</v>
@@ -529,10 +529,10 @@
         <v>105800</v>
       </c>
       <c r="F3" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G3" t="n">
-        <v>34702400</v>
+        <v>35125600</v>
       </c>
       <c r="H3" t="n">
         <v>17.17</v>
@@ -563,10 +563,10 @@
         <v>33750</v>
       </c>
       <c r="F4" t="n">
-        <v>782</v>
+        <v>791</v>
       </c>
       <c r="G4" t="n">
-        <v>26392500</v>
+        <v>26696250</v>
       </c>
       <c r="H4" t="n">
         <v>0.29</v>
@@ -597,10 +597,10 @@
         <v>86300</v>
       </c>
       <c r="F5" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="G5" t="n">
-        <v>30032400</v>
+        <v>30377600</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -629,10 +629,10 @@
         <v>21000</v>
       </c>
       <c r="F6" t="n">
-        <v>1501</v>
+        <v>1517</v>
       </c>
       <c r="G6" t="n">
-        <v>31521000</v>
+        <v>31857000</v>
       </c>
       <c r="H6" t="n">
         <v>3.96</v>
@@ -663,10 +663,10 @@
         <v>21900</v>
       </c>
       <c r="F7" t="n">
-        <v>888</v>
+        <v>906</v>
       </c>
       <c r="G7" t="n">
-        <v>19447200</v>
+        <v>19841400</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -695,10 +695,10 @@
         <v>135300</v>
       </c>
       <c r="F8" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G8" t="n">
-        <v>30036600</v>
+        <v>30577800</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -727,10 +727,10 @@
         <v>22250</v>
       </c>
       <c r="F9" t="n">
-        <v>1373</v>
+        <v>1399</v>
       </c>
       <c r="G9" t="n">
-        <v>30549250</v>
+        <v>31127750</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -759,13 +759,13 @@
         <v>33500</v>
       </c>
       <c r="F10" t="n">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="G10" t="n">
-        <v>28307500</v>
+        <v>28408000</v>
       </c>
       <c r="H10" t="n">
-        <v>-9.09</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="11">
@@ -827,10 +827,10 @@
         <v>28200</v>
       </c>
       <c r="F12" t="n">
-        <v>1084</v>
+        <v>1105</v>
       </c>
       <c r="G12" t="n">
-        <v>30568800</v>
+        <v>31161000</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -893,13 +893,13 @@
         <v>5620</v>
       </c>
       <c r="F14" t="n">
-        <v>4692</v>
+        <v>4707</v>
       </c>
       <c r="G14" t="n">
-        <v>26369040</v>
+        <v>26453340</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.210000000000001</v>
+        <v>-8.220000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -927,10 +927,10 @@
         <v>126900</v>
       </c>
       <c r="F15" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="G15" t="n">
-        <v>30582900</v>
+        <v>31217400</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -991,10 +991,10 @@
         <v>50600</v>
       </c>
       <c r="F17" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G17" t="n">
-        <v>9310400</v>
+        <v>9411600</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -1023,10 +1023,10 @@
         <v>11720</v>
       </c>
       <c r="F18" t="n">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="G18" t="n">
-        <v>7711760</v>
+        <v>7793800</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1119,10 +1119,10 @@
         <v>33900</v>
       </c>
       <c r="F21" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G21" t="n">
-        <v>9797100</v>
+        <v>9898800</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1183,10 +1183,10 @@
         <v>141200</v>
       </c>
       <c r="F23" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G23" t="n">
-        <v>11296000</v>
+        <v>11437200</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1215,10 +1215,10 @@
         <v>6320</v>
       </c>
       <c r="F24" t="n">
-        <v>1381</v>
+        <v>1396</v>
       </c>
       <c r="G24" t="n">
-        <v>8727920</v>
+        <v>8822720</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1247,10 +1247,10 @@
         <v>90300</v>
       </c>
       <c r="F25" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G25" t="n">
-        <v>29618400</v>
+        <v>29979600</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1313,10 +1313,10 @@
         <v>37900</v>
       </c>
       <c r="F27" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G27" t="n">
-        <v>6101900</v>
+        <v>6177700</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1345,10 +1345,10 @@
         <v>19990</v>
       </c>
       <c r="F28" t="n">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="G28" t="n">
-        <v>12153920</v>
+        <v>12293850</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1377,10 +1377,10 @@
         <v>35100</v>
       </c>
       <c r="F29" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G29" t="n">
-        <v>11126700</v>
+        <v>11232000</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1475,10 +1475,10 @@
         <v>49450</v>
       </c>
       <c r="F32" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G32" t="n">
-        <v>7466950</v>
+        <v>7565850</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1507,10 +1507,10 @@
         <v>138000</v>
       </c>
       <c r="F33" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G33" t="n">
-        <v>9246000</v>
+        <v>9384000</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1539,10 +1539,10 @@
         <v>31950</v>
       </c>
       <c r="F34" t="n">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="G34" t="n">
-        <v>10703250</v>
+        <v>10831050</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1571,10 +1571,10 @@
         <v>124800</v>
       </c>
       <c r="F35" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G35" t="n">
-        <v>9609600</v>
+        <v>9734400</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1603,10 +1603,10 @@
         <v>10800</v>
       </c>
       <c r="F36" t="n">
-        <v>1872</v>
+        <v>1892</v>
       </c>
       <c r="G36" t="n">
-        <v>20217600</v>
+        <v>20433600</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1669,10 +1669,10 @@
         <v>20200</v>
       </c>
       <c r="F38" t="n">
-        <v>1501</v>
+        <v>1517</v>
       </c>
       <c r="G38" t="n">
-        <v>30320200</v>
+        <v>30643400</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1701,10 +1701,10 @@
         <v>102200</v>
       </c>
       <c r="F39" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G39" t="n">
-        <v>20235600</v>
+        <v>20440000</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1801,10 +1801,10 @@
         <v>32550</v>
       </c>
       <c r="F42" t="n">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="G42" t="n">
-        <v>20213550</v>
+        <v>20441400</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,36 +473,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>32250</v>
+        <v>21800</v>
       </c>
       <c r="F2" t="n">
-        <v>878</v>
+        <v>832</v>
       </c>
       <c r="G2" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>18137600</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,12 +510,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -526,16 +524,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105800</v>
+        <v>32250</v>
       </c>
       <c r="F3" t="n">
-        <v>332</v>
+        <v>878</v>
       </c>
       <c r="G3" t="n">
-        <v>35125600</v>
+        <v>28315500</v>
       </c>
       <c r="H3" t="n">
-        <v>17.17</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="4">
@@ -546,12 +544,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -560,16 +558,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>33750</v>
+        <v>105800</v>
       </c>
       <c r="F4" t="n">
-        <v>791</v>
+        <v>332</v>
       </c>
       <c r="G4" t="n">
-        <v>26696250</v>
+        <v>35125600</v>
       </c>
       <c r="H4" t="n">
-        <v>0.29</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="5">
@@ -580,63 +578,63 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>86300</v>
+        <v>33750</v>
       </c>
       <c r="F5" t="n">
-        <v>352</v>
+        <v>791</v>
       </c>
       <c r="G5" t="n">
-        <v>30377600</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21000</v>
+        <v>86300</v>
       </c>
       <c r="F6" t="n">
-        <v>1517</v>
+        <v>352</v>
       </c>
       <c r="G6" t="n">
-        <v>31857000</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.96</v>
-      </c>
+        <v>30377600</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -646,29 +644,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>21900</v>
+        <v>21000</v>
       </c>
       <c r="F7" t="n">
-        <v>906</v>
+        <v>1517</v>
       </c>
       <c r="G7" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>31857000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -678,44 +678,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>135300</v>
+        <v>21900</v>
       </c>
       <c r="F8" t="n">
-        <v>226</v>
+        <v>906</v>
       </c>
       <c r="G8" t="n">
-        <v>30577800</v>
+        <v>19841400</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>22250</v>
+        <v>135300</v>
       </c>
       <c r="F9" t="n">
-        <v>1399</v>
+        <v>226</v>
       </c>
       <c r="G9" t="n">
-        <v>31127750</v>
+        <v>30577800</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -742,31 +742,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>33500</v>
+        <v>22250</v>
       </c>
       <c r="F10" t="n">
-        <v>848</v>
+        <v>1399</v>
       </c>
       <c r="G10" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -776,12 +774,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -790,49 +788,51 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>300000</v>
+        <v>33500</v>
       </c>
       <c r="F11" t="n">
-        <v>104</v>
+        <v>848</v>
       </c>
       <c r="G11" t="n">
-        <v>31200000</v>
+        <v>28408000</v>
       </c>
       <c r="H11" t="n">
-        <v>20.95</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>28200</v>
+        <v>300000</v>
       </c>
       <c r="F12" t="n">
-        <v>1105</v>
+        <v>104</v>
       </c>
       <c r="G12" t="n">
-        <v>31161000</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -842,31 +842,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>398000</v>
+        <v>28200</v>
       </c>
       <c r="F13" t="n">
-        <v>72</v>
+        <v>1105</v>
       </c>
       <c r="G13" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31161000</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -876,12 +874,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -890,16 +888,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5620</v>
+        <v>398000</v>
       </c>
       <c r="F14" t="n">
-        <v>4707</v>
+        <v>72</v>
       </c>
       <c r="G14" t="n">
-        <v>26453340</v>
+        <v>28656000</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.220000000000001</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="15">
@@ -910,59 +908,61 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>126900</v>
+        <v>5620</v>
       </c>
       <c r="F15" t="n">
-        <v>246</v>
+        <v>4707</v>
       </c>
       <c r="G15" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1671000</v>
+        <v>126900</v>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>246</v>
       </c>
       <c r="G16" t="n">
-        <v>73524000</v>
+        <v>31217400</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -974,27 +974,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>50600</v>
+        <v>1671000</v>
       </c>
       <c r="F17" t="n">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G17" t="n">
-        <v>9411600</v>
+        <v>73524000</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11720</v>
+        <v>50600</v>
       </c>
       <c r="F18" t="n">
-        <v>665</v>
+        <v>186</v>
       </c>
       <c r="G18" t="n">
-        <v>7793800</v>
+        <v>9411600</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>414000</v>
+        <v>11720</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>665</v>
       </c>
       <c r="G19" t="n">
-        <v>10764000</v>
+        <v>7793800</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1070,27 +1070,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>257000</v>
+        <v>414000</v>
       </c>
       <c r="F20" t="n">
-        <v>239</v>
+        <v>26</v>
       </c>
       <c r="G20" t="n">
-        <v>61423000</v>
+        <v>10764000</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1102,27 +1102,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33900</v>
+        <v>257000</v>
       </c>
       <c r="F21" t="n">
-        <v>292</v>
+        <v>239</v>
       </c>
       <c r="G21" t="n">
-        <v>9898800</v>
+        <v>61423000</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>515000</v>
+        <v>33900</v>
       </c>
       <c r="F22" t="n">
-        <v>17</v>
+        <v>292</v>
       </c>
       <c r="G22" t="n">
-        <v>8755000</v>
+        <v>9898800</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>141200</v>
+        <v>515000</v>
       </c>
       <c r="F23" t="n">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="G23" t="n">
-        <v>11437200</v>
+        <v>8755000</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6320</v>
+        <v>141200</v>
       </c>
       <c r="F24" t="n">
-        <v>1396</v>
+        <v>81</v>
       </c>
       <c r="G24" t="n">
-        <v>8822720</v>
+        <v>11437200</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1230,27 +1230,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>90300</v>
+        <v>6320</v>
       </c>
       <c r="F25" t="n">
-        <v>332</v>
+        <v>1396</v>
       </c>
       <c r="G25" t="n">
-        <v>29979600</v>
+        <v>8822720</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1262,31 +1262,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>163100</v>
+        <v>90300</v>
       </c>
       <c r="F26" t="n">
-        <v>119</v>
+        <v>332</v>
       </c>
       <c r="G26" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>29979600</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1296,29 +1294,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>37900</v>
+        <v>163100</v>
       </c>
       <c r="F27" t="n">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="G27" t="n">
-        <v>6177700</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1342,13 +1342,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>19990</v>
+        <v>37900</v>
       </c>
       <c r="F28" t="n">
-        <v>615</v>
+        <v>163</v>
       </c>
       <c r="G28" t="n">
-        <v>12293850</v>
+        <v>6177700</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1374,13 +1374,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>35100</v>
+        <v>19990</v>
       </c>
       <c r="F29" t="n">
-        <v>320</v>
+        <v>615</v>
       </c>
       <c r="G29" t="n">
-        <v>11232000</v>
+        <v>12293850</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1406,13 +1406,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>286000</v>
+        <v>35100</v>
       </c>
       <c r="F30" t="n">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="G30" t="n">
-        <v>5720000</v>
+        <v>11232000</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1424,31 +1424,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>416000</v>
+        <v>286000</v>
       </c>
       <c r="F31" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G31" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H31" t="n">
-        <v>5.85</v>
-      </c>
+        <v>5720000</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1458,29 +1456,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>49450</v>
+        <v>416000</v>
       </c>
       <c r="F32" t="n">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="G32" t="n">
-        <v>7565850</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>138000</v>
+        <v>49450</v>
       </c>
       <c r="F33" t="n">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="G33" t="n">
-        <v>9384000</v>
+        <v>7565850</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>31950</v>
+        <v>138000</v>
       </c>
       <c r="F34" t="n">
-        <v>339</v>
+        <v>68</v>
       </c>
       <c r="G34" t="n">
-        <v>10831050</v>
+        <v>9384000</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1568,45 +1568,45 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>124800</v>
+        <v>31950</v>
       </c>
       <c r="F35" t="n">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="G35" t="n">
-        <v>9734400</v>
+        <v>10831050</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>10800</v>
+        <v>124800</v>
       </c>
       <c r="F36" t="n">
-        <v>1892</v>
+        <v>78</v>
       </c>
       <c r="G36" t="n">
-        <v>20433600</v>
+        <v>9734400</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1618,31 +1618,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>11880</v>
+        <v>10800</v>
       </c>
       <c r="F37" t="n">
-        <v>1474</v>
+        <v>1892</v>
       </c>
       <c r="G37" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1652,29 +1650,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>20200</v>
+        <v>11880</v>
       </c>
       <c r="F38" t="n">
-        <v>1517</v>
+        <v>1474</v>
       </c>
       <c r="G38" t="n">
-        <v>30643400</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1684,27 +1684,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102200</v>
+        <v>20200</v>
       </c>
       <c r="F39" t="n">
-        <v>200</v>
+        <v>1517</v>
       </c>
       <c r="G39" t="n">
-        <v>20440000</v>
+        <v>30643400</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1716,31 +1716,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>23450</v>
+        <v>102200</v>
       </c>
       <c r="F40" t="n">
-        <v>762</v>
+        <v>200</v>
       </c>
       <c r="G40" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1750,12 +1748,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1764,16 +1762,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>22050</v>
+        <v>23450</v>
       </c>
       <c r="F41" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G41" t="n">
-        <v>19293750</v>
+        <v>17868900</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.5</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="42">
@@ -1784,29 +1782,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>32550</v>
+        <v>22050</v>
       </c>
       <c r="F42" t="n">
-        <v>628</v>
+        <v>875</v>
       </c>
       <c r="G42" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1816,63 +1816,63 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>99700</v>
+        <v>32550</v>
       </c>
       <c r="F43" t="n">
-        <v>180</v>
+        <v>628</v>
       </c>
       <c r="G43" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20441400</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1662000</v>
+        <v>99700</v>
       </c>
       <c r="F44" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G44" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1896,13 +1896,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>49700</v>
+        <v>1662000</v>
       </c>
       <c r="F45" t="n">
-        <v>402</v>
+        <v>150</v>
       </c>
       <c r="G45" t="n">
-        <v>19979400</v>
+        <v>249300000</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>435000</v>
+        <v>49700</v>
       </c>
       <c r="F46" t="n">
-        <v>46</v>
+        <v>402</v>
       </c>
       <c r="G46" t="n">
-        <v>20010000</v>
+        <v>19979400</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1960,13 +1960,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>268500</v>
+        <v>435000</v>
       </c>
       <c r="F47" t="n">
-        <v>931</v>
+        <v>46</v>
       </c>
       <c r="G47" t="n">
-        <v>249973500</v>
+        <v>20010000</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>13570</v>
+        <v>268500</v>
       </c>
       <c r="F48" t="n">
-        <v>1474</v>
+        <v>931</v>
       </c>
       <c r="G48" t="n">
-        <v>20002180</v>
+        <v>249973500</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2024,13 +2024,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>343500</v>
+        <v>13570</v>
       </c>
       <c r="F49" t="n">
-        <v>87</v>
+        <v>1474</v>
       </c>
       <c r="G49" t="n">
-        <v>29884500</v>
+        <v>20002180</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>34150</v>
+        <v>343500</v>
       </c>
       <c r="F50" t="n">
-        <v>586</v>
+        <v>87</v>
       </c>
       <c r="G50" t="n">
-        <v>20011900</v>
+        <v>29884500</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2074,12 +2074,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>488000</v>
+        <v>34150</v>
       </c>
       <c r="F51" t="n">
-        <v>41</v>
+        <v>586</v>
       </c>
       <c r="G51" t="n">
-        <v>20008000</v>
+        <v>20011900</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>153600</v>
+        <v>488000</v>
       </c>
       <c r="F52" t="n">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="G52" t="n">
-        <v>19968000</v>
+        <v>20008000</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>99800</v>
+        <v>153600</v>
       </c>
       <c r="F53" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="G53" t="n">
-        <v>19960000</v>
+        <v>19968000</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2184,13 +2184,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6040</v>
+        <v>99800</v>
       </c>
       <c r="F54" t="n">
-        <v>3311</v>
+        <v>200</v>
       </c>
       <c r="G54" t="n">
-        <v>19998440</v>
+        <v>19960000</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>26250</v>
+        <v>6040</v>
       </c>
       <c r="F55" t="n">
-        <v>762</v>
+        <v>3311</v>
       </c>
       <c r="G55" t="n">
-        <v>20002500</v>
+        <v>19998440</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2248,13 +2248,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>22850</v>
+        <v>26250</v>
       </c>
       <c r="F56" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G56" t="n">
-        <v>19993750</v>
+        <v>20002500</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>168500</v>
+        <v>22850</v>
       </c>
       <c r="F57" t="n">
-        <v>119</v>
+        <v>875</v>
       </c>
       <c r="G57" t="n">
-        <v>20051500</v>
+        <v>19993750</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2298,12 +2298,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>22850</v>
+        <v>168500</v>
       </c>
       <c r="F58" t="n">
-        <v>875</v>
+        <v>119</v>
       </c>
       <c r="G58" t="n">
-        <v>19993750</v>
+        <v>20051500</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>37900</v>
+        <v>22850</v>
       </c>
       <c r="F59" t="n">
-        <v>528</v>
+        <v>875</v>
       </c>
       <c r="G59" t="n">
-        <v>20011200</v>
+        <v>19993750</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2362,12 +2362,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2376,13 +2376,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>239000</v>
+        <v>37900</v>
       </c>
       <c r="F60" t="n">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="G60" t="n">
-        <v>20076000</v>
+        <v>20011200</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>298000</v>
+        <v>239000</v>
       </c>
       <c r="F61" t="n">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="G61" t="n">
-        <v>34866000</v>
+        <v>20076000</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2426,12 +2426,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2440,13 +2440,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>393000</v>
+        <v>298000</v>
       </c>
       <c r="F62" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="G62" t="n">
-        <v>20043000</v>
+        <v>34866000</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2458,12 +2458,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>110900</v>
+        <v>393000</v>
       </c>
       <c r="F63" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="G63" t="n">
-        <v>19962000</v>
+        <v>20043000</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2490,12 +2490,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2504,13 +2504,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>44500</v>
+        <v>110900</v>
       </c>
       <c r="F64" t="n">
-        <v>449</v>
+        <v>180</v>
       </c>
       <c r="G64" t="n">
-        <v>19980500</v>
+        <v>19962000</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2536,13 +2536,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>135000</v>
+        <v>44500</v>
       </c>
       <c r="F65" t="n">
-        <v>148</v>
+        <v>449</v>
       </c>
       <c r="G65" t="n">
-        <v>19980000</v>
+        <v>19980500</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>33750</v>
+        <v>135000</v>
       </c>
       <c r="F66" t="n">
-        <v>593</v>
+        <v>148</v>
       </c>
       <c r="G66" t="n">
-        <v>20013750</v>
+        <v>19980000</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2586,29 +2586,61 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F67" t="n">
+        <v>593</v>
+      </c>
+      <c r="G67" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
         <v>124600</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F68" t="n">
         <v>161</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G68" t="n">
         <v>20060600</v>
       </c>
-      <c r="H67" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,68 +473,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>21800</v>
+        <v>92500</v>
       </c>
       <c r="F2" t="n">
-        <v>832</v>
+        <v>106</v>
       </c>
       <c r="G2" t="n">
-        <v>18137600</v>
+        <v>9805000</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>32250</v>
+        <v>21800</v>
       </c>
       <c r="F3" t="n">
-        <v>878</v>
+        <v>832</v>
       </c>
       <c r="G3" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>18137600</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,12 +542,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -558,16 +556,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105800</v>
+        <v>32250</v>
       </c>
       <c r="F4" t="n">
-        <v>332</v>
+        <v>878</v>
       </c>
       <c r="G4" t="n">
-        <v>35125600</v>
+        <v>28315500</v>
       </c>
       <c r="H4" t="n">
-        <v>17.17</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="5">
@@ -578,12 +576,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -592,16 +590,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>33750</v>
+        <v>105800</v>
       </c>
       <c r="F5" t="n">
-        <v>791</v>
+        <v>332</v>
       </c>
       <c r="G5" t="n">
-        <v>26696250</v>
+        <v>35125600</v>
       </c>
       <c r="H5" t="n">
-        <v>0.29</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="6">
@@ -612,63 +610,63 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>86300</v>
+        <v>33750</v>
       </c>
       <c r="F6" t="n">
-        <v>352</v>
+        <v>791</v>
       </c>
       <c r="G6" t="n">
-        <v>30377600</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>21000</v>
+        <v>86300</v>
       </c>
       <c r="F7" t="n">
-        <v>1517</v>
+        <v>352</v>
       </c>
       <c r="G7" t="n">
-        <v>31857000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.96</v>
-      </c>
+        <v>30377600</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -678,29 +676,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21900</v>
+        <v>21000</v>
       </c>
       <c r="F8" t="n">
-        <v>906</v>
+        <v>1517</v>
       </c>
       <c r="G8" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>31857000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -710,44 +710,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>135300</v>
+        <v>21900</v>
       </c>
       <c r="F9" t="n">
-        <v>226</v>
+        <v>906</v>
       </c>
       <c r="G9" t="n">
-        <v>30577800</v>
+        <v>19841400</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -756,13 +756,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22250</v>
+        <v>135300</v>
       </c>
       <c r="F10" t="n">
-        <v>1399</v>
+        <v>226</v>
       </c>
       <c r="G10" t="n">
-        <v>31127750</v>
+        <v>30577800</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -774,31 +774,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>33500</v>
+        <v>22250</v>
       </c>
       <c r="F11" t="n">
-        <v>848</v>
+        <v>1399</v>
       </c>
       <c r="G11" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -808,12 +806,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -822,49 +820,51 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>300000</v>
+        <v>33500</v>
       </c>
       <c r="F12" t="n">
-        <v>104</v>
+        <v>848</v>
       </c>
       <c r="G12" t="n">
-        <v>31200000</v>
+        <v>28408000</v>
       </c>
       <c r="H12" t="n">
-        <v>20.95</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>28200</v>
+        <v>300000</v>
       </c>
       <c r="F13" t="n">
-        <v>1105</v>
+        <v>104</v>
       </c>
       <c r="G13" t="n">
-        <v>31161000</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -874,31 +874,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>398000</v>
+        <v>28200</v>
       </c>
       <c r="F14" t="n">
-        <v>72</v>
+        <v>1105</v>
       </c>
       <c r="G14" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31161000</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -908,12 +906,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -922,16 +920,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5620</v>
+        <v>398000</v>
       </c>
       <c r="F15" t="n">
-        <v>4707</v>
+        <v>72</v>
       </c>
       <c r="G15" t="n">
-        <v>26453340</v>
+        <v>28656000</v>
       </c>
       <c r="H15" t="n">
-        <v>-8.220000000000001</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="16">
@@ -942,59 +940,61 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>126900</v>
+        <v>5620</v>
       </c>
       <c r="F16" t="n">
-        <v>246</v>
+        <v>4707</v>
       </c>
       <c r="G16" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1671000</v>
+        <v>126900</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>246</v>
       </c>
       <c r="G17" t="n">
-        <v>73524000</v>
+        <v>31217400</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -1006,27 +1006,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>50600</v>
+        <v>1671000</v>
       </c>
       <c r="F18" t="n">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G18" t="n">
-        <v>9411600</v>
+        <v>73524000</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11720</v>
+        <v>50600</v>
       </c>
       <c r="F19" t="n">
-        <v>665</v>
+        <v>186</v>
       </c>
       <c r="G19" t="n">
-        <v>7793800</v>
+        <v>9411600</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1084,13 +1084,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>414000</v>
+        <v>11720</v>
       </c>
       <c r="F20" t="n">
-        <v>26</v>
+        <v>665</v>
       </c>
       <c r="G20" t="n">
-        <v>10764000</v>
+        <v>7793800</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1102,27 +1102,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>257000</v>
+        <v>414000</v>
       </c>
       <c r="F21" t="n">
-        <v>239</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>61423000</v>
+        <v>10764000</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1134,27 +1134,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>33900</v>
+        <v>257000</v>
       </c>
       <c r="F22" t="n">
-        <v>292</v>
+        <v>239</v>
       </c>
       <c r="G22" t="n">
-        <v>9898800</v>
+        <v>61423000</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>515000</v>
+        <v>33900</v>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>292</v>
       </c>
       <c r="G23" t="n">
-        <v>8755000</v>
+        <v>9898800</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>141200</v>
+        <v>515000</v>
       </c>
       <c r="F24" t="n">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="G24" t="n">
-        <v>11437200</v>
+        <v>8755000</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6320</v>
+        <v>141200</v>
       </c>
       <c r="F25" t="n">
-        <v>1396</v>
+        <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>8822720</v>
+        <v>11437200</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1262,27 +1262,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>90300</v>
+        <v>6320</v>
       </c>
       <c r="F26" t="n">
-        <v>332</v>
+        <v>1396</v>
       </c>
       <c r="G26" t="n">
-        <v>29979600</v>
+        <v>8822720</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1294,31 +1294,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>163100</v>
+        <v>90300</v>
       </c>
       <c r="F27" t="n">
-        <v>119</v>
+        <v>332</v>
       </c>
       <c r="G27" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>29979600</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1328,29 +1326,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>37900</v>
+        <v>163100</v>
       </c>
       <c r="F28" t="n">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="G28" t="n">
-        <v>6177700</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1374,13 +1374,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>19990</v>
+        <v>37900</v>
       </c>
       <c r="F29" t="n">
-        <v>615</v>
+        <v>163</v>
       </c>
       <c r="G29" t="n">
-        <v>12293850</v>
+        <v>6177700</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1406,13 +1406,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>35100</v>
+        <v>19990</v>
       </c>
       <c r="F30" t="n">
-        <v>320</v>
+        <v>615</v>
       </c>
       <c r="G30" t="n">
-        <v>11232000</v>
+        <v>12293850</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>286000</v>
+        <v>35100</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="G31" t="n">
-        <v>5720000</v>
+        <v>11232000</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1456,31 +1456,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>416000</v>
+        <v>286000</v>
       </c>
       <c r="F32" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G32" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H32" t="n">
-        <v>5.85</v>
-      </c>
+        <v>5720000</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1490,29 +1488,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>49450</v>
+        <v>416000</v>
       </c>
       <c r="F33" t="n">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="G33" t="n">
-        <v>7565850</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>138000</v>
+        <v>49450</v>
       </c>
       <c r="F34" t="n">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="G34" t="n">
-        <v>9384000</v>
+        <v>7565850</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>31950</v>
+        <v>138000</v>
       </c>
       <c r="F35" t="n">
-        <v>339</v>
+        <v>68</v>
       </c>
       <c r="G35" t="n">
-        <v>10831050</v>
+        <v>9384000</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1600,45 +1600,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>124800</v>
+        <v>31950</v>
       </c>
       <c r="F36" t="n">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="G36" t="n">
-        <v>9734400</v>
+        <v>10831050</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>10800</v>
+        <v>124800</v>
       </c>
       <c r="F37" t="n">
-        <v>1892</v>
+        <v>78</v>
       </c>
       <c r="G37" t="n">
-        <v>20433600</v>
+        <v>9734400</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1650,31 +1650,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>11880</v>
+        <v>10800</v>
       </c>
       <c r="F38" t="n">
-        <v>1474</v>
+        <v>1892</v>
       </c>
       <c r="G38" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1684,29 +1682,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>20200</v>
+        <v>11880</v>
       </c>
       <c r="F39" t="n">
-        <v>1517</v>
+        <v>1474</v>
       </c>
       <c r="G39" t="n">
-        <v>30643400</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1716,27 +1716,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102200</v>
+        <v>20200</v>
       </c>
       <c r="F40" t="n">
-        <v>200</v>
+        <v>1517</v>
       </c>
       <c r="G40" t="n">
-        <v>20440000</v>
+        <v>30643400</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1748,31 +1748,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>23450</v>
+        <v>102200</v>
       </c>
       <c r="F41" t="n">
-        <v>762</v>
+        <v>200</v>
       </c>
       <c r="G41" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1782,12 +1780,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1796,16 +1794,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>22050</v>
+        <v>23450</v>
       </c>
       <c r="F42" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G42" t="n">
-        <v>19293750</v>
+        <v>17868900</v>
       </c>
       <c r="H42" t="n">
-        <v>-3.5</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="43">
@@ -1816,29 +1814,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>32550</v>
+        <v>22050</v>
       </c>
       <c r="F43" t="n">
-        <v>628</v>
+        <v>875</v>
       </c>
       <c r="G43" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1848,63 +1848,63 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>99700</v>
+        <v>32550</v>
       </c>
       <c r="F44" t="n">
-        <v>180</v>
+        <v>628</v>
       </c>
       <c r="G44" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20441400</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1662000</v>
+        <v>99700</v>
       </c>
       <c r="F45" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G45" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>49700</v>
+        <v>1662000</v>
       </c>
       <c r="F46" t="n">
-        <v>402</v>
+        <v>150</v>
       </c>
       <c r="G46" t="n">
-        <v>19979400</v>
+        <v>249300000</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1960,13 +1960,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>435000</v>
+        <v>49700</v>
       </c>
       <c r="F47" t="n">
-        <v>46</v>
+        <v>402</v>
       </c>
       <c r="G47" t="n">
-        <v>20010000</v>
+        <v>19979400</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>268500</v>
+        <v>435000</v>
       </c>
       <c r="F48" t="n">
-        <v>931</v>
+        <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>249973500</v>
+        <v>20010000</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2024,13 +2024,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>13570</v>
+        <v>268500</v>
       </c>
       <c r="F49" t="n">
-        <v>1474</v>
+        <v>931</v>
       </c>
       <c r="G49" t="n">
-        <v>20002180</v>
+        <v>249973500</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>343500</v>
+        <v>13570</v>
       </c>
       <c r="F50" t="n">
-        <v>87</v>
+        <v>1474</v>
       </c>
       <c r="G50" t="n">
-        <v>29884500</v>
+        <v>20002180</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2074,12 +2074,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>34150</v>
+        <v>343500</v>
       </c>
       <c r="F51" t="n">
-        <v>586</v>
+        <v>87</v>
       </c>
       <c r="G51" t="n">
-        <v>20011900</v>
+        <v>29884500</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>488000</v>
+        <v>34150</v>
       </c>
       <c r="F52" t="n">
-        <v>41</v>
+        <v>586</v>
       </c>
       <c r="G52" t="n">
-        <v>20008000</v>
+        <v>20011900</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>153600</v>
+        <v>488000</v>
       </c>
       <c r="F53" t="n">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="G53" t="n">
-        <v>19968000</v>
+        <v>20008000</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2184,13 +2184,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>99800</v>
+        <v>153600</v>
       </c>
       <c r="F54" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="G54" t="n">
-        <v>19960000</v>
+        <v>19968000</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6040</v>
+        <v>99800</v>
       </c>
       <c r="F55" t="n">
-        <v>3311</v>
+        <v>200</v>
       </c>
       <c r="G55" t="n">
-        <v>19998440</v>
+        <v>19960000</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2248,13 +2248,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>26250</v>
+        <v>6040</v>
       </c>
       <c r="F56" t="n">
-        <v>762</v>
+        <v>3311</v>
       </c>
       <c r="G56" t="n">
-        <v>20002500</v>
+        <v>19998440</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>22850</v>
+        <v>26250</v>
       </c>
       <c r="F57" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G57" t="n">
-        <v>19993750</v>
+        <v>20002500</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2298,12 +2298,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>168500</v>
+        <v>22850</v>
       </c>
       <c r="F58" t="n">
-        <v>119</v>
+        <v>875</v>
       </c>
       <c r="G58" t="n">
-        <v>20051500</v>
+        <v>19993750</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>22850</v>
+        <v>168500</v>
       </c>
       <c r="F59" t="n">
-        <v>875</v>
+        <v>119</v>
       </c>
       <c r="G59" t="n">
-        <v>19993750</v>
+        <v>20051500</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2362,12 +2362,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2376,13 +2376,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>37900</v>
+        <v>22850</v>
       </c>
       <c r="F60" t="n">
-        <v>528</v>
+        <v>875</v>
       </c>
       <c r="G60" t="n">
-        <v>20011200</v>
+        <v>19993750</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>239000</v>
+        <v>37900</v>
       </c>
       <c r="F61" t="n">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="G61" t="n">
-        <v>20076000</v>
+        <v>20011200</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2426,12 +2426,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2440,13 +2440,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>298000</v>
+        <v>239000</v>
       </c>
       <c r="F62" t="n">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="G62" t="n">
-        <v>34866000</v>
+        <v>20076000</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2458,12 +2458,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>393000</v>
+        <v>298000</v>
       </c>
       <c r="F63" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="G63" t="n">
-        <v>20043000</v>
+        <v>34866000</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2490,12 +2490,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2504,13 +2504,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>110900</v>
+        <v>393000</v>
       </c>
       <c r="F64" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="G64" t="n">
-        <v>19962000</v>
+        <v>20043000</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2536,13 +2536,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>44500</v>
+        <v>110900</v>
       </c>
       <c r="F65" t="n">
-        <v>449</v>
+        <v>180</v>
       </c>
       <c r="G65" t="n">
-        <v>19980500</v>
+        <v>19962000</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>135000</v>
+        <v>44500</v>
       </c>
       <c r="F66" t="n">
-        <v>148</v>
+        <v>449</v>
       </c>
       <c r="G66" t="n">
-        <v>19980000</v>
+        <v>19980500</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2600,13 +2600,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>33750</v>
+        <v>135000</v>
       </c>
       <c r="F67" t="n">
-        <v>593</v>
+        <v>148</v>
       </c>
       <c r="G67" t="n">
-        <v>20013750</v>
+        <v>19980000</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2618,29 +2618,61 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F68" t="n">
+        <v>593</v>
+      </c>
+      <c r="G68" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
         <v>124600</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F69" t="n">
         <v>161</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G69" t="n">
         <v>20060600</v>
       </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,68 +505,66 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>21800</v>
+        <v>25550</v>
       </c>
       <c r="F3" t="n">
-        <v>832</v>
+        <v>1151</v>
       </c>
       <c r="G3" t="n">
-        <v>18137600</v>
+        <v>29408050</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>32250</v>
+        <v>21800</v>
       </c>
       <c r="F4" t="n">
-        <v>878</v>
+        <v>832</v>
       </c>
       <c r="G4" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>18137600</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -576,12 +574,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -590,16 +588,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105800</v>
+        <v>32250</v>
       </c>
       <c r="F5" t="n">
-        <v>332</v>
+        <v>878</v>
       </c>
       <c r="G5" t="n">
-        <v>35125600</v>
+        <v>28315500</v>
       </c>
       <c r="H5" t="n">
-        <v>17.17</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="6">
@@ -610,12 +608,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -624,16 +622,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>33750</v>
+        <v>105800</v>
       </c>
       <c r="F6" t="n">
-        <v>791</v>
+        <v>332</v>
       </c>
       <c r="G6" t="n">
-        <v>26696250</v>
+        <v>35125600</v>
       </c>
       <c r="H6" t="n">
-        <v>0.29</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="7">
@@ -644,63 +642,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>86300</v>
+        <v>33750</v>
       </c>
       <c r="F7" t="n">
-        <v>352</v>
+        <v>791</v>
       </c>
       <c r="G7" t="n">
-        <v>30377600</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21000</v>
+        <v>86300</v>
       </c>
       <c r="F8" t="n">
-        <v>1517</v>
+        <v>352</v>
       </c>
       <c r="G8" t="n">
-        <v>31857000</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.96</v>
-      </c>
+        <v>30377600</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -710,29 +708,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>21900</v>
+        <v>21000</v>
       </c>
       <c r="F9" t="n">
-        <v>906</v>
+        <v>1517</v>
       </c>
       <c r="G9" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>31857000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -742,44 +742,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>135300</v>
+        <v>21900</v>
       </c>
       <c r="F10" t="n">
-        <v>226</v>
+        <v>906</v>
       </c>
       <c r="G10" t="n">
-        <v>30577800</v>
+        <v>19841400</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -788,13 +788,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22250</v>
+        <v>135300</v>
       </c>
       <c r="F11" t="n">
-        <v>1399</v>
+        <v>226</v>
       </c>
       <c r="G11" t="n">
-        <v>31127750</v>
+        <v>30577800</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -806,31 +806,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>33500</v>
+        <v>22250</v>
       </c>
       <c r="F12" t="n">
-        <v>848</v>
+        <v>1399</v>
       </c>
       <c r="G12" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -840,12 +838,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -854,49 +852,51 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>300000</v>
+        <v>33500</v>
       </c>
       <c r="F13" t="n">
-        <v>104</v>
+        <v>848</v>
       </c>
       <c r="G13" t="n">
-        <v>31200000</v>
+        <v>28408000</v>
       </c>
       <c r="H13" t="n">
-        <v>20.95</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>28200</v>
+        <v>300000</v>
       </c>
       <c r="F14" t="n">
-        <v>1105</v>
+        <v>104</v>
       </c>
       <c r="G14" t="n">
-        <v>31161000</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -906,31 +906,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>398000</v>
+        <v>28200</v>
       </c>
       <c r="F15" t="n">
-        <v>72</v>
+        <v>1105</v>
       </c>
       <c r="G15" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31161000</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -940,12 +938,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -954,16 +952,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5620</v>
+        <v>398000</v>
       </c>
       <c r="F16" t="n">
-        <v>4707</v>
+        <v>72</v>
       </c>
       <c r="G16" t="n">
-        <v>26453340</v>
+        <v>28656000</v>
       </c>
       <c r="H16" t="n">
-        <v>-8.220000000000001</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="17">
@@ -974,59 +972,61 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>126900</v>
+        <v>5620</v>
       </c>
       <c r="F17" t="n">
-        <v>246</v>
+        <v>4707</v>
       </c>
       <c r="G17" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1671000</v>
+        <v>126900</v>
       </c>
       <c r="F18" t="n">
-        <v>44</v>
+        <v>246</v>
       </c>
       <c r="G18" t="n">
-        <v>73524000</v>
+        <v>31217400</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1038,27 +1038,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>50600</v>
+        <v>1671000</v>
       </c>
       <c r="F19" t="n">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G19" t="n">
-        <v>9411600</v>
+        <v>73524000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1084,13 +1084,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11720</v>
+        <v>50600</v>
       </c>
       <c r="F20" t="n">
-        <v>665</v>
+        <v>186</v>
       </c>
       <c r="G20" t="n">
-        <v>7793800</v>
+        <v>9411600</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1116,13 +1116,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>414000</v>
+        <v>11720</v>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>665</v>
       </c>
       <c r="G21" t="n">
-        <v>10764000</v>
+        <v>7793800</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1134,27 +1134,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>257000</v>
+        <v>414000</v>
       </c>
       <c r="F22" t="n">
-        <v>239</v>
+        <v>26</v>
       </c>
       <c r="G22" t="n">
-        <v>61423000</v>
+        <v>10764000</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>33900</v>
+        <v>257000</v>
       </c>
       <c r="F23" t="n">
-        <v>292</v>
+        <v>239</v>
       </c>
       <c r="G23" t="n">
-        <v>9898800</v>
+        <v>61423000</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>515000</v>
+        <v>33900</v>
       </c>
       <c r="F24" t="n">
-        <v>17</v>
+        <v>292</v>
       </c>
       <c r="G24" t="n">
-        <v>8755000</v>
+        <v>9898800</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>141200</v>
+        <v>515000</v>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="G25" t="n">
-        <v>11437200</v>
+        <v>8755000</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1276,13 +1276,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6320</v>
+        <v>141200</v>
       </c>
       <c r="F26" t="n">
-        <v>1396</v>
+        <v>81</v>
       </c>
       <c r="G26" t="n">
-        <v>8822720</v>
+        <v>11437200</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1294,27 +1294,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>90300</v>
+        <v>6320</v>
       </c>
       <c r="F27" t="n">
-        <v>332</v>
+        <v>1396</v>
       </c>
       <c r="G27" t="n">
-        <v>29979600</v>
+        <v>8822720</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1326,31 +1326,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>163100</v>
+        <v>90300</v>
       </c>
       <c r="F28" t="n">
-        <v>119</v>
+        <v>332</v>
       </c>
       <c r="G28" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>29979600</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1360,29 +1358,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>37900</v>
+        <v>163100</v>
       </c>
       <c r="F29" t="n">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="G29" t="n">
-        <v>6177700</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1406,13 +1406,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>19990</v>
+        <v>37900</v>
       </c>
       <c r="F30" t="n">
-        <v>615</v>
+        <v>163</v>
       </c>
       <c r="G30" t="n">
-        <v>12293850</v>
+        <v>6177700</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>35100</v>
+        <v>19990</v>
       </c>
       <c r="F31" t="n">
-        <v>320</v>
+        <v>615</v>
       </c>
       <c r="G31" t="n">
-        <v>11232000</v>
+        <v>12293850</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1470,13 +1470,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>286000</v>
+        <v>35100</v>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="G32" t="n">
-        <v>5720000</v>
+        <v>11232000</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1488,31 +1488,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>416000</v>
+        <v>286000</v>
       </c>
       <c r="F33" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G33" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H33" t="n">
-        <v>5.85</v>
-      </c>
+        <v>5720000</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1522,29 +1520,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>49450</v>
+        <v>416000</v>
       </c>
       <c r="F34" t="n">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="G34" t="n">
-        <v>7565850</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>138000</v>
+        <v>49450</v>
       </c>
       <c r="F35" t="n">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="G35" t="n">
-        <v>9384000</v>
+        <v>7565850</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1600,13 +1600,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>31950</v>
+        <v>138000</v>
       </c>
       <c r="F36" t="n">
-        <v>339</v>
+        <v>68</v>
       </c>
       <c r="G36" t="n">
-        <v>10831050</v>
+        <v>9384000</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1632,45 +1632,45 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>124800</v>
+        <v>31950</v>
       </c>
       <c r="F37" t="n">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="G37" t="n">
-        <v>9734400</v>
+        <v>10831050</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>10800</v>
+        <v>124800</v>
       </c>
       <c r="F38" t="n">
-        <v>1892</v>
+        <v>78</v>
       </c>
       <c r="G38" t="n">
-        <v>20433600</v>
+        <v>9734400</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1682,31 +1682,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>11880</v>
+        <v>10800</v>
       </c>
       <c r="F39" t="n">
-        <v>1474</v>
+        <v>1892</v>
       </c>
       <c r="G39" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1716,29 +1714,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>20200</v>
+        <v>11880</v>
       </c>
       <c r="F40" t="n">
-        <v>1517</v>
+        <v>1474</v>
       </c>
       <c r="G40" t="n">
-        <v>30643400</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1748,27 +1748,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102200</v>
+        <v>20200</v>
       </c>
       <c r="F41" t="n">
-        <v>200</v>
+        <v>1517</v>
       </c>
       <c r="G41" t="n">
-        <v>20440000</v>
+        <v>30643400</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1780,31 +1780,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>23450</v>
+        <v>102200</v>
       </c>
       <c r="F42" t="n">
-        <v>762</v>
+        <v>200</v>
       </c>
       <c r="G42" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1814,12 +1812,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1828,16 +1826,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>22050</v>
+        <v>23450</v>
       </c>
       <c r="F43" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G43" t="n">
-        <v>19293750</v>
+        <v>17868900</v>
       </c>
       <c r="H43" t="n">
-        <v>-3.5</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="44">
@@ -1848,29 +1846,31 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>32550</v>
+        <v>22050</v>
       </c>
       <c r="F44" t="n">
-        <v>628</v>
+        <v>875</v>
       </c>
       <c r="G44" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1880,63 +1880,63 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>99700</v>
+        <v>32550</v>
       </c>
       <c r="F45" t="n">
-        <v>180</v>
+        <v>628</v>
       </c>
       <c r="G45" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20441400</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1662000</v>
+        <v>99700</v>
       </c>
       <c r="F46" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G46" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1960,13 +1960,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>49700</v>
+        <v>1662000</v>
       </c>
       <c r="F47" t="n">
-        <v>402</v>
+        <v>150</v>
       </c>
       <c r="G47" t="n">
-        <v>19979400</v>
+        <v>249300000</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>435000</v>
+        <v>49700</v>
       </c>
       <c r="F48" t="n">
-        <v>46</v>
+        <v>402</v>
       </c>
       <c r="G48" t="n">
-        <v>20010000</v>
+        <v>19979400</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2024,13 +2024,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>268500</v>
+        <v>435000</v>
       </c>
       <c r="F49" t="n">
-        <v>931</v>
+        <v>46</v>
       </c>
       <c r="G49" t="n">
-        <v>249973500</v>
+        <v>20010000</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>13570</v>
+        <v>268500</v>
       </c>
       <c r="F50" t="n">
-        <v>1474</v>
+        <v>931</v>
       </c>
       <c r="G50" t="n">
-        <v>20002180</v>
+        <v>249973500</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2074,12 +2074,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>343500</v>
+        <v>13570</v>
       </c>
       <c r="F51" t="n">
-        <v>87</v>
+        <v>1474</v>
       </c>
       <c r="G51" t="n">
-        <v>29884500</v>
+        <v>20002180</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>34150</v>
+        <v>343500</v>
       </c>
       <c r="F52" t="n">
-        <v>586</v>
+        <v>87</v>
       </c>
       <c r="G52" t="n">
-        <v>20011900</v>
+        <v>29884500</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>488000</v>
+        <v>34150</v>
       </c>
       <c r="F53" t="n">
-        <v>41</v>
+        <v>586</v>
       </c>
       <c r="G53" t="n">
-        <v>20008000</v>
+        <v>20011900</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2184,13 +2184,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>153600</v>
+        <v>488000</v>
       </c>
       <c r="F54" t="n">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="G54" t="n">
-        <v>19968000</v>
+        <v>20008000</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>99800</v>
+        <v>153600</v>
       </c>
       <c r="F55" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="G55" t="n">
-        <v>19960000</v>
+        <v>19968000</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2248,13 +2248,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6040</v>
+        <v>99800</v>
       </c>
       <c r="F56" t="n">
-        <v>3311</v>
+        <v>200</v>
       </c>
       <c r="G56" t="n">
-        <v>19998440</v>
+        <v>19960000</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>26250</v>
+        <v>6040</v>
       </c>
       <c r="F57" t="n">
-        <v>762</v>
+        <v>3311</v>
       </c>
       <c r="G57" t="n">
-        <v>20002500</v>
+        <v>19998440</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2298,12 +2298,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>22850</v>
+        <v>26250</v>
       </c>
       <c r="F58" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G58" t="n">
-        <v>19993750</v>
+        <v>20002500</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>168500</v>
+        <v>22850</v>
       </c>
       <c r="F59" t="n">
-        <v>119</v>
+        <v>875</v>
       </c>
       <c r="G59" t="n">
-        <v>20051500</v>
+        <v>19993750</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2362,12 +2362,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2376,13 +2376,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>22850</v>
+        <v>168500</v>
       </c>
       <c r="F60" t="n">
-        <v>875</v>
+        <v>119</v>
       </c>
       <c r="G60" t="n">
-        <v>19993750</v>
+        <v>20051500</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>37900</v>
+        <v>22850</v>
       </c>
       <c r="F61" t="n">
-        <v>528</v>
+        <v>875</v>
       </c>
       <c r="G61" t="n">
-        <v>20011200</v>
+        <v>19993750</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2426,12 +2426,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2440,13 +2440,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>239000</v>
+        <v>37900</v>
       </c>
       <c r="F62" t="n">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="G62" t="n">
-        <v>20076000</v>
+        <v>20011200</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2458,12 +2458,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>298000</v>
+        <v>239000</v>
       </c>
       <c r="F63" t="n">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="G63" t="n">
-        <v>34866000</v>
+        <v>20076000</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2490,12 +2490,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2504,13 +2504,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>393000</v>
+        <v>298000</v>
       </c>
       <c r="F64" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="G64" t="n">
-        <v>20043000</v>
+        <v>34866000</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2536,13 +2536,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>110900</v>
+        <v>393000</v>
       </c>
       <c r="F65" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="G65" t="n">
-        <v>19962000</v>
+        <v>20043000</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>44500</v>
+        <v>110900</v>
       </c>
       <c r="F66" t="n">
-        <v>449</v>
+        <v>180</v>
       </c>
       <c r="G66" t="n">
-        <v>19980500</v>
+        <v>19962000</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2600,13 +2600,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>135000</v>
+        <v>44500</v>
       </c>
       <c r="F67" t="n">
-        <v>148</v>
+        <v>449</v>
       </c>
       <c r="G67" t="n">
-        <v>19980000</v>
+        <v>19980500</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2618,12 +2618,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>33750</v>
+        <v>135000</v>
       </c>
       <c r="F68" t="n">
-        <v>593</v>
+        <v>148</v>
       </c>
       <c r="G68" t="n">
-        <v>20013750</v>
+        <v>19980000</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2650,29 +2650,61 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F69" t="n">
+        <v>593</v>
+      </c>
+      <c r="G69" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
         <v>124600</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F70" t="n">
         <v>161</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G70" t="n">
         <v>20060600</v>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,32 +473,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>92500</v>
+        <v>78600</v>
       </c>
       <c r="F2" t="n">
-        <v>106</v>
+        <v>389</v>
       </c>
       <c r="G2" t="n">
-        <v>9805000</v>
+        <v>30575400</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -510,95 +510,93 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25550</v>
+        <v>92500</v>
       </c>
       <c r="F3" t="n">
-        <v>1151</v>
+        <v>106</v>
       </c>
       <c r="G3" t="n">
-        <v>29408050</v>
+        <v>9805000</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>21800</v>
+        <v>25550</v>
       </c>
       <c r="F4" t="n">
-        <v>832</v>
+        <v>1151</v>
       </c>
       <c r="G4" t="n">
-        <v>18137600</v>
+        <v>29408050</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>32250</v>
+        <v>21800</v>
       </c>
       <c r="F5" t="n">
-        <v>878</v>
+        <v>832</v>
       </c>
       <c r="G5" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>18137600</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -608,12 +606,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -622,16 +620,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105800</v>
+        <v>32250</v>
       </c>
       <c r="F6" t="n">
-        <v>332</v>
+        <v>878</v>
       </c>
       <c r="G6" t="n">
-        <v>35125600</v>
+        <v>28315500</v>
       </c>
       <c r="H6" t="n">
-        <v>17.17</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="7">
@@ -642,12 +640,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -656,16 +654,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>33750</v>
+        <v>105800</v>
       </c>
       <c r="F7" t="n">
-        <v>791</v>
+        <v>332</v>
       </c>
       <c r="G7" t="n">
-        <v>26696250</v>
+        <v>35125600</v>
       </c>
       <c r="H7" t="n">
-        <v>0.29</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="8">
@@ -676,63 +674,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>86300</v>
+        <v>33750</v>
       </c>
       <c r="F8" t="n">
-        <v>352</v>
+        <v>791</v>
       </c>
       <c r="G8" t="n">
-        <v>30377600</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>21000</v>
+        <v>86300</v>
       </c>
       <c r="F9" t="n">
-        <v>1517</v>
+        <v>352</v>
       </c>
       <c r="G9" t="n">
-        <v>31857000</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.96</v>
-      </c>
+        <v>30377600</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -742,29 +740,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>21900</v>
+        <v>21000</v>
       </c>
       <c r="F10" t="n">
-        <v>906</v>
+        <v>1517</v>
       </c>
       <c r="G10" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>31857000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -774,44 +774,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>135300</v>
+        <v>21900</v>
       </c>
       <c r="F11" t="n">
-        <v>226</v>
+        <v>906</v>
       </c>
       <c r="G11" t="n">
-        <v>30577800</v>
+        <v>19841400</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -820,13 +820,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>22250</v>
+        <v>135300</v>
       </c>
       <c r="F12" t="n">
-        <v>1399</v>
+        <v>226</v>
       </c>
       <c r="G12" t="n">
-        <v>31127750</v>
+        <v>30577800</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -838,31 +838,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>33500</v>
+        <v>22250</v>
       </c>
       <c r="F13" t="n">
-        <v>848</v>
+        <v>1399</v>
       </c>
       <c r="G13" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -872,12 +870,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -886,49 +884,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>300000</v>
+        <v>33500</v>
       </c>
       <c r="F14" t="n">
-        <v>104</v>
+        <v>848</v>
       </c>
       <c r="G14" t="n">
-        <v>31200000</v>
+        <v>28408000</v>
       </c>
       <c r="H14" t="n">
-        <v>20.95</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>28200</v>
+        <v>300000</v>
       </c>
       <c r="F15" t="n">
-        <v>1105</v>
+        <v>104</v>
       </c>
       <c r="G15" t="n">
-        <v>31161000</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -938,31 +938,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>398000</v>
+        <v>28200</v>
       </c>
       <c r="F16" t="n">
-        <v>72</v>
+        <v>1105</v>
       </c>
       <c r="G16" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31161000</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -972,12 +970,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -986,16 +984,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5620</v>
+        <v>398000</v>
       </c>
       <c r="F17" t="n">
-        <v>4707</v>
+        <v>72</v>
       </c>
       <c r="G17" t="n">
-        <v>26453340</v>
+        <v>28656000</v>
       </c>
       <c r="H17" t="n">
-        <v>-8.220000000000001</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="18">
@@ -1006,59 +1004,61 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>126900</v>
+        <v>5620</v>
       </c>
       <c r="F18" t="n">
-        <v>246</v>
+        <v>4707</v>
       </c>
       <c r="G18" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1671000</v>
+        <v>126900</v>
       </c>
       <c r="F19" t="n">
-        <v>44</v>
+        <v>246</v>
       </c>
       <c r="G19" t="n">
-        <v>73524000</v>
+        <v>31217400</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1070,27 +1070,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>50600</v>
+        <v>1671000</v>
       </c>
       <c r="F20" t="n">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G20" t="n">
-        <v>9411600</v>
+        <v>73524000</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1116,13 +1116,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>11720</v>
+        <v>50600</v>
       </c>
       <c r="F21" t="n">
-        <v>665</v>
+        <v>186</v>
       </c>
       <c r="G21" t="n">
-        <v>7793800</v>
+        <v>9411600</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>414000</v>
+        <v>11720</v>
       </c>
       <c r="F22" t="n">
-        <v>26</v>
+        <v>665</v>
       </c>
       <c r="G22" t="n">
-        <v>10764000</v>
+        <v>7793800</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>257000</v>
+        <v>414000</v>
       </c>
       <c r="F23" t="n">
-        <v>239</v>
+        <v>26</v>
       </c>
       <c r="G23" t="n">
-        <v>61423000</v>
+        <v>10764000</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1198,27 +1198,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>33900</v>
+        <v>257000</v>
       </c>
       <c r="F24" t="n">
-        <v>292</v>
+        <v>239</v>
       </c>
       <c r="G24" t="n">
-        <v>9898800</v>
+        <v>61423000</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>515000</v>
+        <v>33900</v>
       </c>
       <c r="F25" t="n">
-        <v>17</v>
+        <v>292</v>
       </c>
       <c r="G25" t="n">
-        <v>8755000</v>
+        <v>9898800</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1276,13 +1276,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>141200</v>
+        <v>515000</v>
       </c>
       <c r="F26" t="n">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>11437200</v>
+        <v>8755000</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6320</v>
+        <v>141200</v>
       </c>
       <c r="F27" t="n">
-        <v>1396</v>
+        <v>81</v>
       </c>
       <c r="G27" t="n">
-        <v>8822720</v>
+        <v>11437200</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1326,27 +1326,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>90300</v>
+        <v>6320</v>
       </c>
       <c r="F28" t="n">
-        <v>332</v>
+        <v>1396</v>
       </c>
       <c r="G28" t="n">
-        <v>29979600</v>
+        <v>8822720</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1358,31 +1358,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>163100</v>
+        <v>90300</v>
       </c>
       <c r="F29" t="n">
-        <v>119</v>
+        <v>332</v>
       </c>
       <c r="G29" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>29979600</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1392,29 +1390,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>37900</v>
+        <v>163100</v>
       </c>
       <c r="F30" t="n">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="G30" t="n">
-        <v>6177700</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>19990</v>
+        <v>37900</v>
       </c>
       <c r="F31" t="n">
-        <v>615</v>
+        <v>163</v>
       </c>
       <c r="G31" t="n">
-        <v>12293850</v>
+        <v>6177700</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1470,13 +1470,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>35100</v>
+        <v>19990</v>
       </c>
       <c r="F32" t="n">
-        <v>320</v>
+        <v>615</v>
       </c>
       <c r="G32" t="n">
-        <v>11232000</v>
+        <v>12293850</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1502,13 +1502,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>286000</v>
+        <v>35100</v>
       </c>
       <c r="F33" t="n">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="G33" t="n">
-        <v>5720000</v>
+        <v>11232000</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1520,31 +1520,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>416000</v>
+        <v>286000</v>
       </c>
       <c r="F34" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G34" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H34" t="n">
-        <v>5.85</v>
-      </c>
+        <v>5720000</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1554,29 +1552,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>49450</v>
+        <v>416000</v>
       </c>
       <c r="F35" t="n">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="G35" t="n">
-        <v>7565850</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1600,13 +1600,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>138000</v>
+        <v>49450</v>
       </c>
       <c r="F36" t="n">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="G36" t="n">
-        <v>9384000</v>
+        <v>7565850</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1632,13 +1632,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>31950</v>
+        <v>138000</v>
       </c>
       <c r="F37" t="n">
-        <v>339</v>
+        <v>68</v>
       </c>
       <c r="G37" t="n">
-        <v>10831050</v>
+        <v>9384000</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1664,45 +1664,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>124800</v>
+        <v>31950</v>
       </c>
       <c r="F38" t="n">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="G38" t="n">
-        <v>9734400</v>
+        <v>10831050</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>10800</v>
+        <v>124800</v>
       </c>
       <c r="F39" t="n">
-        <v>1892</v>
+        <v>78</v>
       </c>
       <c r="G39" t="n">
-        <v>20433600</v>
+        <v>9734400</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1714,31 +1714,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>11880</v>
+        <v>10800</v>
       </c>
       <c r="F40" t="n">
-        <v>1474</v>
+        <v>1892</v>
       </c>
       <c r="G40" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1748,29 +1746,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>20200</v>
+        <v>11880</v>
       </c>
       <c r="F41" t="n">
-        <v>1517</v>
+        <v>1474</v>
       </c>
       <c r="G41" t="n">
-        <v>30643400</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1780,27 +1780,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102200</v>
+        <v>20200</v>
       </c>
       <c r="F42" t="n">
-        <v>200</v>
+        <v>1517</v>
       </c>
       <c r="G42" t="n">
-        <v>20440000</v>
+        <v>30643400</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1812,31 +1812,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>23450</v>
+        <v>102200</v>
       </c>
       <c r="F43" t="n">
-        <v>762</v>
+        <v>200</v>
       </c>
       <c r="G43" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1846,12 +1844,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1860,16 +1858,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>22050</v>
+        <v>23450</v>
       </c>
       <c r="F44" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G44" t="n">
-        <v>19293750</v>
+        <v>17868900</v>
       </c>
       <c r="H44" t="n">
-        <v>-3.5</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="45">
@@ -1880,29 +1878,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>32550</v>
+        <v>22050</v>
       </c>
       <c r="F45" t="n">
-        <v>628</v>
+        <v>875</v>
       </c>
       <c r="G45" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1912,63 +1912,63 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>99700</v>
+        <v>32550</v>
       </c>
       <c r="F46" t="n">
-        <v>180</v>
+        <v>628</v>
       </c>
       <c r="G46" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20441400</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1662000</v>
+        <v>99700</v>
       </c>
       <c r="F47" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G47" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>49700</v>
+        <v>1662000</v>
       </c>
       <c r="F48" t="n">
-        <v>402</v>
+        <v>150</v>
       </c>
       <c r="G48" t="n">
-        <v>19979400</v>
+        <v>249300000</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2024,13 +2024,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>435000</v>
+        <v>49700</v>
       </c>
       <c r="F49" t="n">
-        <v>46</v>
+        <v>402</v>
       </c>
       <c r="G49" t="n">
-        <v>20010000</v>
+        <v>19979400</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>268500</v>
+        <v>435000</v>
       </c>
       <c r="F50" t="n">
-        <v>931</v>
+        <v>46</v>
       </c>
       <c r="G50" t="n">
-        <v>249973500</v>
+        <v>20010000</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2074,12 +2074,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>13570</v>
+        <v>268500</v>
       </c>
       <c r="F51" t="n">
-        <v>1474</v>
+        <v>931</v>
       </c>
       <c r="G51" t="n">
-        <v>20002180</v>
+        <v>249973500</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>343500</v>
+        <v>13570</v>
       </c>
       <c r="F52" t="n">
-        <v>87</v>
+        <v>1474</v>
       </c>
       <c r="G52" t="n">
-        <v>29884500</v>
+        <v>20002180</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>34150</v>
+        <v>343500</v>
       </c>
       <c r="F53" t="n">
-        <v>586</v>
+        <v>87</v>
       </c>
       <c r="G53" t="n">
-        <v>20011900</v>
+        <v>29884500</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2184,13 +2184,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>488000</v>
+        <v>34150</v>
       </c>
       <c r="F54" t="n">
-        <v>41</v>
+        <v>586</v>
       </c>
       <c r="G54" t="n">
-        <v>20008000</v>
+        <v>20011900</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>153600</v>
+        <v>488000</v>
       </c>
       <c r="F55" t="n">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="G55" t="n">
-        <v>19968000</v>
+        <v>20008000</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2248,13 +2248,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>99800</v>
+        <v>153600</v>
       </c>
       <c r="F56" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="G56" t="n">
-        <v>19960000</v>
+        <v>19968000</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6040</v>
+        <v>99800</v>
       </c>
       <c r="F57" t="n">
-        <v>3311</v>
+        <v>200</v>
       </c>
       <c r="G57" t="n">
-        <v>19998440</v>
+        <v>19960000</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2298,12 +2298,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>26250</v>
+        <v>6040</v>
       </c>
       <c r="F58" t="n">
-        <v>762</v>
+        <v>3311</v>
       </c>
       <c r="G58" t="n">
-        <v>20002500</v>
+        <v>19998440</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>22850</v>
+        <v>26250</v>
       </c>
       <c r="F59" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G59" t="n">
-        <v>19993750</v>
+        <v>20002500</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2362,12 +2362,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2376,13 +2376,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>168500</v>
+        <v>22850</v>
       </c>
       <c r="F60" t="n">
-        <v>119</v>
+        <v>875</v>
       </c>
       <c r="G60" t="n">
-        <v>20051500</v>
+        <v>19993750</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>22850</v>
+        <v>168500</v>
       </c>
       <c r="F61" t="n">
-        <v>875</v>
+        <v>119</v>
       </c>
       <c r="G61" t="n">
-        <v>19993750</v>
+        <v>20051500</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2426,12 +2426,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2440,13 +2440,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>37900</v>
+        <v>22850</v>
       </c>
       <c r="F62" t="n">
-        <v>528</v>
+        <v>875</v>
       </c>
       <c r="G62" t="n">
-        <v>20011200</v>
+        <v>19993750</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2458,12 +2458,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>239000</v>
+        <v>37900</v>
       </c>
       <c r="F63" t="n">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="G63" t="n">
-        <v>20076000</v>
+        <v>20011200</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2490,12 +2490,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2504,13 +2504,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>298000</v>
+        <v>239000</v>
       </c>
       <c r="F64" t="n">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="G64" t="n">
-        <v>34866000</v>
+        <v>20076000</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2536,13 +2536,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>393000</v>
+        <v>298000</v>
       </c>
       <c r="F65" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="G65" t="n">
-        <v>20043000</v>
+        <v>34866000</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>110900</v>
+        <v>393000</v>
       </c>
       <c r="F66" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="G66" t="n">
-        <v>19962000</v>
+        <v>20043000</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2600,13 +2600,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>44500</v>
+        <v>110900</v>
       </c>
       <c r="F67" t="n">
-        <v>449</v>
+        <v>180</v>
       </c>
       <c r="G67" t="n">
-        <v>19980500</v>
+        <v>19962000</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2618,12 +2618,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>135000</v>
+        <v>44500</v>
       </c>
       <c r="F68" t="n">
-        <v>148</v>
+        <v>449</v>
       </c>
       <c r="G68" t="n">
-        <v>19980000</v>
+        <v>19980500</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2664,13 +2664,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>33750</v>
+        <v>135000</v>
       </c>
       <c r="F69" t="n">
-        <v>593</v>
+        <v>148</v>
       </c>
       <c r="G69" t="n">
-        <v>20013750</v>
+        <v>19980000</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2682,29 +2682,61 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F70" t="n">
+        <v>593</v>
+      </c>
+      <c r="G70" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
         <v>124600</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F71" t="n">
         <v>161</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G71" t="n">
         <v>20060600</v>
       </c>
-      <c r="H70" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,49 +473,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78600</v>
+        <v>1856000</v>
       </c>
       <c r="F2" t="n">
-        <v>389</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>30575400</v>
+        <v>42688000</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,262 +524,254 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>92500</v>
+        <v>49000</v>
       </c>
       <c r="F3" t="n">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="G3" t="n">
-        <v>9805000</v>
+        <v>8183000</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25550</v>
+        <v>13340</v>
       </c>
       <c r="F4" t="n">
-        <v>1151</v>
+        <v>236</v>
       </c>
       <c r="G4" t="n">
-        <v>29408050</v>
+        <v>3148240</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21800</v>
+        <v>29800</v>
       </c>
       <c r="F5" t="n">
-        <v>832</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>18137600</v>
+        <v>1966800</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>32250</v>
+        <v>269500</v>
       </c>
       <c r="F6" t="n">
-        <v>878</v>
+        <v>118</v>
       </c>
       <c r="G6" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>31801000</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105800</v>
+        <v>330000</v>
       </c>
       <c r="F7" t="n">
-        <v>332</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>35125600</v>
-      </c>
-      <c r="H7" t="n">
-        <v>17.17</v>
-      </c>
+        <v>7920000</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>33750</v>
+        <v>35550</v>
       </c>
       <c r="F8" t="n">
-        <v>791</v>
+        <v>581</v>
       </c>
       <c r="G8" t="n">
-        <v>26696250</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.29</v>
-      </c>
+        <v>20654550</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>86300</v>
+        <v>574000</v>
       </c>
       <c r="F9" t="n">
-        <v>352</v>
+        <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>30377600</v>
+        <v>12628000</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>21000</v>
+        <v>165900</v>
       </c>
       <c r="F10" t="n">
-        <v>1517</v>
+        <v>24</v>
       </c>
       <c r="G10" t="n">
-        <v>31857000</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.96</v>
-      </c>
+        <v>3981600</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -788,30 +780,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>21900</v>
+        <v>91300</v>
       </c>
       <c r="F11" t="n">
-        <v>906</v>
+        <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>19841400</v>
+        <v>4108500</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -820,30 +812,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>135300</v>
+        <v>224500</v>
       </c>
       <c r="F12" t="n">
-        <v>226</v>
+        <v>92</v>
       </c>
       <c r="G12" t="n">
-        <v>30577800</v>
+        <v>20654000</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -852,98 +844,94 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>22250</v>
+        <v>6010</v>
       </c>
       <c r="F13" t="n">
-        <v>1399</v>
+        <v>3435</v>
       </c>
       <c r="G13" t="n">
-        <v>31127750</v>
+        <v>20644350</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>33500</v>
+        <v>25800</v>
       </c>
       <c r="F14" t="n">
-        <v>848</v>
+        <v>351</v>
       </c>
       <c r="G14" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>9055800</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>300000</v>
+        <v>49150</v>
       </c>
       <c r="F15" t="n">
-        <v>104</v>
+        <v>420</v>
       </c>
       <c r="G15" t="n">
-        <v>31200000</v>
-      </c>
-      <c r="H15" t="n">
-        <v>20.95</v>
-      </c>
+        <v>20643000</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -952,258 +940,254 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>28200</v>
+        <v>19280</v>
       </c>
       <c r="F16" t="n">
-        <v>1105</v>
+        <v>1071</v>
       </c>
       <c r="G16" t="n">
-        <v>31161000</v>
+        <v>20648880</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>398000</v>
+        <v>19740</v>
       </c>
       <c r="F17" t="n">
-        <v>72</v>
+        <v>523</v>
       </c>
       <c r="G17" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>10324020</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5620</v>
+        <v>25150</v>
       </c>
       <c r="F18" t="n">
-        <v>4707</v>
+        <v>821</v>
       </c>
       <c r="G18" t="n">
-        <v>26453340</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-8.220000000000001</v>
-      </c>
+        <v>20648150</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>126900</v>
+        <v>153500</v>
       </c>
       <c r="F19" t="n">
-        <v>246</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>31217400</v>
+        <v>3684000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1671000</v>
+        <v>6240</v>
       </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>3308</v>
       </c>
       <c r="G20" t="n">
-        <v>73524000</v>
+        <v>20641920</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>50600</v>
+        <v>15520</v>
       </c>
       <c r="F21" t="n">
-        <v>186</v>
+        <v>1330</v>
       </c>
       <c r="G21" t="n">
-        <v>9411600</v>
+        <v>20641600</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>11720</v>
+        <v>24200</v>
       </c>
       <c r="F22" t="n">
-        <v>665</v>
+        <v>210</v>
       </c>
       <c r="G22" t="n">
-        <v>7793800</v>
+        <v>5082000</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>414000</v>
+        <v>36300</v>
       </c>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>569</v>
       </c>
       <c r="G23" t="n">
-        <v>10764000</v>
+        <v>20654700</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1212,386 +1196,382 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>257000</v>
+        <v>279500</v>
       </c>
       <c r="F24" t="n">
-        <v>239</v>
+        <v>43</v>
       </c>
       <c r="G24" t="n">
-        <v>61423000</v>
+        <v>12018500</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>33900</v>
+        <v>132600</v>
       </c>
       <c r="F25" t="n">
-        <v>292</v>
+        <v>90</v>
       </c>
       <c r="G25" t="n">
-        <v>9898800</v>
+        <v>11934000</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>515000</v>
+        <v>44600</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="G26" t="n">
-        <v>8755000</v>
+        <v>6199400</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>141200</v>
+        <v>147100</v>
       </c>
       <c r="F27" t="n">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>11437200</v>
+        <v>882600</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6320</v>
+        <v>33500</v>
       </c>
       <c r="F28" t="n">
-        <v>1396</v>
+        <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>8822720</v>
+        <v>268000</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>90300</v>
+        <v>143100</v>
       </c>
       <c r="F29" t="n">
-        <v>332</v>
+        <v>95</v>
       </c>
       <c r="G29" t="n">
-        <v>29979600</v>
+        <v>13594500</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>163100</v>
+        <v>83800</v>
       </c>
       <c r="F30" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="G30" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>8882800</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>37900</v>
+        <v>42300</v>
       </c>
       <c r="F31" t="n">
-        <v>163</v>
+        <v>488</v>
       </c>
       <c r="G31" t="n">
-        <v>6177700</v>
+        <v>20642400</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>19990</v>
+        <v>81200</v>
       </c>
       <c r="F32" t="n">
-        <v>615</v>
+        <v>135</v>
       </c>
       <c r="G32" t="n">
-        <v>12293850</v>
+        <v>10962000</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>35100</v>
+        <v>78600</v>
       </c>
       <c r="F33" t="n">
-        <v>320</v>
+        <v>389</v>
       </c>
       <c r="G33" t="n">
-        <v>11232000</v>
+        <v>30575400</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>286000</v>
+        <v>92500</v>
       </c>
       <c r="F34" t="n">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="G34" t="n">
-        <v>5720000</v>
+        <v>9805000</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>416000</v>
+        <v>25550</v>
       </c>
       <c r="F35" t="n">
-        <v>51</v>
+        <v>1151</v>
       </c>
       <c r="G35" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H35" t="n">
-        <v>5.85</v>
-      </c>
+        <v>29408050</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1600,126 +1580,132 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>49450</v>
+        <v>21800</v>
       </c>
       <c r="F36" t="n">
-        <v>153</v>
+        <v>832</v>
       </c>
       <c r="G36" t="n">
-        <v>7565850</v>
+        <v>18137600</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>138000</v>
+        <v>32250</v>
       </c>
       <c r="F37" t="n">
-        <v>68</v>
+        <v>878</v>
       </c>
       <c r="G37" t="n">
-        <v>9384000</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>28315500</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-5.33</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>31950</v>
+        <v>105800</v>
       </c>
       <c r="F38" t="n">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="G38" t="n">
-        <v>10831050</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>35125600</v>
+      </c>
+      <c r="H38" t="n">
+        <v>17.17</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>124800</v>
+        <v>33750</v>
       </c>
       <c r="F39" t="n">
-        <v>78</v>
+        <v>791</v>
       </c>
       <c r="G39" t="n">
-        <v>9734400</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1728,30 +1714,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10800</v>
+        <v>86300</v>
       </c>
       <c r="F40" t="n">
-        <v>1892</v>
+        <v>352</v>
       </c>
       <c r="G40" t="n">
-        <v>20433600</v>
+        <v>30377600</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1760,130 +1746,128 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>11880</v>
+        <v>21000</v>
       </c>
       <c r="F41" t="n">
-        <v>1474</v>
+        <v>1517</v>
       </c>
       <c r="G41" t="n">
-        <v>17511120</v>
+        <v>31857000</v>
       </c>
       <c r="H41" t="n">
-        <v>-12.45</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>20200</v>
+        <v>21900</v>
       </c>
       <c r="F42" t="n">
-        <v>1517</v>
+        <v>906</v>
       </c>
       <c r="G42" t="n">
-        <v>30643400</v>
+        <v>19841400</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102200</v>
+        <v>135300</v>
       </c>
       <c r="F43" t="n">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="G43" t="n">
-        <v>20440000</v>
+        <v>30577800</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>23450</v>
+        <v>22250</v>
       </c>
       <c r="F44" t="n">
-        <v>762</v>
+        <v>1399</v>
       </c>
       <c r="G44" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1892,162 +1876,166 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>22050</v>
+        <v>33500</v>
       </c>
       <c r="F45" t="n">
-        <v>875</v>
+        <v>848</v>
       </c>
       <c r="G45" t="n">
-        <v>19293750</v>
+        <v>28408000</v>
       </c>
       <c r="H45" t="n">
-        <v>-3.5</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>32550</v>
+        <v>300000</v>
       </c>
       <c r="F46" t="n">
-        <v>628</v>
+        <v>104</v>
       </c>
       <c r="G46" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H46" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>99700</v>
+        <v>28200</v>
       </c>
       <c r="F47" t="n">
-        <v>180</v>
+        <v>1105</v>
       </c>
       <c r="G47" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>31161000</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1662000</v>
+        <v>398000</v>
       </c>
       <c r="F48" t="n">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="G48" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>49700</v>
+        <v>5620</v>
       </c>
       <c r="F49" t="n">
-        <v>402</v>
+        <v>4707</v>
       </c>
       <c r="G49" t="n">
-        <v>19979400</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2056,318 +2044,318 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>435000</v>
+        <v>126900</v>
       </c>
       <c r="F50" t="n">
-        <v>46</v>
+        <v>246</v>
       </c>
       <c r="G50" t="n">
-        <v>20010000</v>
+        <v>31217400</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>268500</v>
+        <v>1671000</v>
       </c>
       <c r="F51" t="n">
-        <v>931</v>
+        <v>44</v>
       </c>
       <c r="G51" t="n">
-        <v>249973500</v>
+        <v>73524000</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>13570</v>
+        <v>50600</v>
       </c>
       <c r="F52" t="n">
-        <v>1474</v>
+        <v>186</v>
       </c>
       <c r="G52" t="n">
-        <v>20002180</v>
+        <v>9411600</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>343500</v>
+        <v>11720</v>
       </c>
       <c r="F53" t="n">
-        <v>87</v>
+        <v>665</v>
       </c>
       <c r="G53" t="n">
-        <v>29884500</v>
+        <v>7793800</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>34150</v>
+        <v>414000</v>
       </c>
       <c r="F54" t="n">
-        <v>586</v>
+        <v>26</v>
       </c>
       <c r="G54" t="n">
-        <v>20011900</v>
+        <v>10764000</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>488000</v>
+        <v>257000</v>
       </c>
       <c r="F55" t="n">
-        <v>41</v>
+        <v>239</v>
       </c>
       <c r="G55" t="n">
-        <v>20008000</v>
+        <v>61423000</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>153600</v>
+        <v>33900</v>
       </c>
       <c r="F56" t="n">
-        <v>130</v>
+        <v>292</v>
       </c>
       <c r="G56" t="n">
-        <v>19968000</v>
+        <v>9898800</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>99800</v>
+        <v>515000</v>
       </c>
       <c r="F57" t="n">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="G57" t="n">
-        <v>19960000</v>
+        <v>8755000</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6040</v>
+        <v>141200</v>
       </c>
       <c r="F58" t="n">
-        <v>3311</v>
+        <v>81</v>
       </c>
       <c r="G58" t="n">
-        <v>19998440</v>
+        <v>11437200</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>26250</v>
+        <v>6320</v>
       </c>
       <c r="F59" t="n">
-        <v>762</v>
+        <v>1396</v>
       </c>
       <c r="G59" t="n">
-        <v>20002500</v>
+        <v>8822720</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2376,20 +2364,20 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>22850</v>
+        <v>90300</v>
       </c>
       <c r="F60" t="n">
-        <v>875</v>
+        <v>332</v>
       </c>
       <c r="G60" t="n">
-        <v>19993750</v>
+        <v>29979600</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2404,152 +2392,154 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>168500</v>
+        <v>163100</v>
       </c>
       <c r="F61" t="n">
         <v>119</v>
       </c>
       <c r="G61" t="n">
-        <v>20051500</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>22850</v>
+        <v>37900</v>
       </c>
       <c r="F62" t="n">
-        <v>875</v>
+        <v>163</v>
       </c>
       <c r="G62" t="n">
-        <v>19993750</v>
+        <v>6177700</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>37900</v>
+        <v>19990</v>
       </c>
       <c r="F63" t="n">
-        <v>528</v>
+        <v>615</v>
       </c>
       <c r="G63" t="n">
-        <v>20011200</v>
+        <v>12293850</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>239000</v>
+        <v>35100</v>
       </c>
       <c r="F64" t="n">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G64" t="n">
-        <v>20076000</v>
+        <v>11232000</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>298000</v>
+        <v>286000</v>
       </c>
       <c r="F65" t="n">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="G65" t="n">
-        <v>34866000</v>
+        <v>5720000</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2564,179 +2554,1181 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>393000</v>
+        <v>416000</v>
       </c>
       <c r="F66" t="n">
         <v>51</v>
       </c>
       <c r="G66" t="n">
-        <v>20043000</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H66" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>110900</v>
+        <v>49450</v>
       </c>
       <c r="F67" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="G67" t="n">
-        <v>19962000</v>
+        <v>7565850</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>44500</v>
+        <v>138000</v>
       </c>
       <c r="F68" t="n">
-        <v>449</v>
+        <v>68</v>
       </c>
       <c r="G68" t="n">
-        <v>19980500</v>
+        <v>9384000</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>135000</v>
+        <v>31950</v>
       </c>
       <c r="F69" t="n">
-        <v>148</v>
+        <v>339</v>
       </c>
       <c r="G69" t="n">
-        <v>19980000</v>
+        <v>10831050</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>33750</v>
+        <v>124800</v>
       </c>
       <c r="F70" t="n">
-        <v>593</v>
+        <v>78</v>
       </c>
       <c r="G70" t="n">
-        <v>20013750</v>
+        <v>9734400</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>한국화장품제조</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>003350</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1892</v>
+      </c>
+      <c r="G71" t="n">
+        <v>20433600</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>이수화학</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>005950</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>11880</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1474</v>
+      </c>
+      <c r="G72" t="n">
+        <v>17511120</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-12.45</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>20200</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1517</v>
+      </c>
+      <c r="G73" t="n">
+        <v>30643400</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SK텔레콤</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>017670</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>102200</v>
+      </c>
+      <c r="F74" t="n">
+        <v>200</v>
+      </c>
+      <c r="G74" t="n">
+        <v>20440000</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>STX엔진</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>077970</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>23450</v>
+      </c>
+      <c r="F75" t="n">
+        <v>762</v>
+      </c>
+      <c r="G75" t="n">
+        <v>17868900</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-10.67</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>089890</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>22050</v>
+      </c>
+      <c r="F76" t="n">
+        <v>875</v>
+      </c>
+      <c r="G76" t="n">
+        <v>19293750</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>아이티센글로벌</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>124500</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>32550</v>
+      </c>
+      <c r="F77" t="n">
+        <v>628</v>
+      </c>
+      <c r="G77" t="n">
+        <v>20441400</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>99700</v>
+      </c>
+      <c r="F78" t="n">
+        <v>180</v>
+      </c>
+      <c r="G78" t="n">
+        <v>17946000</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-10.1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1662000</v>
+      </c>
+      <c r="F79" t="n">
+        <v>150</v>
+      </c>
+      <c r="G79" t="n">
+        <v>249300000</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>현대해상</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>001450</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>49700</v>
+      </c>
+      <c r="F80" t="n">
+        <v>402</v>
+      </c>
+      <c r="G80" t="n">
+        <v>19979400</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>005380</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>435000</v>
+      </c>
+      <c r="F81" t="n">
+        <v>46</v>
+      </c>
+      <c r="G81" t="n">
+        <v>20010000</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>268500</v>
+      </c>
+      <c r="F82" t="n">
+        <v>931</v>
+      </c>
+      <c r="G82" t="n">
+        <v>249973500</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>이수화학</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>005950</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>13570</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1474</v>
+      </c>
+      <c r="G83" t="n">
+        <v>20002180</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>006260</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>343500</v>
+      </c>
+      <c r="F84" t="n">
+        <v>87</v>
+      </c>
+      <c r="G84" t="n">
+        <v>29884500</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>006360</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>34150</v>
+      </c>
+      <c r="F85" t="n">
+        <v>586</v>
+      </c>
+      <c r="G85" t="n">
+        <v>20011900</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>006400</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>488000</v>
+      </c>
+      <c r="F86" t="n">
+        <v>41</v>
+      </c>
+      <c r="G86" t="n">
+        <v>20008000</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>S-OIL</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>010950</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>153600</v>
+      </c>
+      <c r="F87" t="n">
+        <v>130</v>
+      </c>
+      <c r="G87" t="n">
+        <v>19968000</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SK텔레콤</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>017670</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>99800</v>
+      </c>
+      <c r="F88" t="n">
+        <v>200</v>
+      </c>
+      <c r="G88" t="n">
+        <v>19960000</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>팬오션</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>028670</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6040</v>
+      </c>
+      <c r="F89" t="n">
+        <v>3311</v>
+      </c>
+      <c r="G89" t="n">
+        <v>19998440</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>STX엔진</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>077970</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>26250</v>
+      </c>
+      <c r="F90" t="n">
+        <v>762</v>
+      </c>
+      <c r="G90" t="n">
+        <v>20002500</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>089890</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>22850</v>
+      </c>
+      <c r="F91" t="n">
+        <v>875</v>
+      </c>
+      <c r="G91" t="n">
+        <v>19993750</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>KB금융</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>105560</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>168500</v>
+      </c>
+      <c r="F92" t="n">
+        <v>119</v>
+      </c>
+      <c r="G92" t="n">
+        <v>20051500</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>22850</v>
+      </c>
+      <c r="F93" t="n">
+        <v>875</v>
+      </c>
+      <c r="G93" t="n">
+        <v>19993750</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F94" t="n">
+        <v>528</v>
+      </c>
+      <c r="G94" t="n">
+        <v>20011200</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>코스맥스</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>192820</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>239000</v>
+      </c>
+      <c r="F95" t="n">
+        <v>84</v>
+      </c>
+      <c r="G95" t="n">
+        <v>20076000</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>298000</v>
+      </c>
+      <c r="F96" t="n">
+        <v>117</v>
+      </c>
+      <c r="G96" t="n">
+        <v>34866000</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>393000</v>
+      </c>
+      <c r="F97" t="n">
+        <v>51</v>
+      </c>
+      <c r="G97" t="n">
+        <v>20043000</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F98" t="n">
+        <v>180</v>
+      </c>
+      <c r="G98" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F99" t="n">
+        <v>449</v>
+      </c>
+      <c r="G99" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F100" t="n">
+        <v>148</v>
+      </c>
+      <c r="G100" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F101" t="n">
+        <v>593</v>
+      </c>
+      <c r="G101" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
         <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
         <v>124600</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F102" t="n">
         <v>161</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G102" t="n">
         <v>20060600</v>
       </c>
-      <c r="H71" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,30 +492,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1856000</v>
+        <v>1853000</v>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>42688000</v>
+        <v>20383000</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,77 +524,77 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49000</v>
+        <v>269000</v>
       </c>
       <c r="F3" t="n">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>8183000</v>
+        <v>20444000</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>13340</v>
+        <v>106300</v>
       </c>
       <c r="F4" t="n">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="G4" t="n">
-        <v>3148240</v>
+        <v>20622200</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>29800</v>
+        <v>123100</v>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G5" t="n">
-        <v>1966800</v>
+        <v>20557700</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -606,12 +606,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>269500</v>
+        <v>1856000</v>
       </c>
       <c r="F6" t="n">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>31801000</v>
+        <v>42688000</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -638,12 +638,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>330000</v>
+        <v>49000</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="G7" t="n">
-        <v>7920000</v>
+        <v>8183000</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -670,27 +670,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>35550</v>
+        <v>13340</v>
       </c>
       <c r="F8" t="n">
-        <v>581</v>
+        <v>236</v>
       </c>
       <c r="G8" t="n">
-        <v>20654550</v>
+        <v>3148240</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -702,12 +702,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -716,13 +716,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>574000</v>
+        <v>29800</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="G9" t="n">
-        <v>12628000</v>
+        <v>1966800</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -748,13 +748,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>165900</v>
+        <v>269500</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="G10" t="n">
-        <v>3981600</v>
+        <v>31801000</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -766,27 +766,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>91300</v>
+        <v>330000</v>
       </c>
       <c r="F11" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G11" t="n">
-        <v>4108500</v>
+        <v>7920000</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224500</v>
+        <v>35550</v>
       </c>
       <c r="F12" t="n">
-        <v>92</v>
+        <v>581</v>
       </c>
       <c r="G12" t="n">
-        <v>20654000</v>
+        <v>20654550</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -830,27 +830,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6010</v>
+        <v>574000</v>
       </c>
       <c r="F13" t="n">
-        <v>3435</v>
+        <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>20644350</v>
+        <v>12628000</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25800</v>
+        <v>165900</v>
       </c>
       <c r="F14" t="n">
-        <v>351</v>
+        <v>24</v>
       </c>
       <c r="G14" t="n">
-        <v>9055800</v>
+        <v>3981600</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -894,27 +894,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>49150</v>
+        <v>91300</v>
       </c>
       <c r="F15" t="n">
-        <v>420</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
-        <v>20643000</v>
+        <v>4108500</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19280</v>
+        <v>224500</v>
       </c>
       <c r="F16" t="n">
-        <v>1071</v>
+        <v>92</v>
       </c>
       <c r="G16" t="n">
-        <v>20648880</v>
+        <v>20654000</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -958,27 +958,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>19740</v>
+        <v>6010</v>
       </c>
       <c r="F17" t="n">
-        <v>523</v>
+        <v>3435</v>
       </c>
       <c r="G17" t="n">
-        <v>10324020</v>
+        <v>20644350</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -990,27 +990,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>25150</v>
+        <v>25800</v>
       </c>
       <c r="F18" t="n">
-        <v>821</v>
+        <v>351</v>
       </c>
       <c r="G18" t="n">
-        <v>20648150</v>
+        <v>9055800</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1022,27 +1022,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>153500</v>
+        <v>49150</v>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>420</v>
       </c>
       <c r="G19" t="n">
-        <v>3684000</v>
+        <v>20643000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6240</v>
+        <v>19280</v>
       </c>
       <c r="F20" t="n">
-        <v>3308</v>
+        <v>1071</v>
       </c>
       <c r="G20" t="n">
-        <v>20641920</v>
+        <v>20648880</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1086,27 +1086,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>15520</v>
+        <v>19740</v>
       </c>
       <c r="F21" t="n">
-        <v>1330</v>
+        <v>523</v>
       </c>
       <c r="G21" t="n">
-        <v>20641600</v>
+        <v>10324020</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1118,27 +1118,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>24200</v>
+        <v>25150</v>
       </c>
       <c r="F22" t="n">
-        <v>210</v>
+        <v>821</v>
       </c>
       <c r="G22" t="n">
-        <v>5082000</v>
+        <v>20648150</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1150,27 +1150,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>36300</v>
+        <v>153500</v>
       </c>
       <c r="F23" t="n">
-        <v>569</v>
+        <v>24</v>
       </c>
       <c r="G23" t="n">
-        <v>20654700</v>
+        <v>3684000</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1182,27 +1182,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>279500</v>
+        <v>6240</v>
       </c>
       <c r="F24" t="n">
-        <v>43</v>
+        <v>3308</v>
       </c>
       <c r="G24" t="n">
-        <v>12018500</v>
+        <v>20641920</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1214,27 +1214,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>132600</v>
+        <v>15520</v>
       </c>
       <c r="F25" t="n">
-        <v>90</v>
+        <v>1330</v>
       </c>
       <c r="G25" t="n">
-        <v>11934000</v>
+        <v>20641600</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>44600</v>
+        <v>24200</v>
       </c>
       <c r="F26" t="n">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="G26" t="n">
-        <v>6199400</v>
+        <v>5082000</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1278,27 +1278,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>147100</v>
+        <v>36300</v>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>569</v>
       </c>
       <c r="G27" t="n">
-        <v>882600</v>
+        <v>20654700</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1324,13 +1324,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>33500</v>
+        <v>279500</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="G28" t="n">
-        <v>268000</v>
+        <v>12018500</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1356,13 +1356,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>143100</v>
+        <v>132600</v>
       </c>
       <c r="F29" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G29" t="n">
-        <v>13594500</v>
+        <v>11934000</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>83800</v>
+        <v>44600</v>
       </c>
       <c r="F30" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="G30" t="n">
-        <v>8882800</v>
+        <v>6199400</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1406,27 +1406,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>42300</v>
+        <v>147100</v>
       </c>
       <c r="F31" t="n">
-        <v>488</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
-        <v>20642400</v>
+        <v>882600</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1452,62 +1452,62 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>81200</v>
+        <v>33500</v>
       </c>
       <c r="F32" t="n">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>10962000</v>
+        <v>268000</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>78600</v>
+        <v>143100</v>
       </c>
       <c r="F33" t="n">
-        <v>389</v>
+        <v>95</v>
       </c>
       <c r="G33" t="n">
-        <v>30575400</v>
+        <v>13594500</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1516,30 +1516,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>92500</v>
+        <v>83800</v>
       </c>
       <c r="F34" t="n">
         <v>106</v>
       </c>
       <c r="G34" t="n">
-        <v>9805000</v>
+        <v>8882800</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1548,196 +1548,190 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>25550</v>
+        <v>42300</v>
       </c>
       <c r="F35" t="n">
-        <v>1151</v>
+        <v>488</v>
       </c>
       <c r="G35" t="n">
-        <v>29408050</v>
+        <v>20642400</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>21800</v>
+        <v>81200</v>
       </c>
       <c r="F36" t="n">
-        <v>832</v>
+        <v>135</v>
       </c>
       <c r="G36" t="n">
-        <v>18137600</v>
+        <v>10962000</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>32250</v>
+        <v>78600</v>
       </c>
       <c r="F37" t="n">
-        <v>878</v>
+        <v>389</v>
       </c>
       <c r="G37" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>30575400</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105800</v>
+        <v>92500</v>
       </c>
       <c r="F38" t="n">
-        <v>332</v>
+        <v>106</v>
       </c>
       <c r="G38" t="n">
-        <v>35125600</v>
-      </c>
-      <c r="H38" t="n">
-        <v>17.17</v>
-      </c>
+        <v>9805000</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>33750</v>
+        <v>25550</v>
       </c>
       <c r="F39" t="n">
-        <v>791</v>
+        <v>1151</v>
       </c>
       <c r="G39" t="n">
-        <v>26696250</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.29</v>
-      </c>
+        <v>29408050</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>86300</v>
+        <v>21800</v>
       </c>
       <c r="F40" t="n">
-        <v>352</v>
+        <v>832</v>
       </c>
       <c r="G40" t="n">
-        <v>30377600</v>
+        <v>18137600</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1746,96 +1740,100 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>21000</v>
+        <v>32250</v>
       </c>
       <c r="F41" t="n">
-        <v>1517</v>
+        <v>878</v>
       </c>
       <c r="G41" t="n">
-        <v>31857000</v>
+        <v>28315500</v>
       </c>
       <c r="H41" t="n">
-        <v>3.96</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>21900</v>
+        <v>105800</v>
       </c>
       <c r="F42" t="n">
-        <v>906</v>
+        <v>332</v>
       </c>
       <c r="G42" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>35125600</v>
+      </c>
+      <c r="H42" t="n">
+        <v>17.17</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>135300</v>
+        <v>33750</v>
       </c>
       <c r="F43" t="n">
-        <v>226</v>
+        <v>791</v>
       </c>
       <c r="G43" t="n">
-        <v>30577800</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1844,30 +1842,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>22250</v>
+        <v>86300</v>
       </c>
       <c r="F44" t="n">
-        <v>1399</v>
+        <v>352</v>
       </c>
       <c r="G44" t="n">
-        <v>31127750</v>
+        <v>30377600</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1876,66 +1874,64 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>33500</v>
+        <v>21000</v>
       </c>
       <c r="F45" t="n">
-        <v>848</v>
+        <v>1517</v>
       </c>
       <c r="G45" t="n">
-        <v>28408000</v>
+        <v>31857000</v>
       </c>
       <c r="H45" t="n">
-        <v>-9.07</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>300000</v>
+        <v>21900</v>
       </c>
       <c r="F46" t="n">
-        <v>104</v>
+        <v>906</v>
       </c>
       <c r="G46" t="n">
-        <v>31200000</v>
-      </c>
-      <c r="H46" t="n">
-        <v>20.95</v>
-      </c>
+        <v>19841400</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1944,64 +1940,62 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>28200</v>
+        <v>135300</v>
       </c>
       <c r="F47" t="n">
-        <v>1105</v>
+        <v>226</v>
       </c>
       <c r="G47" t="n">
-        <v>31161000</v>
+        <v>30577800</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>398000</v>
+        <v>22250</v>
       </c>
       <c r="F48" t="n">
-        <v>72</v>
+        <v>1399</v>
       </c>
       <c r="G48" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2010,175 +2004,181 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5620</v>
+        <v>33500</v>
       </c>
       <c r="F49" t="n">
-        <v>4707</v>
+        <v>848</v>
       </c>
       <c r="G49" t="n">
-        <v>26453340</v>
+        <v>28408000</v>
       </c>
       <c r="H49" t="n">
-        <v>-8.220000000000001</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>126900</v>
+        <v>300000</v>
       </c>
       <c r="F50" t="n">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="G50" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H50" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1671000</v>
+        <v>28200</v>
       </c>
       <c r="F51" t="n">
-        <v>44</v>
+        <v>1105</v>
       </c>
       <c r="G51" t="n">
-        <v>73524000</v>
+        <v>31161000</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>50600</v>
+        <v>398000</v>
       </c>
       <c r="F52" t="n">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="G52" t="n">
-        <v>9411600</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>11720</v>
+        <v>5620</v>
       </c>
       <c r="F53" t="n">
-        <v>665</v>
+        <v>4707</v>
       </c>
       <c r="G53" t="n">
-        <v>7793800</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>414000</v>
+        <v>126900</v>
       </c>
       <c r="F54" t="n">
-        <v>26</v>
+        <v>246</v>
       </c>
       <c r="G54" t="n">
-        <v>10764000</v>
+        <v>31217400</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2204,13 +2204,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>257000</v>
+        <v>1671000</v>
       </c>
       <c r="F55" t="n">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="G55" t="n">
-        <v>61423000</v>
+        <v>73524000</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2222,12 +2222,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2236,13 +2236,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>33900</v>
+        <v>50600</v>
       </c>
       <c r="F56" t="n">
-        <v>292</v>
+        <v>186</v>
       </c>
       <c r="G56" t="n">
-        <v>9898800</v>
+        <v>9411600</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>515000</v>
+        <v>11720</v>
       </c>
       <c r="F57" t="n">
-        <v>17</v>
+        <v>665</v>
       </c>
       <c r="G57" t="n">
-        <v>8755000</v>
+        <v>7793800</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>141200</v>
+        <v>414000</v>
       </c>
       <c r="F58" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="G58" t="n">
-        <v>11437200</v>
+        <v>10764000</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2318,27 +2318,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6320</v>
+        <v>257000</v>
       </c>
       <c r="F59" t="n">
-        <v>1396</v>
+        <v>239</v>
       </c>
       <c r="G59" t="n">
-        <v>8822720</v>
+        <v>61423000</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2350,27 +2350,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>90300</v>
+        <v>33900</v>
       </c>
       <c r="F60" t="n">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="G60" t="n">
-        <v>29979600</v>
+        <v>9898800</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2382,31 +2382,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>163100</v>
+        <v>515000</v>
       </c>
       <c r="F61" t="n">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="G61" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>8755000</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2416,12 +2414,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2430,13 +2428,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>37900</v>
+        <v>141200</v>
       </c>
       <c r="F62" t="n">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="G62" t="n">
-        <v>6177700</v>
+        <v>11437200</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2448,12 +2446,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2462,13 +2460,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>19990</v>
+        <v>6320</v>
       </c>
       <c r="F63" t="n">
-        <v>615</v>
+        <v>1396</v>
       </c>
       <c r="G63" t="n">
-        <v>12293850</v>
+        <v>8822720</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2480,27 +2478,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>35100</v>
+        <v>90300</v>
       </c>
       <c r="F64" t="n">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="G64" t="n">
-        <v>11232000</v>
+        <v>29979600</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2512,29 +2510,31 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>286000</v>
+        <v>163100</v>
       </c>
       <c r="F65" t="n">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G65" t="n">
-        <v>5720000</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2544,31 +2544,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>416000</v>
+        <v>37900</v>
       </c>
       <c r="F66" t="n">
-        <v>51</v>
+        <v>163</v>
       </c>
       <c r="G66" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H66" t="n">
-        <v>5.85</v>
-      </c>
+        <v>6177700</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2578,12 +2576,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2592,13 +2590,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>49450</v>
+        <v>19990</v>
       </c>
       <c r="F67" t="n">
-        <v>153</v>
+        <v>615</v>
       </c>
       <c r="G67" t="n">
-        <v>7565850</v>
+        <v>12293850</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2610,12 +2608,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2624,13 +2622,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>138000</v>
+        <v>35100</v>
       </c>
       <c r="F68" t="n">
-        <v>68</v>
+        <v>320</v>
       </c>
       <c r="G68" t="n">
-        <v>9384000</v>
+        <v>11232000</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2642,12 +2640,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2656,13 +2654,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>31950</v>
+        <v>286000</v>
       </c>
       <c r="F69" t="n">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="G69" t="n">
-        <v>10831050</v>
+        <v>5720000</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2674,142 +2672,142 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>124800</v>
+        <v>416000</v>
       </c>
       <c r="F70" t="n">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="G70" t="n">
-        <v>9734400</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H70" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>10800</v>
+        <v>49450</v>
       </c>
       <c r="F71" t="n">
-        <v>1892</v>
+        <v>153</v>
       </c>
       <c r="G71" t="n">
-        <v>20433600</v>
+        <v>7565850</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>11880</v>
+        <v>138000</v>
       </c>
       <c r="F72" t="n">
-        <v>1474</v>
+        <v>68</v>
       </c>
       <c r="G72" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>9384000</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>20200</v>
+        <v>31950</v>
       </c>
       <c r="F73" t="n">
-        <v>1517</v>
+        <v>339</v>
       </c>
       <c r="G73" t="n">
-        <v>30643400</v>
+        <v>10831050</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2818,13 +2816,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102200</v>
+        <v>124800</v>
       </c>
       <c r="F74" t="n">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="G74" t="n">
-        <v>20440000</v>
+        <v>9734400</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2836,31 +2834,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>23450</v>
+        <v>10800</v>
       </c>
       <c r="F75" t="n">
-        <v>762</v>
+        <v>1892</v>
       </c>
       <c r="G75" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2870,12 +2866,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2884,16 +2880,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>22050</v>
+        <v>11880</v>
       </c>
       <c r="F76" t="n">
-        <v>875</v>
+        <v>1474</v>
       </c>
       <c r="G76" t="n">
-        <v>19293750</v>
+        <v>17511120</v>
       </c>
       <c r="H76" t="n">
-        <v>-3.5</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="77">
@@ -2904,12 +2900,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2918,13 +2914,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>32550</v>
+        <v>20200</v>
       </c>
       <c r="F77" t="n">
-        <v>628</v>
+        <v>1517</v>
       </c>
       <c r="G77" t="n">
-        <v>20441400</v>
+        <v>30643400</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2936,110 +2932,112 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>99700</v>
+        <v>102200</v>
       </c>
       <c r="F78" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="G78" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1662000</v>
+        <v>23450</v>
       </c>
       <c r="F79" t="n">
-        <v>150</v>
+        <v>762</v>
       </c>
       <c r="G79" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H79" t="inlineStr"/>
+        <v>17868900</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-10.67</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>49700</v>
+        <v>22050</v>
       </c>
       <c r="F80" t="n">
-        <v>402</v>
+        <v>875</v>
       </c>
       <c r="G80" t="n">
-        <v>19979400</v>
-      </c>
-      <c r="H80" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3048,47 +3046,49 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>435000</v>
+        <v>32550</v>
       </c>
       <c r="F81" t="n">
-        <v>46</v>
+        <v>628</v>
       </c>
       <c r="G81" t="n">
-        <v>20010000</v>
+        <v>20441400</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>268500</v>
+        <v>99700</v>
       </c>
       <c r="F82" t="n">
-        <v>931</v>
+        <v>180</v>
       </c>
       <c r="G82" t="n">
-        <v>249973500</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>13570</v>
+        <v>1662000</v>
       </c>
       <c r="F83" t="n">
-        <v>1474</v>
+        <v>150</v>
       </c>
       <c r="G83" t="n">
-        <v>20002180</v>
+        <v>249300000</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>343500</v>
+        <v>49700</v>
       </c>
       <c r="F84" t="n">
-        <v>87</v>
+        <v>402</v>
       </c>
       <c r="G84" t="n">
-        <v>29884500</v>
+        <v>19979400</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3162,12 +3162,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3176,13 +3176,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>34150</v>
+        <v>435000</v>
       </c>
       <c r="F85" t="n">
-        <v>586</v>
+        <v>46</v>
       </c>
       <c r="G85" t="n">
-        <v>20011900</v>
+        <v>20010000</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3208,13 +3208,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>488000</v>
+        <v>268500</v>
       </c>
       <c r="F86" t="n">
-        <v>41</v>
+        <v>931</v>
       </c>
       <c r="G86" t="n">
-        <v>20008000</v>
+        <v>249973500</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3240,13 +3240,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>153600</v>
+        <v>13570</v>
       </c>
       <c r="F87" t="n">
-        <v>130</v>
+        <v>1474</v>
       </c>
       <c r="G87" t="n">
-        <v>19968000</v>
+        <v>20002180</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3258,12 +3258,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3272,13 +3272,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>99800</v>
+        <v>343500</v>
       </c>
       <c r="F88" t="n">
-        <v>200</v>
+        <v>87</v>
       </c>
       <c r="G88" t="n">
-        <v>19960000</v>
+        <v>29884500</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3290,12 +3290,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6040</v>
+        <v>34150</v>
       </c>
       <c r="F89" t="n">
-        <v>3311</v>
+        <v>586</v>
       </c>
       <c r="G89" t="n">
-        <v>19998440</v>
+        <v>20011900</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3322,12 +3322,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3336,13 +3336,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>26250</v>
+        <v>488000</v>
       </c>
       <c r="F90" t="n">
-        <v>762</v>
+        <v>41</v>
       </c>
       <c r="G90" t="n">
-        <v>20002500</v>
+        <v>20008000</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3354,12 +3354,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>22850</v>
+        <v>153600</v>
       </c>
       <c r="F91" t="n">
-        <v>875</v>
+        <v>130</v>
       </c>
       <c r="G91" t="n">
-        <v>19993750</v>
+        <v>19968000</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3400,13 +3400,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>168500</v>
+        <v>99800</v>
       </c>
       <c r="F92" t="n">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="G92" t="n">
-        <v>20051500</v>
+        <v>19960000</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3418,12 +3418,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3432,13 +3432,13 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>22850</v>
+        <v>6040</v>
       </c>
       <c r="F93" t="n">
-        <v>875</v>
+        <v>3311</v>
       </c>
       <c r="G93" t="n">
-        <v>19993750</v>
+        <v>19998440</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3464,13 +3464,13 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>37900</v>
+        <v>26250</v>
       </c>
       <c r="F94" t="n">
-        <v>528</v>
+        <v>762</v>
       </c>
       <c r="G94" t="n">
-        <v>20011200</v>
+        <v>20002500</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3496,13 +3496,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>239000</v>
+        <v>22850</v>
       </c>
       <c r="F95" t="n">
-        <v>84</v>
+        <v>875</v>
       </c>
       <c r="G95" t="n">
-        <v>20076000</v>
+        <v>19993750</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3528,13 +3528,13 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>298000</v>
+        <v>168500</v>
       </c>
       <c r="F96" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G96" t="n">
-        <v>34866000</v>
+        <v>20051500</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -3546,12 +3546,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3560,13 +3560,13 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>393000</v>
+        <v>22850</v>
       </c>
       <c r="F97" t="n">
-        <v>51</v>
+        <v>875</v>
       </c>
       <c r="G97" t="n">
-        <v>20043000</v>
+        <v>19993750</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3592,13 +3592,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>110900</v>
+        <v>37900</v>
       </c>
       <c r="F98" t="n">
-        <v>180</v>
+        <v>528</v>
       </c>
       <c r="G98" t="n">
-        <v>19962000</v>
+        <v>20011200</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3624,13 +3624,13 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>44500</v>
+        <v>239000</v>
       </c>
       <c r="F99" t="n">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="G99" t="n">
-        <v>19980500</v>
+        <v>20076000</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -3642,12 +3642,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3656,13 +3656,13 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>135000</v>
+        <v>298000</v>
       </c>
       <c r="F100" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="G100" t="n">
-        <v>19980000</v>
+        <v>34866000</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3674,12 +3674,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3688,13 +3688,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>33750</v>
+        <v>393000</v>
       </c>
       <c r="F101" t="n">
-        <v>593</v>
+        <v>51</v>
       </c>
       <c r="G101" t="n">
-        <v>20013750</v>
+        <v>20043000</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3706,29 +3706,157 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F102" t="n">
+        <v>180</v>
+      </c>
+      <c r="G102" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F103" t="n">
+        <v>449</v>
+      </c>
+      <c r="G103" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F104" t="n">
+        <v>148</v>
+      </c>
+      <c r="G104" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F105" t="n">
+        <v>593</v>
+      </c>
+      <c r="G105" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
         <v>124600</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F106" t="n">
         <v>161</v>
       </c>
-      <c r="G102" t="n">
+      <c r="G106" t="n">
         <v>20060600</v>
       </c>
-      <c r="H102" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1853000</v>
+        <v>29000</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>353</v>
       </c>
       <c r="G2" t="n">
-        <v>20383000</v>
+        <v>10237000</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -510,12 +510,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>269000</v>
+        <v>1853000</v>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>20444000</v>
+        <v>20383000</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -542,27 +542,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106300</v>
+        <v>269000</v>
       </c>
       <c r="F4" t="n">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="G4" t="n">
-        <v>20622200</v>
+        <v>20444000</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -574,12 +574,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,45 +588,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>123100</v>
+        <v>106300</v>
       </c>
       <c r="F5" t="n">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="G5" t="n">
-        <v>20557700</v>
+        <v>20622200</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1856000</v>
+        <v>123100</v>
       </c>
       <c r="F6" t="n">
-        <v>23</v>
+        <v>167</v>
       </c>
       <c r="G6" t="n">
-        <v>42688000</v>
+        <v>20557700</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -638,12 +638,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49000</v>
+        <v>1856000</v>
       </c>
       <c r="F7" t="n">
-        <v>167</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>8183000</v>
+        <v>42688000</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -670,12 +670,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,13 +684,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>13340</v>
+        <v>49000</v>
       </c>
       <c r="F8" t="n">
-        <v>236</v>
+        <v>167</v>
       </c>
       <c r="G8" t="n">
-        <v>3148240</v>
+        <v>8183000</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -702,12 +702,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -716,13 +716,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>29800</v>
+        <v>13340</v>
       </c>
       <c r="F9" t="n">
-        <v>66</v>
+        <v>236</v>
       </c>
       <c r="G9" t="n">
-        <v>1966800</v>
+        <v>3148240</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -748,13 +748,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>269500</v>
+        <v>29800</v>
       </c>
       <c r="F10" t="n">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>31801000</v>
+        <v>1966800</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>330000</v>
+        <v>269500</v>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="G11" t="n">
-        <v>7920000</v>
+        <v>31801000</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -798,27 +798,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>35550</v>
+        <v>330000</v>
       </c>
       <c r="F12" t="n">
-        <v>581</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>20654550</v>
+        <v>7920000</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -830,27 +830,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>574000</v>
+        <v>35550</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>581</v>
       </c>
       <c r="G13" t="n">
-        <v>12628000</v>
+        <v>20654550</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>165900</v>
+        <v>574000</v>
       </c>
       <c r="F14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>3981600</v>
+        <v>12628000</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -894,27 +894,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>91300</v>
+        <v>165900</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>4108500</v>
+        <v>3981600</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -926,27 +926,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>224500</v>
+        <v>91300</v>
       </c>
       <c r="F16" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>20654000</v>
+        <v>4108500</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -972,13 +972,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6010</v>
+        <v>224500</v>
       </c>
       <c r="F17" t="n">
-        <v>3435</v>
+        <v>92</v>
       </c>
       <c r="G17" t="n">
-        <v>20644350</v>
+        <v>20654000</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -990,27 +990,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>25800</v>
+        <v>6010</v>
       </c>
       <c r="F18" t="n">
-        <v>351</v>
+        <v>3435</v>
       </c>
       <c r="G18" t="n">
-        <v>9055800</v>
+        <v>20644350</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1022,27 +1022,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>49150</v>
+        <v>25800</v>
       </c>
       <c r="F19" t="n">
-        <v>420</v>
+        <v>351</v>
       </c>
       <c r="G19" t="n">
-        <v>20643000</v>
+        <v>9055800</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>19280</v>
+        <v>49150</v>
       </c>
       <c r="F20" t="n">
-        <v>1071</v>
+        <v>420</v>
       </c>
       <c r="G20" t="n">
-        <v>20648880</v>
+        <v>20643000</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1086,27 +1086,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>19740</v>
+        <v>19280</v>
       </c>
       <c r="F21" t="n">
-        <v>523</v>
+        <v>1071</v>
       </c>
       <c r="G21" t="n">
-        <v>10324020</v>
+        <v>20648880</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1118,27 +1118,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>25150</v>
+        <v>19740</v>
       </c>
       <c r="F22" t="n">
-        <v>821</v>
+        <v>523</v>
       </c>
       <c r="G22" t="n">
-        <v>20648150</v>
+        <v>10324020</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1150,27 +1150,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>153500</v>
+        <v>25150</v>
       </c>
       <c r="F23" t="n">
-        <v>24</v>
+        <v>821</v>
       </c>
       <c r="G23" t="n">
-        <v>3684000</v>
+        <v>20648150</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1182,27 +1182,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6240</v>
+        <v>153500</v>
       </c>
       <c r="F24" t="n">
-        <v>3308</v>
+        <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>20641920</v>
+        <v>3684000</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1228,13 +1228,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>15520</v>
+        <v>6240</v>
       </c>
       <c r="F25" t="n">
-        <v>1330</v>
+        <v>3308</v>
       </c>
       <c r="G25" t="n">
-        <v>20641600</v>
+        <v>20641920</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1246,27 +1246,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>24200</v>
+        <v>15520</v>
       </c>
       <c r="F26" t="n">
-        <v>210</v>
+        <v>1330</v>
       </c>
       <c r="G26" t="n">
-        <v>5082000</v>
+        <v>20641600</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1278,27 +1278,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>36300</v>
+        <v>24200</v>
       </c>
       <c r="F27" t="n">
-        <v>569</v>
+        <v>210</v>
       </c>
       <c r="G27" t="n">
-        <v>20654700</v>
+        <v>5082000</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1310,27 +1310,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>279500</v>
+        <v>36300</v>
       </c>
       <c r="F28" t="n">
-        <v>43</v>
+        <v>569</v>
       </c>
       <c r="G28" t="n">
-        <v>12018500</v>
+        <v>20654700</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1356,13 +1356,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>132600</v>
+        <v>279500</v>
       </c>
       <c r="F29" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="G29" t="n">
-        <v>11934000</v>
+        <v>12018500</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>44600</v>
+        <v>132600</v>
       </c>
       <c r="F30" t="n">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="G30" t="n">
-        <v>6199400</v>
+        <v>11934000</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1420,13 +1420,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>147100</v>
+        <v>44600</v>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>139</v>
       </c>
       <c r="G31" t="n">
-        <v>882600</v>
+        <v>6199400</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>33500</v>
+        <v>147100</v>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>268000</v>
+        <v>882600</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>143100</v>
+        <v>33500</v>
       </c>
       <c r="F33" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="G33" t="n">
-        <v>13594500</v>
+        <v>268000</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>83800</v>
+        <v>143100</v>
       </c>
       <c r="F34" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="G34" t="n">
-        <v>8882800</v>
+        <v>13594500</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1534,27 +1534,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>42300</v>
+        <v>83800</v>
       </c>
       <c r="F35" t="n">
-        <v>488</v>
+        <v>106</v>
       </c>
       <c r="G35" t="n">
-        <v>20642400</v>
+        <v>8882800</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1566,34 +1566,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>81200</v>
+        <v>42300</v>
       </c>
       <c r="F36" t="n">
-        <v>135</v>
+        <v>488</v>
       </c>
       <c r="G36" t="n">
-        <v>10962000</v>
+        <v>20642400</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1608,49 +1608,49 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>78600</v>
+        <v>81200</v>
       </c>
       <c r="F37" t="n">
-        <v>389</v>
+        <v>135</v>
       </c>
       <c r="G37" t="n">
-        <v>30575400</v>
+        <v>10962000</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>92500</v>
+        <v>78600</v>
       </c>
       <c r="F38" t="n">
-        <v>106</v>
+        <v>389</v>
       </c>
       <c r="G38" t="n">
-        <v>9805000</v>
+        <v>30575400</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1662,95 +1662,93 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>25550</v>
+        <v>92500</v>
       </c>
       <c r="F39" t="n">
-        <v>1151</v>
+        <v>106</v>
       </c>
       <c r="G39" t="n">
-        <v>29408050</v>
+        <v>9805000</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>21800</v>
+        <v>25550</v>
       </c>
       <c r="F40" t="n">
-        <v>832</v>
+        <v>1151</v>
       </c>
       <c r="G40" t="n">
-        <v>18137600</v>
+        <v>29408050</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>32250</v>
+        <v>21800</v>
       </c>
       <c r="F41" t="n">
-        <v>878</v>
+        <v>832</v>
       </c>
       <c r="G41" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>18137600</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1760,12 +1758,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1774,16 +1772,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>105800</v>
+        <v>32250</v>
       </c>
       <c r="F42" t="n">
-        <v>332</v>
+        <v>878</v>
       </c>
       <c r="G42" t="n">
-        <v>35125600</v>
+        <v>28315500</v>
       </c>
       <c r="H42" t="n">
-        <v>17.17</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="43">
@@ -1794,12 +1792,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1808,16 +1806,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>33750</v>
+        <v>105800</v>
       </c>
       <c r="F43" t="n">
-        <v>791</v>
+        <v>332</v>
       </c>
       <c r="G43" t="n">
-        <v>26696250</v>
+        <v>35125600</v>
       </c>
       <c r="H43" t="n">
-        <v>0.29</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="44">
@@ -1828,63 +1826,63 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>86300</v>
+        <v>33750</v>
       </c>
       <c r="F44" t="n">
-        <v>352</v>
+        <v>791</v>
       </c>
       <c r="G44" t="n">
-        <v>30377600</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>21000</v>
+        <v>86300</v>
       </c>
       <c r="F45" t="n">
-        <v>1517</v>
+        <v>352</v>
       </c>
       <c r="G45" t="n">
-        <v>31857000</v>
-      </c>
-      <c r="H45" t="n">
-        <v>3.96</v>
-      </c>
+        <v>30377600</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1894,29 +1892,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>21900</v>
+        <v>21000</v>
       </c>
       <c r="F46" t="n">
-        <v>906</v>
+        <v>1517</v>
       </c>
       <c r="G46" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>31857000</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1926,44 +1926,44 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>135300</v>
+        <v>21900</v>
       </c>
       <c r="F47" t="n">
-        <v>226</v>
+        <v>906</v>
       </c>
       <c r="G47" t="n">
-        <v>30577800</v>
+        <v>19841400</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>22250</v>
+        <v>135300</v>
       </c>
       <c r="F48" t="n">
-        <v>1399</v>
+        <v>226</v>
       </c>
       <c r="G48" t="n">
-        <v>31127750</v>
+        <v>30577800</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1990,31 +1990,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>33500</v>
+        <v>22250</v>
       </c>
       <c r="F49" t="n">
-        <v>848</v>
+        <v>1399</v>
       </c>
       <c r="G49" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2024,12 +2022,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2038,49 +2036,51 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>300000</v>
+        <v>33500</v>
       </c>
       <c r="F50" t="n">
-        <v>104</v>
+        <v>848</v>
       </c>
       <c r="G50" t="n">
-        <v>31200000</v>
+        <v>28408000</v>
       </c>
       <c r="H50" t="n">
-        <v>20.95</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>28200</v>
+        <v>300000</v>
       </c>
       <c r="F51" t="n">
-        <v>1105</v>
+        <v>104</v>
       </c>
       <c r="G51" t="n">
-        <v>31161000</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H51" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2090,31 +2090,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>398000</v>
+        <v>28200</v>
       </c>
       <c r="F52" t="n">
-        <v>72</v>
+        <v>1105</v>
       </c>
       <c r="G52" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31161000</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2124,12 +2122,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2138,16 +2136,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5620</v>
+        <v>398000</v>
       </c>
       <c r="F53" t="n">
-        <v>4707</v>
+        <v>72</v>
       </c>
       <c r="G53" t="n">
-        <v>26453340</v>
+        <v>28656000</v>
       </c>
       <c r="H53" t="n">
-        <v>-8.220000000000001</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="54">
@@ -2158,59 +2156,61 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>126900</v>
+        <v>5620</v>
       </c>
       <c r="F54" t="n">
-        <v>246</v>
+        <v>4707</v>
       </c>
       <c r="G54" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1671000</v>
+        <v>126900</v>
       </c>
       <c r="F55" t="n">
-        <v>44</v>
+        <v>246</v>
       </c>
       <c r="G55" t="n">
-        <v>73524000</v>
+        <v>31217400</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2222,27 +2222,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>50600</v>
+        <v>1671000</v>
       </c>
       <c r="F56" t="n">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G56" t="n">
-        <v>9411600</v>
+        <v>73524000</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>11720</v>
+        <v>50600</v>
       </c>
       <c r="F57" t="n">
-        <v>665</v>
+        <v>186</v>
       </c>
       <c r="G57" t="n">
-        <v>7793800</v>
+        <v>9411600</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>414000</v>
+        <v>11720</v>
       </c>
       <c r="F58" t="n">
-        <v>26</v>
+        <v>665</v>
       </c>
       <c r="G58" t="n">
-        <v>10764000</v>
+        <v>7793800</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2318,27 +2318,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>257000</v>
+        <v>414000</v>
       </c>
       <c r="F59" t="n">
-        <v>239</v>
+        <v>26</v>
       </c>
       <c r="G59" t="n">
-        <v>61423000</v>
+        <v>10764000</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2350,27 +2350,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>33900</v>
+        <v>257000</v>
       </c>
       <c r="F60" t="n">
-        <v>292</v>
+        <v>239</v>
       </c>
       <c r="G60" t="n">
-        <v>9898800</v>
+        <v>61423000</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2396,13 +2396,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>515000</v>
+        <v>33900</v>
       </c>
       <c r="F61" t="n">
-        <v>17</v>
+        <v>292</v>
       </c>
       <c r="G61" t="n">
-        <v>8755000</v>
+        <v>9898800</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>141200</v>
+        <v>515000</v>
       </c>
       <c r="F62" t="n">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="G62" t="n">
-        <v>11437200</v>
+        <v>8755000</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6320</v>
+        <v>141200</v>
       </c>
       <c r="F63" t="n">
-        <v>1396</v>
+        <v>81</v>
       </c>
       <c r="G63" t="n">
-        <v>8822720</v>
+        <v>11437200</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2478,27 +2478,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>90300</v>
+        <v>6320</v>
       </c>
       <c r="F64" t="n">
-        <v>332</v>
+        <v>1396</v>
       </c>
       <c r="G64" t="n">
-        <v>29979600</v>
+        <v>8822720</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2510,31 +2510,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>163100</v>
+        <v>90300</v>
       </c>
       <c r="F65" t="n">
-        <v>119</v>
+        <v>332</v>
       </c>
       <c r="G65" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>29979600</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2544,29 +2542,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>37900</v>
+        <v>163100</v>
       </c>
       <c r="F66" t="n">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="G66" t="n">
-        <v>6177700</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>19990</v>
+        <v>37900</v>
       </c>
       <c r="F67" t="n">
-        <v>615</v>
+        <v>163</v>
       </c>
       <c r="G67" t="n">
-        <v>12293850</v>
+        <v>6177700</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>35100</v>
+        <v>19990</v>
       </c>
       <c r="F68" t="n">
-        <v>320</v>
+        <v>615</v>
       </c>
       <c r="G68" t="n">
-        <v>11232000</v>
+        <v>12293850</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2640,12 +2640,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>286000</v>
+        <v>35100</v>
       </c>
       <c r="F69" t="n">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="G69" t="n">
-        <v>5720000</v>
+        <v>11232000</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2672,31 +2672,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>416000</v>
+        <v>286000</v>
       </c>
       <c r="F70" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G70" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H70" t="n">
-        <v>5.85</v>
-      </c>
+        <v>5720000</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2706,29 +2704,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>49450</v>
+        <v>416000</v>
       </c>
       <c r="F71" t="n">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="G71" t="n">
-        <v>7565850</v>
-      </c>
-      <c r="H71" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H71" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>138000</v>
+        <v>49450</v>
       </c>
       <c r="F72" t="n">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="G72" t="n">
-        <v>9384000</v>
+        <v>7565850</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2784,13 +2784,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>31950</v>
+        <v>138000</v>
       </c>
       <c r="F73" t="n">
-        <v>339</v>
+        <v>68</v>
       </c>
       <c r="G73" t="n">
-        <v>10831050</v>
+        <v>9384000</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2816,45 +2816,45 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>124800</v>
+        <v>31950</v>
       </c>
       <c r="F74" t="n">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="G74" t="n">
-        <v>9734400</v>
+        <v>10831050</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>10800</v>
+        <v>124800</v>
       </c>
       <c r="F75" t="n">
-        <v>1892</v>
+        <v>78</v>
       </c>
       <c r="G75" t="n">
-        <v>20433600</v>
+        <v>9734400</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2866,31 +2866,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>11880</v>
+        <v>10800</v>
       </c>
       <c r="F76" t="n">
-        <v>1474</v>
+        <v>1892</v>
       </c>
       <c r="G76" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2900,29 +2898,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>20200</v>
+        <v>11880</v>
       </c>
       <c r="F77" t="n">
-        <v>1517</v>
+        <v>1474</v>
       </c>
       <c r="G77" t="n">
-        <v>30643400</v>
-      </c>
-      <c r="H77" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2932,27 +2932,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>102200</v>
+        <v>20200</v>
       </c>
       <c r="F78" t="n">
-        <v>200</v>
+        <v>1517</v>
       </c>
       <c r="G78" t="n">
-        <v>20440000</v>
+        <v>30643400</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2964,31 +2964,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>23450</v>
+        <v>102200</v>
       </c>
       <c r="F79" t="n">
-        <v>762</v>
+        <v>200</v>
       </c>
       <c r="G79" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2998,12 +2996,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3012,16 +3010,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>22050</v>
+        <v>23450</v>
       </c>
       <c r="F80" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G80" t="n">
-        <v>19293750</v>
+        <v>17868900</v>
       </c>
       <c r="H80" t="n">
-        <v>-3.5</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="81">
@@ -3032,29 +3030,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>32550</v>
+        <v>22050</v>
       </c>
       <c r="F81" t="n">
-        <v>628</v>
+        <v>875</v>
       </c>
       <c r="G81" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H81" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3064,63 +3064,63 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>99700</v>
+        <v>32550</v>
       </c>
       <c r="F82" t="n">
-        <v>180</v>
+        <v>628</v>
       </c>
       <c r="G82" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20441400</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1662000</v>
+        <v>99700</v>
       </c>
       <c r="F83" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G83" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H83" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>49700</v>
+        <v>1662000</v>
       </c>
       <c r="F84" t="n">
-        <v>402</v>
+        <v>150</v>
       </c>
       <c r="G84" t="n">
-        <v>19979400</v>
+        <v>249300000</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3162,12 +3162,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3176,13 +3176,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>435000</v>
+        <v>49700</v>
       </c>
       <c r="F85" t="n">
-        <v>46</v>
+        <v>402</v>
       </c>
       <c r="G85" t="n">
-        <v>20010000</v>
+        <v>19979400</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3208,13 +3208,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>268500</v>
+        <v>435000</v>
       </c>
       <c r="F86" t="n">
-        <v>931</v>
+        <v>46</v>
       </c>
       <c r="G86" t="n">
-        <v>249973500</v>
+        <v>20010000</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3240,13 +3240,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>13570</v>
+        <v>268500</v>
       </c>
       <c r="F87" t="n">
-        <v>1474</v>
+        <v>931</v>
       </c>
       <c r="G87" t="n">
-        <v>20002180</v>
+        <v>249973500</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3258,12 +3258,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3272,13 +3272,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>343500</v>
+        <v>13570</v>
       </c>
       <c r="F88" t="n">
-        <v>87</v>
+        <v>1474</v>
       </c>
       <c r="G88" t="n">
-        <v>29884500</v>
+        <v>20002180</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3290,12 +3290,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>34150</v>
+        <v>343500</v>
       </c>
       <c r="F89" t="n">
-        <v>586</v>
+        <v>87</v>
       </c>
       <c r="G89" t="n">
-        <v>20011900</v>
+        <v>29884500</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3322,12 +3322,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3336,13 +3336,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>488000</v>
+        <v>34150</v>
       </c>
       <c r="F90" t="n">
-        <v>41</v>
+        <v>586</v>
       </c>
       <c r="G90" t="n">
-        <v>20008000</v>
+        <v>20011900</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3354,12 +3354,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>153600</v>
+        <v>488000</v>
       </c>
       <c r="F91" t="n">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="G91" t="n">
-        <v>19968000</v>
+        <v>20008000</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3400,13 +3400,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>99800</v>
+        <v>153600</v>
       </c>
       <c r="F92" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="G92" t="n">
-        <v>19960000</v>
+        <v>19968000</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3418,12 +3418,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3432,13 +3432,13 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6040</v>
+        <v>99800</v>
       </c>
       <c r="F93" t="n">
-        <v>3311</v>
+        <v>200</v>
       </c>
       <c r="G93" t="n">
-        <v>19998440</v>
+        <v>19960000</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3464,13 +3464,13 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>26250</v>
+        <v>6040</v>
       </c>
       <c r="F94" t="n">
-        <v>762</v>
+        <v>3311</v>
       </c>
       <c r="G94" t="n">
-        <v>20002500</v>
+        <v>19998440</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3496,13 +3496,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>22850</v>
+        <v>26250</v>
       </c>
       <c r="F95" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G95" t="n">
-        <v>19993750</v>
+        <v>20002500</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3528,13 +3528,13 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>168500</v>
+        <v>22850</v>
       </c>
       <c r="F96" t="n">
-        <v>119</v>
+        <v>875</v>
       </c>
       <c r="G96" t="n">
-        <v>20051500</v>
+        <v>19993750</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -3546,12 +3546,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3560,13 +3560,13 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>22850</v>
+        <v>168500</v>
       </c>
       <c r="F97" t="n">
-        <v>875</v>
+        <v>119</v>
       </c>
       <c r="G97" t="n">
-        <v>19993750</v>
+        <v>20051500</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3592,13 +3592,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>37900</v>
+        <v>22850</v>
       </c>
       <c r="F98" t="n">
-        <v>528</v>
+        <v>875</v>
       </c>
       <c r="G98" t="n">
-        <v>20011200</v>
+        <v>19993750</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3624,13 +3624,13 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>239000</v>
+        <v>37900</v>
       </c>
       <c r="F99" t="n">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="G99" t="n">
-        <v>20076000</v>
+        <v>20011200</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -3642,12 +3642,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3656,13 +3656,13 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>298000</v>
+        <v>239000</v>
       </c>
       <c r="F100" t="n">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="G100" t="n">
-        <v>34866000</v>
+        <v>20076000</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3674,12 +3674,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3688,13 +3688,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>393000</v>
+        <v>298000</v>
       </c>
       <c r="F101" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="G101" t="n">
-        <v>20043000</v>
+        <v>34866000</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3706,12 +3706,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3720,13 +3720,13 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>110900</v>
+        <v>393000</v>
       </c>
       <c r="F102" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="G102" t="n">
-        <v>19962000</v>
+        <v>20043000</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -3738,12 +3738,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3752,13 +3752,13 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>44500</v>
+        <v>110900</v>
       </c>
       <c r="F103" t="n">
-        <v>449</v>
+        <v>180</v>
       </c>
       <c r="G103" t="n">
-        <v>19980500</v>
+        <v>19962000</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3770,12 +3770,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3784,13 +3784,13 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>135000</v>
+        <v>44500</v>
       </c>
       <c r="F104" t="n">
-        <v>148</v>
+        <v>449</v>
       </c>
       <c r="G104" t="n">
-        <v>19980000</v>
+        <v>19980500</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3802,12 +3802,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3816,13 +3816,13 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>33750</v>
+        <v>135000</v>
       </c>
       <c r="F105" t="n">
-        <v>593</v>
+        <v>148</v>
       </c>
       <c r="G105" t="n">
-        <v>20013750</v>
+        <v>19980000</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3834,29 +3834,61 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F106" t="n">
+        <v>593</v>
+      </c>
+      <c r="G106" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
         <v>124600</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F107" t="n">
         <v>161</v>
       </c>
-      <c r="G106" t="n">
+      <c r="G107" t="n">
         <v>20060600</v>
       </c>
-      <c r="H106" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
